--- a/src/attributions/attributions_saliency_traj_353.xlsx
+++ b/src/attributions/attributions_saliency_traj_353.xlsx
@@ -1568,1709 +1568,1709 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>9.130253602052107e-06</v>
+        <v>0.04120663553476334</v>
       </c>
       <c r="B3" t="n">
-        <v>8.323579095304012e-05</v>
+        <v>0.3311502039432526</v>
       </c>
       <c r="C3" t="n">
-        <v>1.376294221699936e-05</v>
+        <v>0.0780925452709198</v>
       </c>
       <c r="D3" t="n">
-        <v>4.648383765015751e-05</v>
+        <v>0.0307968445122242</v>
       </c>
       <c r="E3" t="n">
-        <v>3.249688234063797e-07</v>
+        <v>0.09189943224191666</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0001127114373957738</v>
+        <v>0.1041449084877968</v>
       </c>
       <c r="G3" t="n">
-        <v>1.963365866686217e-05</v>
+        <v>0.000444214791059494</v>
       </c>
       <c r="H3" t="n">
-        <v>4.321004234952852e-05</v>
+        <v>0.03616936877369881</v>
       </c>
       <c r="I3" t="n">
-        <v>8.029635864659213e-06</v>
+        <v>0.04504822567105293</v>
       </c>
       <c r="J3" t="n">
-        <v>2.957591823360417e-05</v>
+        <v>0.03487252071499825</v>
       </c>
       <c r="K3" t="n">
-        <v>6.957604637136683e-05</v>
+        <v>0.4579297304153442</v>
       </c>
       <c r="L3" t="n">
-        <v>1.833630267356057e-05</v>
+        <v>0.06022742390632629</v>
       </c>
       <c r="M3" t="n">
-        <v>4.008270479971543e-05</v>
+        <v>0.07597805559635162</v>
       </c>
       <c r="N3" t="n">
-        <v>3.125332659692504e-05</v>
+        <v>0.1668030768632889</v>
       </c>
       <c r="O3" t="n">
-        <v>7.727537013124675e-05</v>
+        <v>0.06762030720710754</v>
       </c>
       <c r="P3" t="n">
-        <v>1.9881652406184e-05</v>
+        <v>0.03323857113718987</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.560874079586938e-05</v>
+        <v>0.05483071878552437</v>
       </c>
       <c r="R3" t="n">
-        <v>1.267280254069192e-06</v>
+        <v>0.01636452041566372</v>
       </c>
       <c r="S3" t="n">
-        <v>3.204337417628267e-06</v>
+        <v>0.00585032906383276</v>
       </c>
       <c r="T3" t="n">
-        <v>2.340233777431422e-06</v>
+        <v>0.03856267407536507</v>
       </c>
       <c r="U3" t="n">
-        <v>1.485362008679658e-05</v>
+        <v>0.01436383463442326</v>
       </c>
       <c r="V3" t="n">
-        <v>4.963748096997733e-07</v>
+        <v>0.1019543260335922</v>
       </c>
       <c r="W3" t="n">
-        <v>2.34746839851141e-05</v>
+        <v>0.04030134901404381</v>
       </c>
       <c r="X3" t="n">
-        <v>1.869923835329246e-05</v>
+        <v>0.03981233760714531</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.957509448402561e-05</v>
+        <v>0.01714612916111946</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.595930709503591e-06</v>
+        <v>0.0528140589594841</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.883153789909557e-06</v>
+        <v>0.04268963262438774</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.987468385777902e-05</v>
+        <v>0.04238030686974525</v>
       </c>
       <c r="AC3" t="n">
-        <v>5.857502856088104e-06</v>
+        <v>0.06866846978664398</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.872402572189458e-05</v>
+        <v>0.05563525855541229</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.199558664666256e-05</v>
+        <v>0.07555005699396133</v>
       </c>
       <c r="AF3" t="n">
-        <v>6.108100933488458e-06</v>
+        <v>0.09878996759653091</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.060735667124391e-05</v>
+        <v>0.03791355341672897</v>
       </c>
       <c r="AH3" t="n">
-        <v>7.878745236666873e-06</v>
+        <v>0.0008624736219644547</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.18389407361974e-05</v>
+        <v>0.1347052454948425</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.353353218291886e-05</v>
+        <v>0.02663207799196243</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.441709264327073e-05</v>
+        <v>0.02794959209859371</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.039721155393636e-05</v>
+        <v>0.1148496270179749</v>
       </c>
       <c r="AM3" t="n">
-        <v>9.620945093047339e-06</v>
+        <v>0.06052206829190254</v>
       </c>
       <c r="AN3" t="n">
-        <v>4.60213186670444e-07</v>
+        <v>0.02443941310048103</v>
       </c>
       <c r="AO3" t="n">
-        <v>2.21675363718532e-05</v>
+        <v>0.07988196611404419</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.590583608252928e-05</v>
+        <v>0.02900230325758457</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8.944981345848646e-06</v>
+        <v>0.04267393797636032</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.916547807923052e-05</v>
+        <v>0.03687957301735878</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.501605301105883e-06</v>
+        <v>0.03698550909757614</v>
       </c>
       <c r="AT3" t="n">
-        <v>5.126768883201294e-06</v>
+        <v>0.03539322316646576</v>
       </c>
       <c r="AU3" t="n">
-        <v>4.226923920214176e-05</v>
+        <v>0.4177187979221344</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.254588369192788e-05</v>
+        <v>0.003787558525800705</v>
       </c>
       <c r="AW3" t="n">
-        <v>2.599765139166266e-05</v>
+        <v>2.267863601446152e-05</v>
       </c>
       <c r="AX3" t="n">
-        <v>2.763941665762104e-05</v>
+        <v>0.06305548548698425</v>
       </c>
       <c r="AY3" t="n">
-        <v>7.458787149516866e-05</v>
+        <v>0.08317422121763229</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2.723241050262004e-05</v>
+        <v>0.02815756946802139</v>
       </c>
       <c r="BA3" t="n">
-        <v>3.886316335410811e-06</v>
+        <v>0.04909295588731766</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.287892064283369e-05</v>
+        <v>0.03194527328014374</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.619881913939025e-06</v>
+        <v>0.01765286549925804</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.366688906680793e-05</v>
+        <v>0.1457555145025253</v>
       </c>
       <c r="BE3" t="n">
-        <v>9.018092896440066e-06</v>
+        <v>0.05434026569128036</v>
       </c>
       <c r="BF3" t="n">
-        <v>6.022095021762652e-06</v>
+        <v>0.02973518148064613</v>
       </c>
       <c r="BG3" t="n">
-        <v>6.645528628723696e-06</v>
+        <v>0.07186833024024963</v>
       </c>
       <c r="BH3" t="n">
-        <v>1.091892863769317e-05</v>
+        <v>0.02364079840481281</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.92592926598445e-06</v>
+        <v>0.06209578737616539</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1.421477804797178e-06</v>
+        <v>0.0369509719312191</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.847350621479563e-07</v>
+        <v>0.00360339879989624</v>
       </c>
       <c r="BL3" t="n">
-        <v>1.219858313561417e-05</v>
+        <v>0.05059969797730446</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.216133114212425e-05</v>
+        <v>0.01811272837221622</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.143006920756306e-05</v>
+        <v>0.001778785139322281</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.34425972646568e-05</v>
+        <v>0.02505897358059883</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.761975560541032e-06</v>
+        <v>0.02896001189947128</v>
       </c>
       <c r="BQ3" t="n">
-        <v>8.824042197375093e-06</v>
+        <v>0.02796904370188713</v>
       </c>
       <c r="BR3" t="n">
-        <v>8.286044248961844e-06</v>
+        <v>0.1378576010465622</v>
       </c>
       <c r="BS3" t="n">
-        <v>8.205994163290597e-06</v>
+        <v>0.006012254860252142</v>
       </c>
       <c r="BT3" t="n">
-        <v>1.06415682239458e-05</v>
+        <v>0.0142814926803112</v>
       </c>
       <c r="BU3" t="n">
-        <v>7.467332579835784e-06</v>
+        <v>0.01207277923822403</v>
       </c>
       <c r="BV3" t="n">
-        <v>2.51879700954305e-05</v>
+        <v>0.2297832816839218</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.179137416329468e-05</v>
+        <v>0.054854366928339</v>
       </c>
       <c r="BX3" t="n">
-        <v>1.87194709724281e-05</v>
+        <v>0.06635195761919022</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.225870073540136e-05</v>
+        <v>0.03745149821043015</v>
       </c>
       <c r="BZ3" t="n">
-        <v>4.148924199398607e-05</v>
+        <v>0.07363834232091904</v>
       </c>
       <c r="CA3" t="n">
-        <v>5.254500138107687e-06</v>
+        <v>0.04747511073946953</v>
       </c>
       <c r="CB3" t="n">
-        <v>7.412901140924077e-06</v>
+        <v>0.01119238696992397</v>
       </c>
       <c r="CC3" t="n">
-        <v>6.162229055917123e-07</v>
+        <v>0.03747002780437469</v>
       </c>
       <c r="CD3" t="n">
-        <v>7.491037649742793e-06</v>
+        <v>0.00393056683242321</v>
       </c>
       <c r="CE3" t="n">
-        <v>5.645641522278311e-06</v>
+        <v>0.1307951807975769</v>
       </c>
       <c r="CF3" t="n">
-        <v>3.273532684033853e-06</v>
+        <v>0.007850062102079391</v>
       </c>
       <c r="CG3" t="n">
-        <v>5.586862243944779e-06</v>
+        <v>0.01778643019497395</v>
       </c>
       <c r="CH3" t="n">
-        <v>7.214230208774097e-06</v>
+        <v>0.01380352489650249</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.618768328626174e-05</v>
+        <v>0.04221397638320923</v>
       </c>
       <c r="CJ3" t="n">
-        <v>6.803441465308424e-06</v>
+        <v>0.02858752012252808</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.067374796548393e-05</v>
+        <v>0.002722788136452436</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.412465735484147e-07</v>
+        <v>0.003128730226308107</v>
       </c>
       <c r="CM3" t="n">
-        <v>1.011001495498931e-05</v>
+        <v>0.06796245276927948</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.407099148309499e-06</v>
+        <v>0.1901995986700058</v>
       </c>
       <c r="CO3" t="n">
-        <v>6.725032562826527e-06</v>
+        <v>0.05309278145432472</v>
       </c>
       <c r="CP3" t="n">
-        <v>7.332168934226502e-06</v>
+        <v>0.03729431331157684</v>
       </c>
       <c r="CQ3" t="n">
-        <v>1.074455030902755e-05</v>
+        <v>0.05160889774560928</v>
       </c>
       <c r="CR3" t="n">
-        <v>2.70264763457817e-06</v>
+        <v>0.0329643078148365</v>
       </c>
       <c r="CS3" t="n">
-        <v>1.584424808243057e-06</v>
+        <v>0.03716418519616127</v>
       </c>
       <c r="CT3" t="n">
-        <v>1.907632758957334e-05</v>
+        <v>0.01031776890158653</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.417503335687798e-05</v>
+        <v>0.003501137020066381</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.922821977335843e-06</v>
+        <v>0.02056347578763962</v>
       </c>
       <c r="CW3" t="n">
-        <v>8.799906936474144e-06</v>
+        <v>0.1291991174221039</v>
       </c>
       <c r="CX3" t="n">
-        <v>2.784368007269222e-06</v>
+        <v>0.01089896075427532</v>
       </c>
       <c r="CY3" t="n">
-        <v>7.630149411852472e-06</v>
+        <v>0.00404741708189249</v>
       </c>
       <c r="CZ3" t="n">
-        <v>3.281024874013383e-07</v>
+        <v>0.005486043635755777</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.87881123565603e-05</v>
+        <v>0.04792409017682076</v>
       </c>
       <c r="DB3" t="n">
-        <v>5.125692723595421e-07</v>
+        <v>0.01216423511505127</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.591661202837713e-05</v>
+        <v>0.002606591209769249</v>
       </c>
       <c r="DD3" t="n">
-        <v>1.324408458458493e-07</v>
+        <v>0.01372227631509304</v>
       </c>
       <c r="DE3" t="n">
-        <v>1.378535853291396e-05</v>
+        <v>0.06509499251842499</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.363529554510023e-05</v>
+        <v>0.04053308814764023</v>
       </c>
       <c r="DG3" t="n">
-        <v>7.633570930920541e-06</v>
+        <v>0.01041600201278925</v>
       </c>
       <c r="DH3" t="n">
-        <v>2.477172165527008e-05</v>
+        <v>0.003607854247093201</v>
       </c>
       <c r="DI3" t="n">
-        <v>1.950781734194607e-05</v>
+        <v>0.08356700837612152</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.066605702566449e-06</v>
+        <v>0.04881690442562103</v>
       </c>
       <c r="DK3" t="n">
-        <v>1.527918584542931e-06</v>
+        <v>0.02873336523771286</v>
       </c>
       <c r="DL3" t="n">
-        <v>4.010798875242472e-05</v>
+        <v>0.005935462191700935</v>
       </c>
       <c r="DM3" t="n">
-        <v>1.194945161842043e-05</v>
+        <v>0.007274477742612362</v>
       </c>
       <c r="DN3" t="n">
-        <v>8.39184667711379e-06</v>
+        <v>0.03580912202596664</v>
       </c>
       <c r="DO3" t="n">
-        <v>8.959867045632564e-06</v>
+        <v>0.05888389050960541</v>
       </c>
       <c r="DP3" t="n">
-        <v>1.389327735523693e-05</v>
+        <v>0.0101199708878994</v>
       </c>
       <c r="DQ3" t="n">
-        <v>8.673887350596488e-06</v>
+        <v>0.06256896257400513</v>
       </c>
       <c r="DR3" t="n">
-        <v>9.905010301736183e-06</v>
+        <v>0.01221798732876778</v>
       </c>
       <c r="DS3" t="n">
-        <v>1.271974099381623e-07</v>
+        <v>0.006058325059711933</v>
       </c>
       <c r="DT3" t="n">
-        <v>6.980180387472501e-06</v>
+        <v>0.01706676743924618</v>
       </c>
       <c r="DU3" t="n">
-        <v>4.744256330013741e-06</v>
+        <v>0.06188397109508514</v>
       </c>
       <c r="DV3" t="n">
-        <v>2.040625304289279e-06</v>
+        <v>0.02785488404333591</v>
       </c>
       <c r="DW3" t="n">
-        <v>1.935377213158063e-06</v>
+        <v>0.04457414522767067</v>
       </c>
       <c r="DX3" t="n">
-        <v>2.247915745101636e-06</v>
+        <v>0.0731518343091011</v>
       </c>
       <c r="DY3" t="n">
-        <v>2.23208689931198e-06</v>
+        <v>0.01941163092851639</v>
       </c>
       <c r="DZ3" t="n">
-        <v>2.200730159529485e-05</v>
+        <v>0.01551004685461521</v>
       </c>
       <c r="EA3" t="n">
-        <v>1.173122564068763e-05</v>
+        <v>0.02721101604402065</v>
       </c>
       <c r="EB3" t="n">
-        <v>6.411481081158854e-06</v>
+        <v>0.1306418925523758</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.412586243532132e-07</v>
+        <v>0.0007347357459366322</v>
       </c>
       <c r="ED3" t="n">
-        <v>1.107898606278468e-05</v>
+        <v>0.04177054017782211</v>
       </c>
       <c r="EE3" t="n">
-        <v>2.958881623271736e-06</v>
+        <v>0.01176755502820015</v>
       </c>
       <c r="EF3" t="n">
-        <v>1.781378841769765e-06</v>
+        <v>0.0007195500656962395</v>
       </c>
       <c r="EG3" t="n">
-        <v>1.979523858608445e-06</v>
+        <v>0.05806050077080727</v>
       </c>
       <c r="EH3" t="n">
-        <v>6.702461178065278e-06</v>
+        <v>0.00571491988375783</v>
       </c>
       <c r="EI3" t="n">
-        <v>2.140585365850711e-06</v>
+        <v>0.06041940301656723</v>
       </c>
       <c r="EJ3" t="n">
-        <v>1.296249592996901e-06</v>
+        <v>0.005167815368622541</v>
       </c>
       <c r="EK3" t="n">
-        <v>1.932051600306295e-05</v>
+        <v>0.01190926600247622</v>
       </c>
       <c r="EL3" t="n">
-        <v>5.93321328778984e-06</v>
+        <v>0.001988187897950411</v>
       </c>
       <c r="EM3" t="n">
-        <v>8.064363100857008e-06</v>
+        <v>0.001393604674376547</v>
       </c>
       <c r="EN3" t="n">
-        <v>5.58382089366205e-06</v>
+        <v>0.008299406617879868</v>
       </c>
       <c r="EO3" t="n">
-        <v>3.340117018524325e-07</v>
+        <v>0.01975301094353199</v>
       </c>
       <c r="EP3" t="n">
-        <v>1.472557642046013e-06</v>
+        <v>0.06940743327140808</v>
       </c>
       <c r="EQ3" t="n">
-        <v>4.535130756266881e-06</v>
+        <v>0.00803816132247448</v>
       </c>
       <c r="ER3" t="n">
-        <v>7.41427720640786e-06</v>
+        <v>0.02742747589945793</v>
       </c>
       <c r="ES3" t="n">
-        <v>4.549829100142233e-07</v>
+        <v>0.02169357240200043</v>
       </c>
       <c r="ET3" t="n">
-        <v>1.112719655793626e-05</v>
+        <v>0.006477590184658766</v>
       </c>
       <c r="EU3" t="n">
-        <v>9.154803592537064e-06</v>
+        <v>0.03975440189242363</v>
       </c>
       <c r="EV3" t="n">
-        <v>3.339275281177834e-05</v>
+        <v>0.01234989706426859</v>
       </c>
       <c r="EW3" t="n">
-        <v>2.837288093360257e-06</v>
+        <v>0.01277120783925056</v>
       </c>
       <c r="EX3" t="n">
-        <v>4.419346169015625e-06</v>
+        <v>0.01474932767450809</v>
       </c>
       <c r="EY3" t="n">
-        <v>5.245595275482628e-06</v>
+        <v>0.1480559110641479</v>
       </c>
       <c r="EZ3" t="n">
-        <v>1.549198373140825e-06</v>
+        <v>0.005462266504764557</v>
       </c>
       <c r="FA3" t="n">
-        <v>6.189115083543584e-06</v>
+        <v>0.009884892031550407</v>
       </c>
       <c r="FB3" t="n">
-        <v>2.831230176525423e-06</v>
+        <v>0.01189590338617563</v>
       </c>
       <c r="FC3" t="n">
-        <v>1.400913697580108e-05</v>
+        <v>0.04327324032783508</v>
       </c>
       <c r="FD3" t="n">
-        <v>8.502293894707691e-06</v>
+        <v>0.0282086469233036</v>
       </c>
       <c r="FE3" t="n">
-        <v>1.169058850791771e-05</v>
+        <v>0.008841704577207565</v>
       </c>
       <c r="FF3" t="n">
-        <v>1.612252162885852e-07</v>
+        <v>0.01553825754672289</v>
       </c>
       <c r="FG3" t="n">
-        <v>2.006412614719011e-06</v>
+        <v>0.02652318589389324</v>
       </c>
       <c r="FH3" t="n">
-        <v>1.277355113415979e-05</v>
+        <v>0.07002973556518555</v>
       </c>
       <c r="FI3" t="n">
-        <v>6.59414445181028e-06</v>
+        <v>0.038176529109478</v>
       </c>
       <c r="FJ3" t="n">
-        <v>3.371086859260686e-05</v>
+        <v>0.06453295052051544</v>
       </c>
       <c r="FK3" t="n">
-        <v>6.166701041365741e-06</v>
+        <v>0.05946984142065048</v>
       </c>
       <c r="FL3" t="n">
-        <v>1.880573108792305e-05</v>
+        <v>0.002895686775445938</v>
       </c>
       <c r="FM3" t="n">
-        <v>8.387060006498359e-06</v>
+        <v>0.03831898421049118</v>
       </c>
       <c r="FN3" t="n">
-        <v>8.031095603655558e-06</v>
+        <v>0.03752502799034119</v>
       </c>
       <c r="FO3" t="n">
-        <v>1.081984555639792e-05</v>
+        <v>0.05867917835712433</v>
       </c>
       <c r="FP3" t="n">
-        <v>9.590596164343879e-06</v>
+        <v>0.1196775585412979</v>
       </c>
       <c r="FQ3" t="n">
-        <v>4.621264451998286e-05</v>
+        <v>0.151255339384079</v>
       </c>
       <c r="FR3" t="n">
-        <v>6.244970791158266e-06</v>
+        <v>0.08674514293670654</v>
       </c>
       <c r="FS3" t="n">
-        <v>2.901608240790665e-05</v>
+        <v>0.07621236145496368</v>
       </c>
       <c r="FT3" t="n">
-        <v>2.37640651903348e-05</v>
+        <v>0.06062205135822296</v>
       </c>
       <c r="FU3" t="n">
-        <v>3.435817052377388e-05</v>
+        <v>0.09642565250396729</v>
       </c>
       <c r="FV3" t="n">
-        <v>1.413686914020218e-05</v>
+        <v>0.009804777801036835</v>
       </c>
       <c r="FW3" t="n">
-        <v>7.084875505825039e-06</v>
+        <v>0.03847634419798851</v>
       </c>
       <c r="FX3" t="n">
-        <v>1.656433028074389e-06</v>
+        <v>0.04477328062057495</v>
       </c>
       <c r="FY3" t="n">
-        <v>9.876443073153496e-06</v>
+        <v>0.02199813723564148</v>
       </c>
       <c r="FZ3" t="n">
-        <v>4.388355137052713e-06</v>
+        <v>0.03186997771263123</v>
       </c>
       <c r="GA3" t="n">
-        <v>6.526724064315204e-06</v>
+        <v>0.04250307008624077</v>
       </c>
       <c r="GB3" t="n">
-        <v>6.061251042410731e-06</v>
+        <v>0.05544156581163406</v>
       </c>
       <c r="GC3" t="n">
-        <v>3.117677988484502e-05</v>
+        <v>0.02338532730937004</v>
       </c>
       <c r="GD3" t="n">
-        <v>4.95890617457917e-07</v>
+        <v>0.006101346574723721</v>
       </c>
       <c r="GE3" t="n">
-        <v>2.826968193403445e-05</v>
+        <v>0.02323443815112114</v>
       </c>
       <c r="GF3" t="n">
-        <v>1.278248601011001e-05</v>
+        <v>0.04334449395537376</v>
       </c>
       <c r="GG3" t="n">
-        <v>3.998831289209193e-06</v>
+        <v>0.03807352483272552</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7.53638540462731e-10</v>
+        <v>0.1240299940109253</v>
       </c>
       <c r="B4" t="n">
-        <v>9.388642085994547e-10</v>
+        <v>0.02937960624694824</v>
       </c>
       <c r="C4" t="n">
-        <v>6.46469988652143e-10</v>
+        <v>0.02021888457238674</v>
       </c>
       <c r="D4" t="n">
-        <v>2.305499680055334e-10</v>
+        <v>0.009567937813699245</v>
       </c>
       <c r="E4" t="n">
-        <v>1.170482377688131e-09</v>
+        <v>0.02800720557570457</v>
       </c>
       <c r="F4" t="n">
-        <v>3.177266449938543e-09</v>
+        <v>0.01840727031230927</v>
       </c>
       <c r="G4" t="n">
-        <v>3.063230225031077e-10</v>
+        <v>0.04416202008724213</v>
       </c>
       <c r="H4" t="n">
-        <v>1.738444055376931e-09</v>
+        <v>0.0002551521174609661</v>
       </c>
       <c r="I4" t="n">
-        <v>1.364231505540658e-10</v>
+        <v>0.006205272395163774</v>
       </c>
       <c r="J4" t="n">
-        <v>1.438880542492527e-10</v>
+        <v>0.1338363438844681</v>
       </c>
       <c r="K4" t="n">
-        <v>8.173179910642148e-10</v>
+        <v>0.04757872223854065</v>
       </c>
       <c r="L4" t="n">
-        <v>4.209187443038331e-10</v>
+        <v>0.02105667814612389</v>
       </c>
       <c r="M4" t="n">
-        <v>5.338799402565542e-10</v>
+        <v>0.02367136627435684</v>
       </c>
       <c r="N4" t="n">
-        <v>5.686074944222241e-10</v>
+        <v>0.01135506015270948</v>
       </c>
       <c r="O4" t="n">
-        <v>2.171630875125174e-09</v>
+        <v>0.06229101121425629</v>
       </c>
       <c r="P4" t="n">
-        <v>6.015000719727936e-10</v>
+        <v>0.004048776812851429</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.642094904497071e-09</v>
+        <v>0.01377856731414795</v>
       </c>
       <c r="R4" t="n">
-        <v>7.976826837952089e-11</v>
+        <v>0.0453856959939003</v>
       </c>
       <c r="S4" t="n">
-        <v>8.548872720837153e-11</v>
+        <v>0.01725084893405437</v>
       </c>
       <c r="T4" t="n">
-        <v>2.482925531843705e-10</v>
+        <v>0.05031145364046097</v>
       </c>
       <c r="U4" t="n">
-        <v>5.065288466443718e-11</v>
+        <v>0.03369640558958054</v>
       </c>
       <c r="V4" t="n">
-        <v>4.096537553621715e-10</v>
+        <v>0.001095228362828493</v>
       </c>
       <c r="W4" t="n">
-        <v>6.217684700438042e-10</v>
+        <v>0.01341363694518805</v>
       </c>
       <c r="X4" t="n">
-        <v>6.683857911582436e-10</v>
+        <v>0.02324622683227062</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.128836492815594e-11</v>
+        <v>0.003500632476061583</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.209451870933577e-10</v>
+        <v>0.04746660217642784</v>
       </c>
       <c r="AA4" t="n">
-        <v>9.512507448405927e-11</v>
+        <v>0.01596466451883316</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.466905344559848e-10</v>
+        <v>0.01715889386832714</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.855376768362561e-10</v>
+        <v>0.03094597905874252</v>
       </c>
       <c r="AD4" t="n">
-        <v>7.138119539895627e-10</v>
+        <v>0.0178568959236145</v>
       </c>
       <c r="AE4" t="n">
-        <v>6.02644434355426e-10</v>
+        <v>0.0004417290911078453</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.637583484954575e-10</v>
+        <v>0.004627392627298832</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.367793461299783e-10</v>
+        <v>0.05918845906853676</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.96168692401244e-10</v>
+        <v>0.02209405228495598</v>
       </c>
       <c r="AI4" t="n">
-        <v>3.070894927237333e-11</v>
+        <v>0.03200480714440346</v>
       </c>
       <c r="AJ4" t="n">
-        <v>3.312682350653517e-10</v>
+        <v>0.01039524935185909</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.275828969722227e-10</v>
+        <v>0.01226967386901379</v>
       </c>
       <c r="AL4" t="n">
-        <v>2.529953191388046e-10</v>
+        <v>0.03291181847453117</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.963084972356199e-10</v>
+        <v>0.06118956953287125</v>
       </c>
       <c r="AN4" t="n">
-        <v>3.248717961312764e-10</v>
+        <v>0.03833431750535965</v>
       </c>
       <c r="AO4" t="n">
-        <v>4.006435738723724e-10</v>
+        <v>0.03974520415067673</v>
       </c>
       <c r="AP4" t="n">
-        <v>8.024406694673303e-10</v>
+        <v>0.01753425039350986</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2.659872877508462e-10</v>
+        <v>0.02824100665748119</v>
       </c>
       <c r="AR4" t="n">
-        <v>5.461270324857992e-11</v>
+        <v>0.004667272325605154</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.99058638963956e-10</v>
+        <v>0.008544912561774254</v>
       </c>
       <c r="AT4" t="n">
-        <v>6.527668405809095e-10</v>
+        <v>0.04734713584184647</v>
       </c>
       <c r="AU4" t="n">
-        <v>9.453156035732491e-10</v>
+        <v>0.00143917603418231</v>
       </c>
       <c r="AV4" t="n">
-        <v>5.690731219587519e-10</v>
+        <v>0.06764589250087738</v>
       </c>
       <c r="AW4" t="n">
-        <v>7.80013886814146e-10</v>
+        <v>0.01028128247708082</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.810406047297874e-09</v>
+        <v>0.02624437399208546</v>
       </c>
       <c r="AY4" t="n">
-        <v>2.229483264670762e-09</v>
+        <v>0.1423909366130829</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4.691618205043824e-10</v>
+        <v>0.01320057734847069</v>
       </c>
       <c r="BA4" t="n">
-        <v>3.576806628657891e-10</v>
+        <v>0.00920107401907444</v>
       </c>
       <c r="BB4" t="n">
-        <v>8.198768330913708e-10</v>
+        <v>0.02776277437806129</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.744332704476051e-10</v>
+        <v>0.01641641557216644</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.007455950942983e-10</v>
+        <v>0.08086174726486206</v>
       </c>
       <c r="BE4" t="n">
-        <v>8.028855358332976e-13</v>
+        <v>0.004225845448672771</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.635321098651502e-10</v>
+        <v>0.0154491076245904</v>
       </c>
       <c r="BG4" t="n">
-        <v>6.866715529518785e-11</v>
+        <v>0.02141759172081947</v>
       </c>
       <c r="BH4" t="n">
-        <v>4.033890443899679e-10</v>
+        <v>0.07608826458454132</v>
       </c>
       <c r="BI4" t="n">
-        <v>5.197599017847665e-10</v>
+        <v>0.04629793018102646</v>
       </c>
       <c r="BJ4" t="n">
-        <v>3.395455305810202e-10</v>
+        <v>0.02646801620721817</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.105156297702251e-10</v>
+        <v>0.02585149370133877</v>
       </c>
       <c r="BL4" t="n">
-        <v>5.885679166262037e-10</v>
+        <v>0.0623672753572464</v>
       </c>
       <c r="BM4" t="n">
-        <v>4.495495642409253e-10</v>
+        <v>0.03129031881690025</v>
       </c>
       <c r="BN4" t="n">
-        <v>6.080662640073342e-10</v>
+        <v>0.02937946282327175</v>
       </c>
       <c r="BO4" t="n">
-        <v>7.344152369581636e-11</v>
+        <v>0.009167329408228397</v>
       </c>
       <c r="BP4" t="n">
-        <v>6.85033141323288e-10</v>
+        <v>0.01102286111563444</v>
       </c>
       <c r="BQ4" t="n">
-        <v>9.19993525805296e-11</v>
+        <v>0.004315064288675785</v>
       </c>
       <c r="BR4" t="n">
-        <v>2.039102775519552e-10</v>
+        <v>0.01306236535310745</v>
       </c>
       <c r="BS4" t="n">
-        <v>4.749646786983419e-10</v>
+        <v>0.001266641309484839</v>
       </c>
       <c r="BT4" t="n">
-        <v>5.598621566349493e-11</v>
+        <v>0.01436480227857828</v>
       </c>
       <c r="BU4" t="n">
-        <v>2.960776068761106e-10</v>
+        <v>0.01626301184296608</v>
       </c>
       <c r="BV4" t="n">
-        <v>2.294136408620417e-11</v>
+        <v>0.03739811480045319</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.272837113486247e-10</v>
+        <v>0.01367853861302137</v>
       </c>
       <c r="BX4" t="n">
-        <v>3.382250035599554e-10</v>
+        <v>0.0003856938565149903</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.012324668536735e-09</v>
+        <v>0.01840459741652012</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1.407863603475334e-09</v>
+        <v>0.03614657744765282</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.038259270225161e-10</v>
+        <v>0.02165941521525383</v>
       </c>
       <c r="CB4" t="n">
-        <v>6.412034792013799e-10</v>
+        <v>0.007338415831327438</v>
       </c>
       <c r="CC4" t="n">
-        <v>6.569579602544451e-11</v>
+        <v>0.01387508865445852</v>
       </c>
       <c r="CD4" t="n">
-        <v>4.931306057942564e-11</v>
+        <v>0.07963883876800537</v>
       </c>
       <c r="CE4" t="n">
-        <v>2.919295083447793e-10</v>
+        <v>0.014227787964046</v>
       </c>
       <c r="CF4" t="n">
-        <v>6.475427138941114e-11</v>
+        <v>0.01712742075324059</v>
       </c>
       <c r="CG4" t="n">
-        <v>8.509731114214603e-11</v>
+        <v>0.001840628683567047</v>
       </c>
       <c r="CH4" t="n">
-        <v>5.993427976136445e-11</v>
+        <v>0.004544701427221298</v>
       </c>
       <c r="CI4" t="n">
-        <v>5.766160326992065e-10</v>
+        <v>0.004628425929695368</v>
       </c>
       <c r="CJ4" t="n">
-        <v>2.686988964661907e-10</v>
+        <v>0.01827538572251797</v>
       </c>
       <c r="CK4" t="n">
-        <v>3.68640618031435e-10</v>
+        <v>0.007080343551933765</v>
       </c>
       <c r="CL4" t="n">
-        <v>3.228493861140436e-12</v>
+        <v>0.004593163728713989</v>
       </c>
       <c r="CM4" t="n">
-        <v>9.100470377276793e-12</v>
+        <v>0.06110986694693565</v>
       </c>
       <c r="CN4" t="n">
-        <v>5.308650186108821e-10</v>
+        <v>0.03009327501058578</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.021231640918607e-10</v>
+        <v>0.07937553524971008</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.005855065905337e-09</v>
+        <v>0.01561513170599937</v>
       </c>
       <c r="CQ4" t="n">
-        <v>6.237920180396372e-10</v>
+        <v>0.1129911690950394</v>
       </c>
       <c r="CR4" t="n">
-        <v>4.739591497049389e-10</v>
+        <v>0.01819100603461266</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.576570623524788e-10</v>
+        <v>0.008216573856770992</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.792526765382775e-10</v>
+        <v>0.03200176358222961</v>
       </c>
       <c r="CU4" t="n">
-        <v>5.036611683273406e-10</v>
+        <v>0.03271935880184174</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.368406221669005e-10</v>
+        <v>0.08506585657596588</v>
       </c>
       <c r="CW4" t="n">
-        <v>3.436731177419716e-10</v>
+        <v>0.01677706651389599</v>
       </c>
       <c r="CX4" t="n">
-        <v>7.42144817822421e-11</v>
+        <v>0.002708668354898691</v>
       </c>
       <c r="CY4" t="n">
-        <v>6.392300577751087e-11</v>
+        <v>0.001749206800013781</v>
       </c>
       <c r="CZ4" t="n">
-        <v>3.176985757802342e-11</v>
+        <v>0.004465924110263586</v>
       </c>
       <c r="DA4" t="n">
-        <v>6.348588321714033e-10</v>
+        <v>0.00955476425588131</v>
       </c>
       <c r="DB4" t="n">
-        <v>3.065986908801221e-10</v>
+        <v>0.01735125854611397</v>
       </c>
       <c r="DC4" t="n">
-        <v>5.198057539956835e-10</v>
+        <v>0.007607422769069672</v>
       </c>
       <c r="DD4" t="n">
-        <v>1.242355940345163e-10</v>
+        <v>0.006215860135853291</v>
       </c>
       <c r="DE4" t="n">
-        <v>9.197560768559043e-11</v>
+        <v>0.06848280131816864</v>
       </c>
       <c r="DF4" t="n">
-        <v>3.379725388441557e-10</v>
+        <v>0.0217057541012764</v>
       </c>
       <c r="DG4" t="n">
-        <v>3.991702246519679e-10</v>
+        <v>0.06450076401233673</v>
       </c>
       <c r="DH4" t="n">
-        <v>9.761184083245666e-10</v>
+        <v>0.02557209506630898</v>
       </c>
       <c r="DI4" t="n">
-        <v>1.297344565109881e-09</v>
+        <v>0.03501488640904427</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.757238243804693e-10</v>
+        <v>0.005545909516513348</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.555590266657305e-10</v>
+        <v>0.0006077275611460209</v>
       </c>
       <c r="DL4" t="n">
-        <v>1.116352565944112e-09</v>
+        <v>0.0210322979837656</v>
       </c>
       <c r="DM4" t="n">
-        <v>1.325639181759541e-10</v>
+        <v>0.05299485847353935</v>
       </c>
       <c r="DN4" t="n">
-        <v>1.169017521673865e-10</v>
+        <v>0.05454573035240173</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.42806100278392e-10</v>
+        <v>0.02107517793774605</v>
       </c>
       <c r="DP4" t="n">
-        <v>4.897410255111367e-10</v>
+        <v>0.06431325525045395</v>
       </c>
       <c r="DQ4" t="n">
-        <v>1.040436348187512e-10</v>
+        <v>0.02673571556806564</v>
       </c>
       <c r="DR4" t="n">
-        <v>1.7871039370565e-10</v>
+        <v>0.03788717463612556</v>
       </c>
       <c r="DS4" t="n">
-        <v>1.092355927934108e-10</v>
+        <v>0.04407960548996925</v>
       </c>
       <c r="DT4" t="n">
-        <v>1.053039253018362e-10</v>
+        <v>0.04238071665167809</v>
       </c>
       <c r="DU4" t="n">
-        <v>1.17497594986915e-10</v>
+        <v>0.0196774173527956</v>
       </c>
       <c r="DV4" t="n">
-        <v>5.263236721453346e-11</v>
+        <v>0.0239527951925993</v>
       </c>
       <c r="DW4" t="n">
-        <v>2.519693065305972e-10</v>
+        <v>0.01583764515817165</v>
       </c>
       <c r="DX4" t="n">
-        <v>2.69601507785211e-10</v>
+        <v>0.03914718329906464</v>
       </c>
       <c r="DY4" t="n">
-        <v>5.65640811966972e-10</v>
+        <v>0.01351712737232447</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.306025453397865e-10</v>
+        <v>0.03356733918190002</v>
       </c>
       <c r="EA4" t="n">
-        <v>4.822212074095944e-10</v>
+        <v>0.09358281642198563</v>
       </c>
       <c r="EB4" t="n">
-        <v>3.102068046878514e-10</v>
+        <v>0.02361021004617214</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.609495952654584e-10</v>
+        <v>0.01259415503591299</v>
       </c>
       <c r="ED4" t="n">
-        <v>5.46957035219009e-10</v>
+        <v>0.006435748189687729</v>
       </c>
       <c r="EE4" t="n">
-        <v>2.602092846748505e-11</v>
+        <v>0.003546948079019785</v>
       </c>
       <c r="EF4" t="n">
-        <v>1.48004958983039e-12</v>
+        <v>0.06084305047988892</v>
       </c>
       <c r="EG4" t="n">
-        <v>3.386117775061592e-10</v>
+        <v>0.03028007224202156</v>
       </c>
       <c r="EH4" t="n">
-        <v>1.004734490051007e-10</v>
+        <v>0.02586130425333977</v>
       </c>
       <c r="EI4" t="n">
-        <v>4.047452373256988e-10</v>
+        <v>0.02062509953975677</v>
       </c>
       <c r="EJ4" t="n">
-        <v>5.089787480372365e-10</v>
+        <v>0.006326773669570684</v>
       </c>
       <c r="EK4" t="n">
-        <v>3.764333844635814e-10</v>
+        <v>0.01043055858463049</v>
       </c>
       <c r="EL4" t="n">
-        <v>1.043280739576602e-11</v>
+        <v>0.01186045166105032</v>
       </c>
       <c r="EM4" t="n">
-        <v>7.109670491223241e-11</v>
+        <v>0.001542335376143456</v>
       </c>
       <c r="EN4" t="n">
-        <v>2.449824787476018e-10</v>
+        <v>0.01319095864892006</v>
       </c>
       <c r="EO4" t="n">
-        <v>2.537448862138802e-10</v>
+        <v>0.06116669625043869</v>
       </c>
       <c r="EP4" t="n">
-        <v>2.493591097496584e-11</v>
+        <v>0.03034764528274536</v>
       </c>
       <c r="EQ4" t="n">
-        <v>6.251581197158629e-11</v>
+        <v>0.001699113636277616</v>
       </c>
       <c r="ER4" t="n">
-        <v>3.424126954199025e-11</v>
+        <v>0.05580296367406845</v>
       </c>
       <c r="ES4" t="n">
-        <v>1.025960011391547e-10</v>
+        <v>0.009938531555235386</v>
       </c>
       <c r="ET4" t="n">
-        <v>6.189398993328155e-10</v>
+        <v>0.007987644523382187</v>
       </c>
       <c r="EU4" t="n">
-        <v>3.167279494231678e-10</v>
+        <v>0.002897240687161684</v>
       </c>
       <c r="EV4" t="n">
-        <v>6.85880241491077e-10</v>
+        <v>0.007275452371686697</v>
       </c>
       <c r="EW4" t="n">
-        <v>1.805167126889273e-11</v>
+        <v>0.1011863872408867</v>
       </c>
       <c r="EX4" t="n">
-        <v>1.394673682098002e-10</v>
+        <v>0.08180385828018188</v>
       </c>
       <c r="EY4" t="n">
-        <v>2.914511965101951e-10</v>
+        <v>0.016227712854743</v>
       </c>
       <c r="EZ4" t="n">
-        <v>2.17837942129151e-10</v>
+        <v>0.01082074642181396</v>
       </c>
       <c r="FA4" t="n">
-        <v>2.253851619227198e-11</v>
+        <v>0.001172433607280254</v>
       </c>
       <c r="FB4" t="n">
-        <v>4.044010265547016e-11</v>
+        <v>0.02387498691678047</v>
       </c>
       <c r="FC4" t="n">
-        <v>5.32211386072845e-10</v>
+        <v>0.008603249676525593</v>
       </c>
       <c r="FD4" t="n">
-        <v>1.439533214853128e-10</v>
+        <v>0.0144531698897481</v>
       </c>
       <c r="FE4" t="n">
-        <v>5.303200656392448e-10</v>
+        <v>0.002886067843064666</v>
       </c>
       <c r="FF4" t="n">
-        <v>1.76519535100006e-10</v>
+        <v>0.008171100169420242</v>
       </c>
       <c r="FG4" t="n">
-        <v>1.373707814167346e-10</v>
+        <v>0.04012486711144447</v>
       </c>
       <c r="FH4" t="n">
-        <v>6.723958057008872e-10</v>
+        <v>0.02259591966867447</v>
       </c>
       <c r="FI4" t="n">
-        <v>3.661690395340145e-10</v>
+        <v>0.005444818176329136</v>
       </c>
       <c r="FJ4" t="n">
-        <v>5.256994839442086e-10</v>
+        <v>0.004336957354098558</v>
       </c>
       <c r="FK4" t="n">
-        <v>4.336351833167384e-10</v>
+        <v>0.03166315704584122</v>
       </c>
       <c r="FL4" t="n">
-        <v>6.725245915717437e-10</v>
+        <v>0.03465060889720917</v>
       </c>
       <c r="FM4" t="n">
-        <v>6.843309946491516e-11</v>
+        <v>0.01895921118557453</v>
       </c>
       <c r="FN4" t="n">
-        <v>4.749733939490852e-11</v>
+        <v>0.0121613061055541</v>
       </c>
       <c r="FO4" t="n">
-        <v>2.211001243201949e-10</v>
+        <v>0.05906625837087631</v>
       </c>
       <c r="FP4" t="n">
-        <v>2.838738688559772e-10</v>
+        <v>0.007522337138652802</v>
       </c>
       <c r="FQ4" t="n">
-        <v>8.694582276369545e-10</v>
+        <v>0.06399883329868317</v>
       </c>
       <c r="FR4" t="n">
-        <v>4.756381399850795e-11</v>
+        <v>0.03560344502329826</v>
       </c>
       <c r="FS4" t="n">
-        <v>7.435810300826518e-10</v>
+        <v>0.04905454069375992</v>
       </c>
       <c r="FT4" t="n">
-        <v>5.95304250339268e-10</v>
+        <v>0.1286792159080505</v>
       </c>
       <c r="FU4" t="n">
-        <v>6.785630390915287e-10</v>
+        <v>0.06464114785194397</v>
       </c>
       <c r="FV4" t="n">
-        <v>2.104073859587885e-12</v>
+        <v>0.02179823443293571</v>
       </c>
       <c r="FW4" t="n">
-        <v>1.263270599238808e-10</v>
+        <v>0.07651352882385254</v>
       </c>
       <c r="FX4" t="n">
-        <v>3.469957654544942e-11</v>
+        <v>0.05898229032754898</v>
       </c>
       <c r="FY4" t="n">
-        <v>2.012385258431948e-10</v>
+        <v>0.05144694074988365</v>
       </c>
       <c r="FZ4" t="n">
-        <v>8.075930202355863e-11</v>
+        <v>0.02409815043210983</v>
       </c>
       <c r="GA4" t="n">
-        <v>1.067483323957674e-10</v>
+        <v>0.02725999429821968</v>
       </c>
       <c r="GB4" t="n">
-        <v>8.056960654201362e-10</v>
+        <v>0.007340575102716684</v>
       </c>
       <c r="GC4" t="n">
-        <v>1.482414191400494e-09</v>
+        <v>0.002957845106720924</v>
       </c>
       <c r="GD4" t="n">
-        <v>3.118467151175253e-10</v>
+        <v>0.01314084418118</v>
       </c>
       <c r="GE4" t="n">
-        <v>5.884536746769697e-10</v>
+        <v>0.03094490244984627</v>
       </c>
       <c r="GF4" t="n">
-        <v>1.693800655289124e-11</v>
+        <v>0.0267803780734539</v>
       </c>
       <c r="GG4" t="n">
-        <v>9.272006079585893e-11</v>
+        <v>0.05235391482710838</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.007017202209681273</v>
+        <v>0.0953260064125061</v>
       </c>
       <c r="B5" t="n">
-        <v>0.004643565509468317</v>
+        <v>0.03055910021066666</v>
       </c>
       <c r="C5" t="n">
-        <v>0.005960437469184399</v>
+        <v>0.3845903277397156</v>
       </c>
       <c r="D5" t="n">
-        <v>0.009464064612984657</v>
+        <v>0.4489254355430603</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001786021632142365</v>
+        <v>0.1947254985570908</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002752989763393998</v>
+        <v>0.1138176023960114</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00118604744784534</v>
+        <v>0.1036918163299561</v>
       </c>
       <c r="H5" t="n">
-        <v>0.004970703274011612</v>
+        <v>0.0230446495115757</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0003961466136388481</v>
+        <v>0.02014876902103424</v>
       </c>
       <c r="J5" t="n">
-        <v>0.009965959936380386</v>
+        <v>0.04049716889858246</v>
       </c>
       <c r="K5" t="n">
-        <v>0.005275469273328781</v>
+        <v>0.04131531715393066</v>
       </c>
       <c r="L5" t="n">
-        <v>0.005291994195431471</v>
+        <v>0.3510655164718628</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01041486021131277</v>
+        <v>0.4535156190395355</v>
       </c>
       <c r="N5" t="n">
-        <v>0.004782856442034245</v>
+        <v>0.3421047627925873</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0006721231620758772</v>
+        <v>0.1642847955226898</v>
       </c>
       <c r="P5" t="n">
-        <v>0.00314897857606411</v>
+        <v>0.04896243661642075</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.004919955972582102</v>
+        <v>0.1381331086158752</v>
       </c>
       <c r="R5" t="n">
-        <v>0.00353109952993691</v>
+        <v>0.06151757761836052</v>
       </c>
       <c r="S5" t="n">
-        <v>0.003002374432981014</v>
+        <v>0.02788177132606506</v>
       </c>
       <c r="T5" t="n">
-        <v>0.001242933445610106</v>
+        <v>0.1008341386914253</v>
       </c>
       <c r="U5" t="n">
-        <v>0.000173851105500944</v>
+        <v>0.0582982711493969</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0006114249699749053</v>
+        <v>0.07452850043773651</v>
       </c>
       <c r="W5" t="n">
-        <v>0.005444944836199284</v>
+        <v>0.01753604784607887</v>
       </c>
       <c r="X5" t="n">
-        <v>0.001261124154552817</v>
+        <v>0.236345037817955</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.024504106491804e-05</v>
+        <v>0.04592126980423927</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.007420092355459929</v>
+        <v>0.03412273153662682</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0002103208680637181</v>
+        <v>0.01893512532114983</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0003547545638866723</v>
+        <v>0.01701671257615089</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.004127656109631062</v>
+        <v>0.02392849326133728</v>
       </c>
       <c r="AD5" t="n">
-        <v>5.096948007121682e-05</v>
+        <v>0.1554429531097412</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.0009521548636257648</v>
+        <v>0.1484968066215515</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.001331293606199324</v>
+        <v>0.1434549391269684</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.001670670229941607</v>
+        <v>0.179908275604248</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.0006640345091000199</v>
+        <v>0.1095560416579247</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.0007692116778343916</v>
+        <v>0.1484623700380325</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.001289145671762526</v>
+        <v>0.1304661929607391</v>
       </c>
       <c r="AK5" t="n">
-        <v>6.237684283405542e-05</v>
+        <v>0.07194130122661591</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.001897015608847141</v>
+        <v>0.06369476765394211</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.000662017147988081</v>
+        <v>0.05866623297333717</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.0007152603357098997</v>
+        <v>0.1466690897941589</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.0001682424044702202</v>
+        <v>0.001023493707180023</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.0009852554649114609</v>
+        <v>0.04342830181121826</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.001892388565465808</v>
+        <v>0.04547256231307983</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.001329935737885535</v>
+        <v>0.0189791563898325</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.0003078390436712652</v>
+        <v>0.001965523697435856</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.000881345069501549</v>
+        <v>0.1181089282035828</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.001047380967065692</v>
+        <v>0.06765113025903702</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.00335492379963398</v>
+        <v>0.3803623914718628</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.006952943280339241</v>
+        <v>0.319225400686264</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.001111259334720671</v>
+        <v>0.1899404525756836</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.002985357539728284</v>
+        <v>0.1228078603744507</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.0003643601667135954</v>
+        <v>0.1257162988185883</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.004287137649953365</v>
+        <v>0.07187284529209137</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.00248825061134994</v>
+        <v>0.02718816325068474</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.009350121952593327</v>
+        <v>0.1638958603143692</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.002647881861776114</v>
+        <v>0.03560330718755722</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.207653622259386e-05</v>
+        <v>0.03186926618218422</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.002005151938647032</v>
+        <v>0.1027144491672516</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.006813309155404568</v>
+        <v>0.2823699116706848</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.00161592336371541</v>
+        <v>0.04443954676389694</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.006824922282248735</v>
+        <v>0.05558622255921364</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.01068065967410803</v>
+        <v>0.08344805240631104</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.000198554655071348</v>
+        <v>0.1537901610136032</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.001547725172713399</v>
+        <v>0.03524769842624664</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.003058376256376505</v>
+        <v>0.01684538275003433</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.002654772019013762</v>
+        <v>0.0358426496386528</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.002653369214385748</v>
+        <v>0.05254737660288811</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.004447576124221087</v>
+        <v>0.03990568965673447</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.001735323923639953</v>
+        <v>0.08555769175291061</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.002156496979296207</v>
+        <v>0.05502057075500488</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.000924675608985126</v>
+        <v>0.006803065538406372</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.001686289673671126</v>
+        <v>0.007924286648631096</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.001079487847164273</v>
+        <v>0.008343209512531757</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.001843697624281049</v>
+        <v>0.09184262156486511</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.002035047858953476</v>
+        <v>0.1669960469007492</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.003532007103785872</v>
+        <v>0.1613342612981796</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.001619397080503404</v>
+        <v>0.09669679403305054</v>
       </c>
       <c r="BZ5" t="n">
-        <v>3.10542163788341e-05</v>
+        <v>0.08378393203020096</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.002089143265038729</v>
+        <v>0.100898876786232</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.007125192321836948</v>
+        <v>0.005887579172849655</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.00330922263674438</v>
+        <v>0.04703124240040779</v>
       </c>
       <c r="CD5" t="n">
-        <v>0.001538124633952975</v>
+        <v>0.03315495699644089</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.001660119858570397</v>
+        <v>0.04416845738887787</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.001697273692116141</v>
+        <v>0.09017778187990189</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.002099470468237996</v>
+        <v>0.04959961399435997</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.001294759567826986</v>
+        <v>0.06800605356693268</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.001128364820033312</v>
+        <v>0.01751141622662544</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.00119343469850719</v>
+        <v>0.03333011269569397</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.001599315321072936</v>
+        <v>0.01448455080389977</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.001526336651295424</v>
+        <v>0.01477771904319525</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.004000884480774403</v>
+        <v>0.07933260500431061</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.000829891418106854</v>
+        <v>0.1012618392705917</v>
       </c>
       <c r="CO5" t="n">
-        <v>3.393335646251217e-05</v>
+        <v>0.01871587708592415</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.00104085577186197</v>
+        <v>0.1980004608631134</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.001973084174096584</v>
+        <v>0.5133448839187622</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.0007972466410137713</v>
+        <v>0.03169160336256027</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.0009725608397275209</v>
+        <v>0.07660543173551559</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.001108300173655152</v>
+        <v>0.03550408780574799</v>
       </c>
       <c r="CU5" t="n">
-        <v>0.001801659120246768</v>
+        <v>0.0901625007390976</v>
       </c>
       <c r="CV5" t="n">
-        <v>0.001534803071990609</v>
+        <v>0.04867691546678543</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.001070146914571524</v>
+        <v>0.007367662154138088</v>
       </c>
       <c r="CX5" t="n">
-        <v>0.000615266733802855</v>
+        <v>0.09597194194793701</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.001359834335744381</v>
+        <v>0.06174658611416817</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.0008969397749751806</v>
+        <v>0.07522156834602356</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.0006086549255996943</v>
+        <v>0.03799805045127869</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.0005475307116284966</v>
+        <v>0.03419941663742065</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.001429036259651184</v>
+        <v>0.0329393595457077</v>
       </c>
       <c r="DD5" t="n">
-        <v>0.001972244819626212</v>
+        <v>0.01477081142365932</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.0004245999734848738</v>
+        <v>0.01139773987233639</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.007998984307050705</v>
+        <v>0.1263943314552307</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.002318660262972116</v>
+        <v>0.3009776771068573</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.0006335297366604209</v>
+        <v>0.01802705973386765</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.0007923556258901954</v>
+        <v>0.237314760684967</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.007362386677414179</v>
+        <v>0.05957774445414543</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.007944012060761452</v>
+        <v>0.02469367161393166</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.0006470829248428345</v>
+        <v>0.1468483954668045</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.002756432164460421</v>
+        <v>0.2588421702384949</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.001510910573415458</v>
+        <v>0.03972797468304634</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.001358756911940873</v>
+        <v>0.06958760321140289</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.002328976755961776</v>
+        <v>0.02030684053897858</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.0007875260780565441</v>
+        <v>0.03385154902935028</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.003443286754190922</v>
+        <v>0.03093862161040306</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.0003588871331885457</v>
+        <v>0.02964198589324951</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.00170404464006424</v>
+        <v>0.07726338505744934</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.001469631213694811</v>
+        <v>0.01742970384657383</v>
       </c>
       <c r="DV5" t="n">
-        <v>0.001300229574553668</v>
+        <v>0.1268197298049927</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.0003351030463818461</v>
+        <v>0.1055860370397568</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.0007635551737621427</v>
+        <v>0.002784946002066135</v>
       </c>
       <c r="DY5" t="n">
-        <v>0.001410662545822561</v>
+        <v>0.05782420188188553</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.0009561257902532816</v>
+        <v>0.121637649834156</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.0009499298175796866</v>
+        <v>0.06478418409824371</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.004882125649601221</v>
+        <v>0.1224714666604996</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.0005627151113003492</v>
+        <v>0.07908330112695694</v>
       </c>
       <c r="ED5" t="n">
-        <v>0.002960431389510632</v>
+        <v>0.104541689157486</v>
       </c>
       <c r="EE5" t="n">
-        <v>0.002376349875703454</v>
+        <v>0.03296226263046265</v>
       </c>
       <c r="EF5" t="n">
-        <v>0.001537866657599807</v>
+        <v>0.03076908551156521</v>
       </c>
       <c r="EG5" t="n">
-        <v>1.1468306183815e-05</v>
+        <v>0.01582247018814087</v>
       </c>
       <c r="EH5" t="n">
-        <v>0.001982709625735879</v>
+        <v>0.06373754143714905</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.002732692752033472</v>
+        <v>0.05562570318579674</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.0009349856991320848</v>
+        <v>0.1493358910083771</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.0007097253110259771</v>
+        <v>0.005532186478376389</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.001135532394982874</v>
+        <v>0.02844393253326416</v>
       </c>
       <c r="EM5" t="n">
-        <v>0.001735506462864578</v>
+        <v>0.04396206885576248</v>
       </c>
       <c r="EN5" t="n">
-        <v>0.002485756063833833</v>
+        <v>0.01544839236885309</v>
       </c>
       <c r="EO5" t="n">
-        <v>0.001571684377267957</v>
+        <v>0.007055551744997501</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.0001608802704140544</v>
+        <v>0.1167105212807655</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0.002039601560682058</v>
+        <v>0.02035949379205704</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.001335195498540998</v>
+        <v>0.1144554018974304</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.0006347779417410493</v>
+        <v>0.08532722294330597</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.0009163632057607174</v>
+        <v>0.1232553347945213</v>
       </c>
       <c r="EU5" t="n">
-        <v>0.001054793247021735</v>
+        <v>0.09081988036632538</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.005522220861166716</v>
+        <v>0.09516340494155884</v>
       </c>
       <c r="EW5" t="n">
-        <v>0.001750537659972906</v>
+        <v>0.04135709628462791</v>
       </c>
       <c r="EX5" t="n">
-        <v>0.00128246087115258</v>
+        <v>0.03079167567193508</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.001365498756058514</v>
+        <v>0.04075853526592255</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0.001293891109526157</v>
+        <v>0.09733109921216965</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.001594095374457538</v>
+        <v>0.04993904381990433</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.0004668007022701204</v>
+        <v>0.05360464006662369</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.001051312778145075</v>
+        <v>0.05420947074890137</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.0007683004951104522</v>
+        <v>0.03500789031386375</v>
       </c>
       <c r="FE5" t="n">
-        <v>0.001071042264811695</v>
+        <v>0.06290537118911743</v>
       </c>
       <c r="FF5" t="n">
-        <v>0.002209420781582594</v>
+        <v>0.02020472846925259</v>
       </c>
       <c r="FG5" t="n">
-        <v>0.0002201231545768678</v>
+        <v>0.01837882585823536</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.001242644502781332</v>
+        <v>0.003637433983385563</v>
       </c>
       <c r="FI5" t="n">
-        <v>0.0005128083867020905</v>
+        <v>0.1866336911916733</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.00330860004760325</v>
+        <v>0.03456911072134972</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.001073022023774683</v>
+        <v>0.1521424651145935</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.002070387126877904</v>
+        <v>0.09321913123130798</v>
       </c>
       <c r="FM5" t="n">
-        <v>7.789151277393103e-05</v>
+        <v>0.02977058477699757</v>
       </c>
       <c r="FN5" t="n">
-        <v>0.0005577460979111493</v>
+        <v>0.1329584568738937</v>
       </c>
       <c r="FO5" t="n">
-        <v>0.00292996340431273</v>
+        <v>0.09461089968681335</v>
       </c>
       <c r="FP5" t="n">
-        <v>0.003609437728300691</v>
+        <v>0.2230332493782043</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.00357956369407475</v>
+        <v>0.02944919839501381</v>
       </c>
       <c r="FR5" t="n">
-        <v>0.006846895441412926</v>
+        <v>0.04523249715566635</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.002889668801799417</v>
+        <v>0.04387388005852699</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.001080782734788954</v>
+        <v>0.1057850867509842</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.00400603050366044</v>
+        <v>0.03150782361626625</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.0006079266313463449</v>
+        <v>0.02614887617528439</v>
       </c>
       <c r="FW5" t="n">
-        <v>0.0004042325308546424</v>
+        <v>0.1734203994274139</v>
       </c>
       <c r="FX5" t="n">
-        <v>0.002785933902487159</v>
+        <v>0.01833516359329224</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.001254018978215754</v>
+        <v>0.04082923382520676</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.001472094561904669</v>
+        <v>0.1283646821975708</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.002248014090582728</v>
+        <v>0.1205585598945618</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.002798480447381735</v>
+        <v>0.1007782965898514</v>
       </c>
       <c r="GC5" t="n">
-        <v>0.004306574817746878</v>
+        <v>0.199232205748558</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.003878588322550058</v>
+        <v>0.08596400171518326</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.0005665551871061325</v>
+        <v>0.1286564469337463</v>
       </c>
       <c r="GF5" t="n">
-        <v>0.002220821101218462</v>
+        <v>0.05366833135485649</v>
       </c>
       <c r="GG5" t="n">
-        <v>0.001144552370533347</v>
+        <v>0.01480697095394135</v>
       </c>
     </row>
     <row r="6">
@@ -3844,5123 +3844,5123 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.000425709062255919</v>
+        <v>1.662057002249639e-05</v>
       </c>
       <c r="B7" t="n">
-        <v>0.02311930246651173</v>
+        <v>3.822470898739994e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>0.00305701675824821</v>
+        <v>2.396293893980328e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01046326849609613</v>
+        <v>1.230092493642587e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00837523490190506</v>
+        <v>5.69838675801293e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01048056222498417</v>
+        <v>2.526865682739299e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0003562213387340307</v>
+        <v>1.657348548178561e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001115900347940624</v>
+        <v>2.485708682797849e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.004456011578440666</v>
+        <v>2.10835878533544e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002207104116678238</v>
+        <v>1.547570718685165e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01777881570160389</v>
+        <v>5.15845968038775e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0002430154563626274</v>
+        <v>5.616988346446306e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01040700823068619</v>
+        <v>1.756758138071746e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>0.005684674717485905</v>
+        <v>1.568763400427997e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01193190272897482</v>
+        <v>2.877257429645397e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0007371457759290934</v>
+        <v>5.80147752771154e-06</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.003212896874174476</v>
+        <v>6.507311809400562e-06</v>
       </c>
       <c r="R7" t="n">
-        <v>0.004021858796477318</v>
+        <v>3.266011481173337e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0004883871297352016</v>
+        <v>1.402622615387372e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>0.003428558818995953</v>
+        <v>8.711348527867813e-06</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0005171963712200522</v>
+        <v>8.971226748144545e-07</v>
       </c>
       <c r="V7" t="n">
-        <v>0.004051428288221359</v>
+        <v>1.469890685257269e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001173527212813497</v>
+        <v>3.561377070582239e-06</v>
       </c>
       <c r="X7" t="n">
-        <v>0.005523903295397758</v>
+        <v>4.080341113876784e-06</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0005223396001383662</v>
+        <v>1.828481572374585e-06</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.001014829729683697</v>
+        <v>5.337307811714709e-06</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.13376445369795e-05</v>
+        <v>2.201455345129943e-06</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.001723163877613842</v>
+        <v>4.244491719873622e-06</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.003683403367176652</v>
+        <v>2.011299147852696e-05</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.0005161953158676624</v>
+        <v>7.028513209661469e-06</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.0007310775108635426</v>
+        <v>1.52720767800929e-05</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.0007816556608304381</v>
+        <v>2.471963307471015e-05</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.00284280558116734</v>
+        <v>9.53337803366594e-06</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.0007042952347546816</v>
+        <v>1.78489540303417e-06</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.001321463380008936</v>
+        <v>2.77124436252052e-05</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.002562319627031684</v>
+        <v>5.277567652228754e-06</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.003978862427175045</v>
+        <v>1.608005050002248e-06</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.002836941741406918</v>
+        <v>7.610078228026396e-06</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.0006295851781032979</v>
+        <v>6.366760771925328e-06</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.001015501096844673</v>
+        <v>5.067695383331738e-06</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.0002096057869493961</v>
+        <v>3.734883193828864e-07</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.001061021932400763</v>
+        <v>6.885503808007343e-06</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.001290206098929048</v>
+        <v>5.664631771651329e-06</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.001764710643328726</v>
+        <v>1.358945792162558e-05</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.002539047505706549</v>
+        <v>1.670630695116415e-06</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.001541912788525224</v>
+        <v>9.329252861789428e-06</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.01734168455004692</v>
+        <v>4.551538222585805e-05</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.001116586616262794</v>
+        <v>5.974307896394748e-06</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.003630213905125856</v>
+        <v>5.747159320890205e-06</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.004686928819864988</v>
+        <v>1.686734685790725e-05</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.002825946314260364</v>
+        <v>2.771257277345285e-05</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.004741834010928869</v>
+        <v>5.555227289733011e-06</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.003154823556542397</v>
+        <v>2.195355818912503e-06</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.001651462051086128</v>
+        <v>1.139393680205103e-05</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.001184758730232716</v>
+        <v>3.998264219262637e-06</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.007206946145743132</v>
+        <v>2.496549495845102e-05</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.00545937567949295</v>
+        <v>1.47287914842309e-06</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.00143263244535774</v>
+        <v>1.361118847853504e-06</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.007167747709900141</v>
+        <v>9.793204753805185e-07</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.006094722542911768</v>
+        <v>4.441487817530287e-06</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.002628404414281249</v>
+        <v>6.996565844019642e-06</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.005489260423928499</v>
+        <v>2.041324842139147e-05</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.004418710246682167</v>
+        <v>4.120235644222703e-06</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.003163854125887156</v>
+        <v>5.230333499639528e-06</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.00528981676325202</v>
+        <v>1.254109156434424e-05</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.002162656746804714</v>
+        <v>2.699445303733228e-06</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.001400699373334646</v>
+        <v>5.184779183764476e-08</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.002275219652801752</v>
+        <v>7.324064426939003e-06</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.00208718073554337</v>
+        <v>1.088137105398346e-05</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.00167966983281076</v>
+        <v>2.312176184204873e-05</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.0007264367304742336</v>
+        <v>8.675012395542581e-06</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.0006601124769076705</v>
+        <v>1.068989058694569e-05</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.001493933494202793</v>
+        <v>2.404223778285086e-06</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.009083348326385021</v>
+        <v>3.203054438927211e-05</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.003628667211160064</v>
+        <v>5.301785222400213e-06</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.003432344645261765</v>
+        <v>1.767622961779125e-05</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.0001684977032709867</v>
+        <v>6.725884304614738e-06</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.001010144245810807</v>
+        <v>9.421260074304882e-06</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.0007100851507857442</v>
+        <v>5.283041446091374e-06</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.0001191717601614073</v>
+        <v>1.341689130640589e-05</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.001003329642117023</v>
+        <v>1.77021343006345e-06</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.0006509395898319781</v>
+        <v>1.468577693231055e-06</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.003191593801602721</v>
+        <v>1.221631282533053e-05</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.001378824352286756</v>
+        <v>6.826375056334655e-07</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.000544206122867763</v>
+        <v>6.340268555504736e-06</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.0005602139281108975</v>
+        <v>1.976640305656474e-06</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.001751881674863398</v>
+        <v>4.485726094571874e-06</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.001304734614677727</v>
+        <v>4.874558726442046e-06</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.0005718161119148135</v>
+        <v>5.333967237675097e-06</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.0005046662408858538</v>
+        <v>2.005395799642429e-06</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.004392034839838743</v>
+        <v>8.507930033374578e-06</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.004028898663818836</v>
+        <v>3.255968294979539e-06</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.0007734731771051884</v>
+        <v>1.452754713682225e-05</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.004452591296285391</v>
+        <v>4.592724053509301e-06</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.001666702446527779</v>
+        <v>1.100951976695796e-05</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.00142549688462168</v>
+        <v>2.417166342638666e-07</v>
       </c>
       <c r="CS7" t="n">
-        <v>0.003374968422576785</v>
+        <v>1.035475452226819e-05</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.003848168067634106</v>
+        <v>3.075454515055753e-06</v>
       </c>
       <c r="CU7" t="n">
-        <v>0.0003337199450470507</v>
+        <v>2.217320070485584e-05</v>
       </c>
       <c r="CV7" t="n">
-        <v>0.0001459949708078057</v>
+        <v>1.338635911452002e-06</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.002339007100090384</v>
+        <v>9.723209586809389e-06</v>
       </c>
       <c r="CX7" t="n">
-        <v>0.002056501572951674</v>
+        <v>1.753375613589014e-07</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.001492807175964117</v>
+        <v>3.601639491535025e-06</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.586889240774326e-05</v>
+        <v>1.753216793076717e-06</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.002188371960073709</v>
+        <v>6.50264246360166e-06</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.0008156119147315621</v>
+        <v>4.021688653210731e-07</v>
       </c>
       <c r="DC7" t="n">
-        <v>0.000984019716270268</v>
+        <v>4.614353201759513e-06</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.97923616017215e-05</v>
+        <v>6.662006626356742e-07</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.001767956651747227</v>
+        <v>1.355782751488732e-05</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.002996093360707164</v>
+        <v>2.80491963167151e-06</v>
       </c>
       <c r="DG7" t="n">
-        <v>0.002154656918719411</v>
+        <v>8.931389857025351e-06</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.004482229240238667</v>
+        <v>4.471081410883926e-06</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.004359109792858362</v>
+        <v>1.570460517541505e-05</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.00295685138553381</v>
+        <v>2.431041593808914e-06</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.004467773251235485</v>
+        <v>4.020856522402028e-06</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.0003457576676737517</v>
+        <v>1.374698058498325e-06</v>
       </c>
       <c r="DM7" t="n">
-        <v>0.00699915736913681</v>
+        <v>7.227082733152201e-06</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.0005455966456793249</v>
+        <v>9.121999937633518e-06</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.001092226710170507</v>
+        <v>2.296620550623629e-06</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.001497698831371963</v>
+        <v>6.524826858367305e-06</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.001918764435686171</v>
+        <v>1.3982010386826e-05</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.001656416454352438</v>
+        <v>1.98529482986487e-06</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.001757393358275294</v>
+        <v>2.197187131969258e-05</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.002678935881704092</v>
+        <v>4.040599833388114e-06</v>
       </c>
       <c r="DU7" t="n">
-        <v>0.00114149134606123</v>
+        <v>4.7041194193298e-06</v>
       </c>
       <c r="DV7" t="n">
-        <v>0.001209990470670164</v>
+        <v>1.266104845853988e-05</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.0006049320800229907</v>
+        <v>7.786698915879242e-06</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.0003516724682413042</v>
+        <v>1.07617652247427e-05</v>
       </c>
       <c r="DY7" t="n">
-        <v>0.003114363877102733</v>
+        <v>6.975988071644679e-07</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.003127333242446184</v>
+        <v>5.46080036656349e-06</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.002140055410563946</v>
+        <v>8.107917892630212e-06</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.001146414084360003</v>
+        <v>1.890371095214505e-05</v>
       </c>
       <c r="EC7" t="n">
-        <v>0.0001292098022531718</v>
+        <v>4.998739314032719e-06</v>
       </c>
       <c r="ED7" t="n">
-        <v>0.001402454450726509</v>
+        <v>5.397700988396537e-07</v>
       </c>
       <c r="EE7" t="n">
-        <v>0.0002762923832051456</v>
+        <v>7.539556463598274e-06</v>
       </c>
       <c r="EF7" t="n">
-        <v>0.0002278203901369125</v>
+        <v>4.093759343959391e-06</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.001814103219658136</v>
+        <v>3.386036951269489e-06</v>
       </c>
       <c r="EH7" t="n">
-        <v>0.0002009073214139789</v>
+        <v>5.494689503393602e-06</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.0005722690839320421</v>
+        <v>2.718912810451002e-07</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.0001838918251451105</v>
+        <v>6.800862593081547e-06</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.001914996188133955</v>
+        <v>1.318762770097237e-07</v>
       </c>
       <c r="EL7" t="n">
-        <v>0.001891964231617749</v>
+        <v>1.096200549000059e-06</v>
       </c>
       <c r="EM7" t="n">
-        <v>0.0005564431776292622</v>
+        <v>7.388553513010265e-06</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.0007919141789898276</v>
+        <v>1.691983015916776e-07</v>
       </c>
       <c r="EO7" t="n">
-        <v>0.0006845209281891584</v>
+        <v>3.505592076180619e-06</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.0002046270383289084</v>
+        <v>4.613618784787832e-06</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0.002223895397037268</v>
+        <v>5.041664735472295e-06</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.0003070148814003915</v>
+        <v>2.651380782481283e-06</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.001023854594677687</v>
+        <v>1.06535762824933e-05</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.003258830634877086</v>
+        <v>1.567528124724049e-05</v>
       </c>
       <c r="EU7" t="n">
-        <v>0.001406569965183735</v>
+        <v>4.216150045976974e-06</v>
       </c>
       <c r="EV7" t="n">
-        <v>0.006128577049821615</v>
+        <v>1.96235919247556e-06</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.002115190029144287</v>
+        <v>2.917337042163126e-06</v>
       </c>
       <c r="EX7" t="n">
-        <v>0.0001072471204679459</v>
+        <v>1.026443214868777e-06</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.002143800025805831</v>
+        <v>1.422230889147613e-05</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0.001049507409334183</v>
+        <v>2.14641204365762e-07</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.0009051972301676869</v>
+        <v>3.772810032387497e-06</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.000530210614670068</v>
+        <v>1.391060891364759e-06</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.002215641085058451</v>
+        <v>3.491262077659485e-06</v>
       </c>
       <c r="FD7" t="n">
-        <v>0.001354312524199486</v>
+        <v>4.733790319733089e-06</v>
       </c>
       <c r="FE7" t="n">
-        <v>0.0004691434442065656</v>
+        <v>2.84472025668947e-06</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.000680109893437475</v>
+        <v>2.747105554590235e-06</v>
       </c>
       <c r="FG7" t="n">
-        <v>0.0006354490760713816</v>
+        <v>1.729014002194162e-06</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.002278918866068125</v>
+        <v>9.697219866211526e-06</v>
       </c>
       <c r="FI7" t="n">
-        <v>0.001783450949005783</v>
+        <v>9.931181921274401e-06</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.004861802794039249</v>
+        <v>9.595840310794301e-06</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.00117299915291369</v>
+        <v>1.033856733556604e-06</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.001493341522291303</v>
+        <v>3.645012384367874e-06</v>
       </c>
       <c r="FM7" t="n">
-        <v>0.001834430615417659</v>
+        <v>4.39956738773617e-06</v>
       </c>
       <c r="FN7" t="n">
-        <v>0.002374907024204731</v>
+        <v>8.627854185760953e-06</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.0003227281267754734</v>
+        <v>1.351769697066629e-05</v>
       </c>
       <c r="FP7" t="n">
-        <v>0.0009975747670978308</v>
+        <v>1.615763176232576e-05</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.007825762964785099</v>
+        <v>2.184671939176042e-05</v>
       </c>
       <c r="FR7" t="n">
-        <v>0.001277722301892936</v>
+        <v>5.878905540157575e-06</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.003412626683712006</v>
+        <v>1.427168081136188e-05</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.003420207882300019</v>
+        <v>1.686203177087009e-08</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.003389046993106604</v>
+        <v>4.989641638530884e-06</v>
       </c>
       <c r="FV7" t="n">
-        <v>0.00686296634376049</v>
+        <v>5.722064997826237e-06</v>
       </c>
       <c r="FW7" t="n">
-        <v>0.001987222582101822</v>
+        <v>1.654253719607368e-05</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.002393980976194143</v>
+        <v>2.167109414585866e-05</v>
       </c>
       <c r="FY7" t="n">
-        <v>0.001808266621083021</v>
+        <v>2.974749577333569e-06</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.0009315703646279871</v>
+        <v>1.296329628530657e-06</v>
       </c>
       <c r="GA7" t="n">
-        <v>0.001823892933316529</v>
+        <v>5.419719855126459e-06</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.001039663911797106</v>
+        <v>1.848043893915019e-06</v>
       </c>
       <c r="GC7" t="n">
-        <v>7.983815157786012e-05</v>
+        <v>1.691628494882025e-05</v>
       </c>
       <c r="GD7" t="n">
-        <v>0.002530116820707917</v>
+        <v>1.099413202609867e-05</v>
       </c>
       <c r="GE7" t="n">
-        <v>0.006586046423763037</v>
+        <v>3.266978410465526e-06</v>
       </c>
       <c r="GF7" t="n">
-        <v>0.002157661598175764</v>
+        <v>1.52756683746702e-06</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.0007267373148351908</v>
+        <v>3.513593128445791e-06</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.003791996976360679</v>
+        <v>0.003131196834146976</v>
       </c>
       <c r="B8" t="n">
-        <v>0.04646717011928558</v>
+        <v>0.01319615077227354</v>
       </c>
       <c r="C8" t="n">
-        <v>0.004181102383881807</v>
+        <v>0.001756702084094286</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02518319524824619</v>
+        <v>0.003532935865223408</v>
       </c>
       <c r="E8" t="n">
-        <v>0.006448712199926376</v>
+        <v>0.003430365351960063</v>
       </c>
       <c r="F8" t="n">
-        <v>0.003642516676336527</v>
+        <v>0.001934577710926533</v>
       </c>
       <c r="G8" t="n">
-        <v>0.006748965010046959</v>
+        <v>0.002617324702441692</v>
       </c>
       <c r="H8" t="n">
-        <v>0.003403274808079004</v>
+        <v>0.001699948101304471</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002902072854340076</v>
+        <v>6.469916115747765e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.008827568963170052</v>
+        <v>0.0009623331134207547</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03620641678571701</v>
+        <v>0.01349042076617479</v>
       </c>
       <c r="L8" t="n">
-        <v>0.00258123641833663</v>
+        <v>0.002089667832478881</v>
       </c>
       <c r="M8" t="n">
-        <v>0.02359130792319775</v>
+        <v>0.006250606849789619</v>
       </c>
       <c r="N8" t="n">
-        <v>0.009905999526381493</v>
+        <v>0.006259548477828503</v>
       </c>
       <c r="O8" t="n">
-        <v>0.007034782320261002</v>
+        <v>0.001261765020899475</v>
       </c>
       <c r="P8" t="n">
-        <v>0.004555481486022472</v>
+        <v>0.002140377881005406</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.005447504110634327</v>
+        <v>0.0009134146384894848</v>
       </c>
       <c r="R8" t="n">
-        <v>0.002612250158563256</v>
+        <v>0.001074120867997408</v>
       </c>
       <c r="S8" t="n">
-        <v>0.002287798561155796</v>
+        <v>0.0003545425715856254</v>
       </c>
       <c r="T8" t="n">
-        <v>0.007637428119778633</v>
+        <v>0.001492445706389844</v>
       </c>
       <c r="U8" t="n">
-        <v>0.002175209810957313</v>
+        <v>0.001114074839279056</v>
       </c>
       <c r="V8" t="n">
-        <v>0.003387325676158071</v>
+        <v>0.001349192578345537</v>
       </c>
       <c r="W8" t="n">
-        <v>0.001210427843034267</v>
+        <v>0.0007716112886555493</v>
       </c>
       <c r="X8" t="n">
-        <v>0.003924030810594559</v>
+        <v>0.0006860380526632071</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.005846397951245308</v>
+        <v>0.0006793415523134172</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.005177710205316544</v>
+        <v>0.0006561948684975505</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.004998826887458563</v>
+        <v>0.002658952260389924</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.00187254510819912</v>
+        <v>0.002035639947280288</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.005084134638309479</v>
+        <v>0.001216301578097045</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.00026730663375929</v>
+        <v>0.001371686230413616</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.0008449089946225286</v>
+        <v>0.002255437662824988</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.002483953256160021</v>
+        <v>0.003421623026952147</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.002007699105888605</v>
+        <v>0.002822304610162973</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.003076558467000723</v>
+        <v>0.001380243804305792</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.0003664238902274519</v>
+        <v>0.001610738574527204</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.002288771560415626</v>
+        <v>0.000944356550462544</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.004201128613203764</v>
+        <v>9.662791853770614e-05</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.007159300614148378</v>
+        <v>0.003178127808496356</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.0008634721161797643</v>
+        <v>0.0006116142030805349</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.00138862943276763</v>
+        <v>0.0009077370050363243</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.0002752819273155183</v>
+        <v>0.001069935271516442</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.001997957471758127</v>
+        <v>0.0008964674780145288</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.002397877397015691</v>
+        <v>8.346690447069705e-05</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.003045244375243783</v>
+        <v>0.0003264941624365747</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.002906613517552614</v>
+        <v>0.0001262417790712789</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.00255483528599143</v>
+        <v>0.0004706502077169716</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.03026426769793034</v>
+        <v>0.007156242616474628</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.0001732306845951825</v>
+        <v>0.0002791466249618679</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.006096597760915756</v>
+        <v>0.001040928298607469</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.0005050646141171455</v>
+        <v>0.005851336754858494</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.001540601253509521</v>
+        <v>0.0006162076024338603</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.001596865011379123</v>
+        <v>0.000563759938813746</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.001510486123152077</v>
+        <v>0.001024701632559299</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.004706126172095537</v>
+        <v>0.0007856575539335608</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.001967987045645714</v>
+        <v>0.001578011550009251</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.00792983639985323</v>
+        <v>0.0002197333378717303</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.007099180482327938</v>
+        <v>0.002263371599838138</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.00420638220384717</v>
+        <v>0.002202899428084493</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.01099409721791744</v>
+        <v>0.001503109117038548</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.001320081995800138</v>
+        <v>0.001021304982714355</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.005842817947268486</v>
+        <v>0.0008780166390351951</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.004788982681930065</v>
+        <v>0.001529087196104228</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.001491509145125747</v>
+        <v>0.0002263332426082343</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.003580412594601512</v>
+        <v>0.0005859662196598947</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.001916532870382071</v>
+        <v>0.0003792022762354463</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.002858617343008518</v>
+        <v>0.0002479646936990321</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.001210987800732255</v>
+        <v>0.0001210865739267319</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.001242430880665779</v>
+        <v>0.001923218835145235</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.002598227001726627</v>
+        <v>2.640137972775847e-05</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.0008895035134628415</v>
+        <v>0.0008714440045878291</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.001123657217249274</v>
+        <v>0.000122553639812395</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.001565325073897839</v>
+        <v>0.0006824269075877964</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.003310000523924828</v>
+        <v>0.0004904225934296846</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.01735245250165462</v>
+        <v>0.006245273631066084</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.00541118485853076</v>
+        <v>5.106299067847431e-05</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.006863052025437355</v>
+        <v>0.001466417917981744</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.0004947456764057279</v>
+        <v>0.001379696652293205</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.00136420875787735</v>
+        <v>0.001467088935896754</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.003253250382840633</v>
+        <v>0.001654980005696416</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.002350944560021162</v>
+        <v>0.001004818826913834</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.00469650886952877</v>
+        <v>0.001987252617254853</v>
       </c>
       <c r="CD8" t="n">
-        <v>0.0009891518857330084</v>
+        <v>0.0005337282782420516</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.007319150492548943</v>
+        <v>0.00380500522442162</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.003368989797309041</v>
+        <v>0.0008342433138750494</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.002488671336323023</v>
+        <v>0.001406385796144605</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.001778932171873748</v>
+        <v>0.000330158625729382</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.001832561567425728</v>
+        <v>0.0007719680434092879</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.001373913371935487</v>
+        <v>0.0002120553399436176</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.0009256982011720538</v>
+        <v>0.000112991729110945</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.0025043950881809</v>
+        <v>0.0001465470995754004</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.008300500921905041</v>
+        <v>0.000803557108156383</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.002186751691624522</v>
+        <v>0.002494495362043381</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.0001025052624754608</v>
+        <v>0.002683945931494236</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.006113723386079073</v>
+        <v>0.005348426755517721</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.006798090413212776</v>
+        <v>0.002431101631373167</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.001373112783767283</v>
+        <v>0.002137568779289722</v>
       </c>
       <c r="CS8" t="n">
-        <v>0.005434349179267883</v>
+        <v>0.0002409131702734157</v>
       </c>
       <c r="CT8" t="n">
-        <v>0.006166799925267696</v>
+        <v>0.0009183072834275663</v>
       </c>
       <c r="CU8" t="n">
-        <v>0.001742057618685067</v>
+        <v>0.001114761456847191</v>
       </c>
       <c r="CV8" t="n">
-        <v>0.0005222559557296336</v>
+        <v>0.0001256335235666484</v>
       </c>
       <c r="CW8" t="n">
-        <v>0.007109335623681545</v>
+        <v>0.003611378837376833</v>
       </c>
       <c r="CX8" t="n">
-        <v>0.003676942083984613</v>
+        <v>0.0008255052380263805</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.004054665099829435</v>
+        <v>0.001463542226701975</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.002333650831133127</v>
+        <v>0.0009298036457039416</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.002244167262688279</v>
+        <v>0.0008118179976008832</v>
       </c>
       <c r="DB8" t="n">
-        <v>0.001208430388942361</v>
+        <v>0.000186806486453861</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.001806355197913945</v>
+        <v>0.0002326050162082538</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.001397703890688717</v>
+        <v>0.0005292892456054688</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.003184189554303885</v>
+        <v>0.001365757780149579</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.005793861579149961</v>
+        <v>0.003745702560991049</v>
       </c>
       <c r="DG8" t="n">
-        <v>0.001007770304568112</v>
+        <v>0.0008836893830448389</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.01301697548478842</v>
+        <v>0.001792257186025381</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.001225458923727274</v>
+        <v>0.002153628272935748</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.0009960063034668565</v>
+        <v>0.004071133211255074</v>
       </c>
       <c r="DK8" t="n">
-        <v>0.005663737654685974</v>
+        <v>0.001202330458909273</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.0006670687580481172</v>
+        <v>0.0008994538802653551</v>
       </c>
       <c r="DM8" t="n">
-        <v>0.0002609244547784328</v>
+        <v>0.001865928759798408</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.0008180392906069756</v>
+        <v>0.0009016130352392793</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.001214681891724467</v>
+        <v>0.002629525493830442</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.002420654520392418</v>
+        <v>0.0005356380715966225</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.001017166883684695</v>
+        <v>0.0006413902156054974</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.004705343395471573</v>
+        <v>0.0009732492035254836</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.003320628078654408</v>
+        <v>0.0004139655502513051</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.0008343042572960258</v>
+        <v>7.150263991206884e-05</v>
       </c>
       <c r="DU8" t="n">
-        <v>0.002402551472187042</v>
+        <v>0.0003393375664018095</v>
       </c>
       <c r="DV8" t="n">
-        <v>0.004195263143628836</v>
+        <v>0.002568214433267713</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.0009755789069458842</v>
+        <v>0.0009814429795369506</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.003092187456786633</v>
+        <v>0.0007871135603636503</v>
       </c>
       <c r="DY8" t="n">
-        <v>0.003343757707625628</v>
+        <v>0.0008528911857865751</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.00214666104875505</v>
+        <v>0.001412403653375804</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.004071713425219059</v>
+        <v>0.0008900886750780046</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.00104603567160666</v>
+        <v>0.002300850581377745</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.002032859716564417</v>
+        <v>0.0004137945070397109</v>
       </c>
       <c r="ED8" t="n">
-        <v>0.001342271454632282</v>
+        <v>0.001626148587092757</v>
       </c>
       <c r="EE8" t="n">
-        <v>0.001319208648055792</v>
+        <v>0.002207995625212789</v>
       </c>
       <c r="EF8" t="n">
-        <v>0.0009948217775672674</v>
+        <v>0.0009525074274279177</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.004625011701136827</v>
+        <v>0.002875556703656912</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.003035616828128695</v>
+        <v>0.0005920601543039083</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.002404473023489118</v>
+        <v>0.001312577165663242</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.0008264167699962854</v>
+        <v>8.473863999824971e-06</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.003028310835361481</v>
+        <v>0.0001941703085321933</v>
       </c>
       <c r="EL8" t="n">
-        <v>0.001404737820848823</v>
+        <v>0.0005015485221520066</v>
       </c>
       <c r="EM8" t="n">
-        <v>2.320087878615595e-05</v>
+        <v>0.0005376297631300986</v>
       </c>
       <c r="EN8" t="n">
-        <v>0.001072424463927746</v>
+        <v>0.0002141554141417146</v>
       </c>
       <c r="EO8" t="n">
-        <v>0.0003395924577489495</v>
+        <v>0.0001850462722359225</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.00469318637624383</v>
+        <v>0.003073683008551598</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.004754144232720137</v>
+        <v>0.0003406180185265839</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.00289761321619153</v>
+        <v>0.001087370561435819</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.003187747672200203</v>
+        <v>0.0007194179925136268</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.006098669487982988</v>
+        <v>0.001462438376620412</v>
       </c>
       <c r="EU8" t="n">
-        <v>0.004142250865697861</v>
+        <v>0.0005212686373852193</v>
       </c>
       <c r="EV8" t="n">
-        <v>0.004703397862613201</v>
+        <v>0.0002385340048931539</v>
       </c>
       <c r="EW8" t="n">
-        <v>8.809745486360043e-05</v>
+        <v>0.001490651164203882</v>
       </c>
       <c r="EX8" t="n">
-        <v>0.0004822312039323151</v>
+        <v>0.0006962430779822171</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.007413256913423538</v>
+        <v>0.004223205149173737</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0.002651349175721407</v>
+        <v>0.0006372504867613316</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.00368369510397315</v>
+        <v>0.001828111242502928</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.00229350384324789</v>
+        <v>0.0003915955894626677</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.00197283155284822</v>
+        <v>0.0008389826980419457</v>
       </c>
       <c r="FD8" t="n">
-        <v>0.002354484749957919</v>
+        <v>0.0002101402205880731</v>
       </c>
       <c r="FE8" t="n">
-        <v>0.0009294868796132505</v>
+        <v>0.000230836245464161</v>
       </c>
       <c r="FF8" t="n">
-        <v>0.002529295161366463</v>
+        <v>0.0005814285832457244</v>
       </c>
       <c r="FG8" t="n">
-        <v>0.0002241346810478717</v>
+        <v>0.0004968149587512016</v>
       </c>
       <c r="FH8" t="n">
-        <v>0.00465213181450963</v>
+        <v>0.001158281462267041</v>
       </c>
       <c r="FI8" t="n">
-        <v>0.003399579087272286</v>
+        <v>0.001152234151959419</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.005074037704616785</v>
+        <v>0.0005501697887666523</v>
       </c>
       <c r="FK8" t="n">
-        <v>0.002001307904720306</v>
+        <v>0.0004232481878716499</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.0008585131727159023</v>
+        <v>0.001048260251991451</v>
       </c>
       <c r="FM8" t="n">
-        <v>0.0003223788226023316</v>
+        <v>0.000188202437129803</v>
       </c>
       <c r="FN8" t="n">
-        <v>0.00103391706943512</v>
+        <v>0.0001820307807065547</v>
       </c>
       <c r="FO8" t="n">
-        <v>0.001812862697988749</v>
+        <v>0.0003599859774112701</v>
       </c>
       <c r="FP8" t="n">
-        <v>0.001440995140001178</v>
+        <v>0.0008031293982639909</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0.00771474651992321</v>
+        <v>2.306071110069752e-05</v>
       </c>
       <c r="FR8" t="n">
-        <v>0.006095036864280701</v>
+        <v>3.331698826514184e-05</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.003362743649631739</v>
+        <v>0.002230430953204632</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.0007592284819111228</v>
+        <v>0.002180594252422452</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.0001142672263085842</v>
+        <v>0.0009480621665716171</v>
       </c>
       <c r="FV8" t="n">
-        <v>0.000133879017084837</v>
+        <v>0.001597684109583497</v>
       </c>
       <c r="FW8" t="n">
-        <v>0.0005383131210692227</v>
+        <v>0.0008422985556535423</v>
       </c>
       <c r="FX8" t="n">
-        <v>0.001866899779997766</v>
+        <v>0.001658081775531173</v>
       </c>
       <c r="FY8" t="n">
-        <v>0.006318783853203058</v>
+        <v>0.001902675605379045</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.0008471339242532849</v>
+        <v>0.002849281299859285</v>
       </c>
       <c r="GA8" t="n">
-        <v>3.976246807724237e-05</v>
+        <v>0.0007116046617738903</v>
       </c>
       <c r="GB8" t="n">
-        <v>0.0006609535194002092</v>
+        <v>0.001364548224955797</v>
       </c>
       <c r="GC8" t="n">
-        <v>0.004726380575448275</v>
+        <v>0.002101818565279245</v>
       </c>
       <c r="GD8" t="n">
-        <v>0.003575901035219431</v>
+        <v>0.001151842880062759</v>
       </c>
       <c r="GE8" t="n">
-        <v>0.01501478441059589</v>
+        <v>0.001104255323298275</v>
       </c>
       <c r="GF8" t="n">
-        <v>0.001815721392631531</v>
+        <v>7.026779348962009e-05</v>
       </c>
       <c r="GG8" t="n">
-        <v>0.002703538164496422</v>
+        <v>0.0008135051466524601</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.001450602663680911</v>
+        <v>0.02888050116598606</v>
       </c>
       <c r="B9" t="n">
-        <v>0.02049245312809944</v>
+        <v>0.08733761310577393</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0012632628204301</v>
+        <v>0.009368135593831539</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01044578850269318</v>
+        <v>0.009226450696587563</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003009150503203273</v>
+        <v>0.02431768737733364</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01497126370668411</v>
+        <v>0.005279737990349531</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0001453346922062337</v>
+        <v>0.01265090331435204</v>
       </c>
       <c r="H9" t="n">
-        <v>0.00638284208253026</v>
+        <v>0.009299211204051971</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001456006313674152</v>
+        <v>0.01210750732570887</v>
       </c>
       <c r="J9" t="n">
-        <v>0.004798084497451782</v>
+        <v>0.02597220428287983</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01668864861130714</v>
+        <v>0.106527715921402</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0007188288727775216</v>
+        <v>0.00761874858289957</v>
       </c>
       <c r="M9" t="n">
-        <v>0.008881472051143646</v>
+        <v>0.03502438962459564</v>
       </c>
       <c r="N9" t="n">
-        <v>0.001467546913772821</v>
+        <v>0.0319761298596859</v>
       </c>
       <c r="O9" t="n">
-        <v>0.01557710207998753</v>
+        <v>0.02009675838053226</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0008676793659105897</v>
+        <v>0.001822989666834474</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.001505514606833458</v>
+        <v>0.003610191401094198</v>
       </c>
       <c r="R9" t="n">
-        <v>0.001279478776268661</v>
+        <v>0.02145556919276714</v>
       </c>
       <c r="S9" t="n">
-        <v>0.001989392098039389</v>
+        <v>0.002884833607822657</v>
       </c>
       <c r="T9" t="n">
-        <v>0.002547079930081964</v>
+        <v>0.0102475443854928</v>
       </c>
       <c r="U9" t="n">
-        <v>0.001332464977167547</v>
+        <v>0.002036446239799261</v>
       </c>
       <c r="V9" t="n">
-        <v>0.001890426850877702</v>
+        <v>0.002083332277834415</v>
       </c>
       <c r="W9" t="n">
-        <v>0.001131683122366667</v>
+        <v>0.003143249312415719</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0008502413402311504</v>
+        <v>0.002774027409031987</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.002012226264923811</v>
+        <v>0.00613500690087676</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.001494040014222264</v>
+        <v>0.007628185674548149</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.002257388783618808</v>
+        <v>0.009648367762565613</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0001515832263976336</v>
+        <v>0.002215073211118579</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.002208144403994083</v>
+        <v>0.006342004053294659</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.00101875641848892</v>
+        <v>0.004921709187328815</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.0001772648538462818</v>
+        <v>0.01034630835056305</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.0005630395608022809</v>
+        <v>0.0140692749992013</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.0008064822759479284</v>
+        <v>0.01471741311252117</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.0007303066086024046</v>
+        <v>0.002653656993061304</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.001003223471343517</v>
+        <v>0.02370771020650864</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.0008438890217803419</v>
+        <v>0.01160351280122995</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.002424097619950771</v>
+        <v>0.001288300496526062</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.00292839971370995</v>
+        <v>0.01424617879092693</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.0009750970639288425</v>
+        <v>0.007453175727277994</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.0002129019849235192</v>
+        <v>0.0004701332654803991</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.0005468606250360608</v>
+        <v>0.002133095636963844</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.002903247717767954</v>
+        <v>0.00707548251375556</v>
       </c>
       <c r="AQ9" t="n">
-        <v>3.40232509188354e-05</v>
+        <v>0.005239080637693405</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.002044572727754712</v>
+        <v>0.009139157831668854</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.00232212501578033</v>
+        <v>0.007457571569830179</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.0008615330443717539</v>
+        <v>0.01289112493395805</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.01381006371229887</v>
+        <v>0.06956976652145386</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.0004560370871331543</v>
+        <v>0.007764431647956371</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.0008653161930851638</v>
+        <v>0.001796173164620996</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.001269742613658309</v>
+        <v>0.02601321041584015</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.007889155298471451</v>
+        <v>0.01271637342870235</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.0005186187336221337</v>
+        <v>0.001535137183964252</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.003245158120989799</v>
+        <v>0.003855817951261997</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.003854849375784397</v>
+        <v>0.003780463244765997</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.000597445061430335</v>
+        <v>0.009739005006849766</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.004393805284053087</v>
+        <v>0.003184829140082002</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.005688916891813278</v>
+        <v>0.01213663630187511</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.002769613638520241</v>
+        <v>0.003198273247107863</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.004695405252277851</v>
+        <v>0.01078308187425137</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.004324499983340502</v>
+        <v>0.006617999635636806</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.0008783069788478315</v>
+        <v>0.0102207325398922</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.003935420885682106</v>
+        <v>0.006299207452684641</v>
       </c>
       <c r="BK9" t="n">
-        <v>7.124105468392372e-05</v>
+        <v>0.01097636949270964</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.000456114299595356</v>
+        <v>0.002069795969873667</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.003955277614295483</v>
+        <v>0.004803420510143042</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.002269138116389513</v>
+        <v>0.001760578481480479</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.0009112682892009616</v>
+        <v>0.01085915602743626</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.001169609138742089</v>
+        <v>0.01199224498122931</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.000787186436355114</v>
+        <v>1.717917621135712e-05</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.001287896884605289</v>
+        <v>0.00816555880010128</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.0005687839584425092</v>
+        <v>0.006931948475539684</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.001445458270609379</v>
+        <v>0.0001133130863308907</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.001553191570565104</v>
+        <v>0.001815894152969122</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.006789284758269787</v>
+        <v>0.05039682239294052</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.002355861943215132</v>
+        <v>0.003412592224776745</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.002138597192242742</v>
+        <v>0.01018111407756805</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.001754148164764047</v>
+        <v>0.004859155509620905</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.002292500343173742</v>
+        <v>0.002855184953659773</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.001122798654250801</v>
+        <v>0.008126144297420979</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.001513435505330563</v>
+        <v>0.0005012576002627611</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.002912488533183932</v>
+        <v>0.001296654809266329</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.0006832184735685587</v>
+        <v>0.007583134341984987</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.003104957519099116</v>
+        <v>0.02726214006543159</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.002312218770384789</v>
+        <v>0.003744746092706919</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.001726632239297032</v>
+        <v>0.004520423710346222</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.001273130066692829</v>
+        <v>0.00494634173810482</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.002445757389068604</v>
+        <v>0.002809063764289021</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.001365569536574185</v>
+        <v>0.0008681460749357939</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.0009506666101515293</v>
+        <v>0.003601834177970886</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.001396112143993378</v>
+        <v>0.001824816106818616</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.002912800293415785</v>
+        <v>0.002783658914268017</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.0006949498201720417</v>
+        <v>0.04117497801780701</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.0008618452120572329</v>
+        <v>0.01270569767802954</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.002686402294784784</v>
+        <v>0.003471810836344957</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.0001146823924500495</v>
+        <v>0.008381780236959457</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.001683697104454041</v>
+        <v>0.009699968621134758</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.003487940644845366</v>
+        <v>0.003083487739786506</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.003673445899039507</v>
+        <v>0.003414805745705962</v>
       </c>
       <c r="CU9" t="n">
-        <v>8.981006976682693e-05</v>
+        <v>0.0005880263634026051</v>
       </c>
       <c r="CV9" t="n">
-        <v>0.0002120963472407311</v>
+        <v>0.00448889983817935</v>
       </c>
       <c r="CW9" t="n">
-        <v>0.002604137873277068</v>
+        <v>0.02791264280676842</v>
       </c>
       <c r="CX9" t="n">
-        <v>0.002396292285993695</v>
+        <v>0.003356235101819038</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.002664259634912014</v>
+        <v>0.004800825845450163</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.0007241920102387667</v>
+        <v>0.001552149886265397</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.002559249522164464</v>
+        <v>0.003221049439162016</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.001293705427087843</v>
+        <v>0.003695416729897261</v>
       </c>
       <c r="DC9" t="n">
-        <v>0.002189293503761292</v>
+        <v>0.004181261640042067</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.0006639283383265138</v>
+        <v>0.007325132377445698</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.002066847402602434</v>
+        <v>0.02231229841709137</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.00199145101942122</v>
+        <v>0.01435372233390808</v>
       </c>
       <c r="DG9" t="n">
-        <v>0.0001013623841572553</v>
+        <v>9.107752703130245e-06</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.006694952491670847</v>
+        <v>0.01324200164526701</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.0005080857081338763</v>
+        <v>0.004676393233239651</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.001124128000810742</v>
+        <v>0.04387885332107544</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.002859728643670678</v>
+        <v>0.002194887492805719</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.001886200858280063</v>
+        <v>0.003703171154484153</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.000744792225304991</v>
+        <v>0.006615279708057642</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.0004345950146671385</v>
+        <v>0.003843109356239438</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.0001281562581425533</v>
+        <v>0.01007697358727455</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.001193278236314654</v>
+        <v>0.007304054219275713</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.001653981395065784</v>
+        <v>0.01895983144640923</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.0003221711958758533</v>
+        <v>0.001016149995848536</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.0003859368734993041</v>
+        <v>0.01342303585261106</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.000589359609875828</v>
+        <v>0.002730748616158962</v>
       </c>
       <c r="DU9" t="n">
-        <v>0.001240783138200641</v>
+        <v>0.01755325123667717</v>
       </c>
       <c r="DV9" t="n">
-        <v>0.002204393735155463</v>
+        <v>0.005197194404900074</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.0005336382891982794</v>
+        <v>0.003872403409332037</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.000914379779715091</v>
+        <v>0.01585121266543865</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.003884975565597415</v>
+        <v>0.01257221587002277</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.0002809849684126675</v>
+        <v>0.006157160270959139</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.0009384939912706614</v>
+        <v>0.01592867448925972</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.0006216262117959559</v>
+        <v>0.01932014897465706</v>
       </c>
       <c r="EC9" t="n">
-        <v>0.0003624396631494164</v>
+        <v>0.0009130676626227796</v>
       </c>
       <c r="ED9" t="n">
-        <v>0.001231644884683192</v>
+        <v>0.03465741127729416</v>
       </c>
       <c r="EE9" t="n">
-        <v>7.926480611786246e-05</v>
+        <v>0.01613249816000462</v>
       </c>
       <c r="EF9" t="n">
-        <v>0.0007988831494003534</v>
+        <v>0.01290498394519091</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.00223432993516326</v>
+        <v>0.01183643005788326</v>
       </c>
       <c r="EH9" t="n">
-        <v>0.001529582077637315</v>
+        <v>0.001510229543782771</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.0001816577860154212</v>
+        <v>0.0210296344012022</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.0001587910810485482</v>
+        <v>0.004502871539443731</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.002417493145912886</v>
+        <v>0.001265533734112978</v>
       </c>
       <c r="EL9" t="n">
-        <v>0.001360071357339621</v>
+        <v>0.001432618824765086</v>
       </c>
       <c r="EM9" t="n">
-        <v>0.0003619189374148846</v>
+        <v>0.009386704303324223</v>
       </c>
       <c r="EN9" t="n">
-        <v>0.000404578517191112</v>
+        <v>0.002935945754870772</v>
       </c>
       <c r="EO9" t="n">
-        <v>0.000118647760245949</v>
+        <v>0.001228217966854572</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.0007984203402884305</v>
+        <v>0.01589671149849892</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.002431124681606889</v>
+        <v>0.002739036455750465</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.0009150095866061747</v>
+        <v>0.0001887800171971321</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.001916225184686482</v>
+        <v>0.01309657748788595</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.003516981145367026</v>
+        <v>0.01151998341083527</v>
       </c>
       <c r="EU9" t="n">
-        <v>0.002778189955279231</v>
+        <v>0.007114185485988855</v>
       </c>
       <c r="EV9" t="n">
-        <v>0.004986673593521118</v>
+        <v>0.002054513432085514</v>
       </c>
       <c r="EW9" t="n">
-        <v>0.0006149155087769032</v>
+        <v>0.004723935388028622</v>
       </c>
       <c r="EX9" t="n">
-        <v>0.000172571002622135</v>
+        <v>0.005293139722198248</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.002457133494317532</v>
+        <v>0.03197960555553436</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0.001696183462627232</v>
+        <v>0.003107891883701086</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.001906371675431728</v>
+        <v>0.0059997932985425</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.0009947861544787884</v>
+        <v>0.00217126845382154</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.002217134460806847</v>
+        <v>0.003202215768396854</v>
       </c>
       <c r="FD9" t="n">
-        <v>0.002028570510447025</v>
+        <v>0.0005547183100134134</v>
       </c>
       <c r="FE9" t="n">
-        <v>0.001349063124507666</v>
+        <v>0.004368341993540525</v>
       </c>
       <c r="FF9" t="n">
-        <v>0.00141203124076128</v>
+        <v>0.006277122069150209</v>
       </c>
       <c r="FG9" t="n">
-        <v>6.06075263931416e-05</v>
+        <v>0.002599765313789248</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.001603122800588608</v>
+        <v>0.01497870124876499</v>
       </c>
       <c r="FI9" t="n">
-        <v>0.002567175310105085</v>
+        <v>0.0141219412907958</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.003327922662720084</v>
+        <v>0.01819063909351826</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.0005222306936047971</v>
+        <v>0.002734754700213671</v>
       </c>
       <c r="FL9" t="n">
-        <v>0.001428513089194894</v>
+        <v>0.001303863944485784</v>
       </c>
       <c r="FM9" t="n">
-        <v>0.0003844275197479874</v>
+        <v>0.005209581926465034</v>
       </c>
       <c r="FN9" t="n">
-        <v>0.001310384715907276</v>
+        <v>0.006077783647924662</v>
       </c>
       <c r="FO9" t="n">
-        <v>0.001499764388427138</v>
+        <v>0.002694517839699984</v>
       </c>
       <c r="FP9" t="n">
-        <v>0.001036673784255981</v>
+        <v>0.0203248206526041</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.005453619174659252</v>
+        <v>0.02430497854948044</v>
       </c>
       <c r="FR9" t="n">
-        <v>0.001857338007539511</v>
+        <v>0.006893485318869352</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.002731960732489824</v>
+        <v>0.008086937479674816</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.0004675806558225304</v>
+        <v>0.02327807806432247</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.002490106504410505</v>
+        <v>0.00120852142572403</v>
       </c>
       <c r="FV9" t="n">
-        <v>0.002061759820207953</v>
+        <v>0.01252999063581228</v>
       </c>
       <c r="FW9" t="n">
-        <v>0.001570044551044703</v>
+        <v>0.002591313328593969</v>
       </c>
       <c r="FX9" t="n">
-        <v>0.0001855501031968743</v>
+        <v>0.01284216903150082</v>
       </c>
       <c r="FY9" t="n">
-        <v>0.003073708154261112</v>
+        <v>0.006546474527567625</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.0008465869468636811</v>
+        <v>0.01110172271728516</v>
       </c>
       <c r="GA9" t="n">
-        <v>0.001533671631477773</v>
+        <v>0.002761092502623796</v>
       </c>
       <c r="GB9" t="n">
-        <v>0.0006096562137827277</v>
+        <v>0.0149499112740159</v>
       </c>
       <c r="GC9" t="n">
-        <v>0.002726989332586527</v>
+        <v>0.01253771595656872</v>
       </c>
       <c r="GD9" t="n">
-        <v>0.001635790569707751</v>
+        <v>0.001664030714891851</v>
       </c>
       <c r="GE9" t="n">
-        <v>0.00976221077144146</v>
+        <v>7.791275857016444e-05</v>
       </c>
       <c r="GF9" t="n">
-        <v>0.0001287468476220965</v>
+        <v>0.0123852239921689</v>
       </c>
       <c r="GG9" t="n">
-        <v>0.001474639168009162</v>
+        <v>0.01239885110408068</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.001448232913389802</v>
+        <v>2.240172705114674e-07</v>
       </c>
       <c r="B10" t="n">
-        <v>0.006541443523019552</v>
+        <v>1.095464085665299e-06</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0005993323284201324</v>
+        <v>2.659200504240289e-07</v>
       </c>
       <c r="D10" t="n">
-        <v>0.004268455319106579</v>
+        <v>5.617398812773899e-08</v>
       </c>
       <c r="E10" t="n">
-        <v>0.001053998013958335</v>
+        <v>4.803350179827248e-07</v>
       </c>
       <c r="F10" t="n">
-        <v>0.00132017454598099</v>
+        <v>6.645907291158437e-08</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0004478920018300414</v>
+        <v>5.520706736206193e-08</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0001253677328350022</v>
+        <v>1.424204043587451e-07</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0003029967483598739</v>
+        <v>1.44854539030348e-07</v>
       </c>
       <c r="J10" t="n">
-        <v>0.001922249561175704</v>
+        <v>8.146702867861677e-08</v>
       </c>
       <c r="K10" t="n">
-        <v>0.004560667555779219</v>
+        <v>1.354870619252324e-06</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0005316674942150712</v>
+        <v>2.497712614513148e-07</v>
       </c>
       <c r="M10" t="n">
-        <v>0.003118237713351846</v>
+        <v>3.110497743818996e-07</v>
       </c>
       <c r="N10" t="n">
-        <v>0.001450709300115705</v>
+        <v>6.426202503462264e-07</v>
       </c>
       <c r="O10" t="n">
-        <v>0.002278503961861134</v>
+        <v>8.772585147198697e-08</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0007852884591557086</v>
+        <v>3.436201723161503e-08</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.001251957030035555</v>
+        <v>2.17240639699412e-07</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0002351079747313634</v>
+        <v>2.989346512549673e-07</v>
       </c>
       <c r="S10" t="n">
-        <v>6.636972830165178e-05</v>
+        <v>4.465792358132603e-08</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0008791182190179825</v>
+        <v>1.502650377460668e-07</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0003424242313485593</v>
+        <v>1.177419761688725e-07</v>
       </c>
       <c r="V10" t="n">
-        <v>0.000730939325876534</v>
+        <v>1.328510990106224e-07</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0004694988019764423</v>
+        <v>4.935021280516594e-08</v>
       </c>
       <c r="X10" t="n">
-        <v>0.0004954889300279319</v>
+        <v>5.885549114736932e-08</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.001182001549750566</v>
+        <v>1.454953917345847e-07</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.0001704340393189341</v>
+        <v>3.410365323475162e-08</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.000739924143999815</v>
+        <v>1.680457728525653e-07</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.0001340085291303694</v>
+        <v>5.774258937663035e-08</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.0004746598715428263</v>
+        <v>1.346089533171835e-07</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.0001258550328202546</v>
+        <v>1.658421950878619e-07</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.964490158774424e-05</v>
+        <v>1.903852080431534e-07</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.0001321442541666329</v>
+        <v>3.353927695570746e-07</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.0002713294525165111</v>
+        <v>1.567234590993394e-07</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.0006943058106116951</v>
+        <v>4.122187391430998e-08</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.0003796544624492526</v>
+        <v>3.952501970161393e-07</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.0002779643109533936</v>
+        <v>1.379059142436745e-07</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.00065100152278319</v>
+        <v>1.093315802336292e-07</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.0009878408163785934</v>
+        <v>2.203755116170214e-07</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.0002243552298750728</v>
+        <v>4.187927871157626e-08</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.0001842279743868858</v>
+        <v>1.694483842129557e-08</v>
       </c>
       <c r="AO10" t="n">
-        <v>6.517954170703888e-05</v>
+        <v>2.791612985220127e-08</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.0003764856373891234</v>
+        <v>8.001556750514283e-08</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.0005382011877372861</v>
+        <v>1.583024413776002e-07</v>
       </c>
       <c r="AR10" t="n">
-        <v>8.276147127617151e-05</v>
+        <v>1.21540040254331e-07</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.0005961160059086978</v>
+        <v>6.265393892590509e-08</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.0001411065459251404</v>
+        <v>1.428229552402627e-07</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.004125706385821104</v>
+        <v>1.156461053142266e-06</v>
       </c>
       <c r="AV10" t="n">
-        <v>6.008936179568991e-05</v>
+        <v>8.962534536749445e-08</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.000923121755477041</v>
+        <v>1.583514261938035e-07</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.0003105677897110581</v>
+        <v>2.994731573835452e-07</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.0002167053753510118</v>
+        <v>7.111031408157942e-08</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.0001280201831832528</v>
+        <v>2.089711870212341e-08</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.0006426867330446839</v>
+        <v>1.061626591081222e-07</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.0007939769420772791</v>
+        <v>1.237696380940179e-07</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.0008100278209894896</v>
+        <v>1.153037487711117e-07</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.001048483420163393</v>
+        <v>1.641585924971878e-07</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.001071538892574608</v>
+        <v>2.743915956671117e-07</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.000931534799747169</v>
+        <v>1.965460114661255e-07</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.00158390833530575</v>
+        <v>2.484019603343768e-07</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.0004397814336698502</v>
+        <v>1.44396224754928e-07</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.0003949037636630237</v>
+        <v>5.948943027078712e-08</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.001469397102482617</v>
+        <v>1.556573181460408e-07</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.0001447516115149483</v>
+        <v>1.077624034451219e-07</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.0009765297872945666</v>
+        <v>3.241109425289324e-08</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.0004827209922950715</v>
+        <v>1.419082309439545e-07</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.0002475768851581961</v>
+        <v>8.096151304926025e-08</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.0003399080014787614</v>
+        <v>1.579017805397598e-08</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.0005349915591068566</v>
+        <v>2.808871215620456e-07</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.0001025082601699978</v>
+        <v>1.871559973665171e-08</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.0004210305050946772</v>
+        <v>2.796833484808303e-07</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.0006575520383194089</v>
+        <v>6.345952385800047e-08</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.0001348100195173174</v>
+        <v>1.320055531550679e-07</v>
       </c>
       <c r="BU10" t="n">
-        <v>3.089992969762534e-05</v>
+        <v>2.634274665069825e-08</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.002238553250208497</v>
+        <v>7.283666718649329e-07</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.0007425975636579096</v>
+        <v>8.227622139145296e-09</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.000568346818909049</v>
+        <v>4.991191104863901e-08</v>
       </c>
       <c r="BY10" t="n">
-        <v>6.751778710167855e-05</v>
+        <v>9.697674130393352e-08</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.0003796686651185155</v>
+        <v>4.258783903310359e-08</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.0009128001402132213</v>
+        <v>2.132740348770312e-07</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.0001645617885515094</v>
+        <v>1.338037520781654e-07</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.0006050997180864215</v>
+        <v>1.241491247583326e-07</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.0003456424456089735</v>
+        <v>2.004737709171422e-08</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.001015660120174289</v>
+        <v>3.986016281487537e-07</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.0004506758996285498</v>
+        <v>1.143573555850708e-07</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.0003062226751353592</v>
+        <v>3.29789102693212e-08</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.000326675915857777</v>
+        <v>1.257205326510302e-07</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.0004002380010206252</v>
+        <v>7.928483114483242e-08</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.0003101370530202985</v>
+        <v>5.496755051126456e-09</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.0001198441532324068</v>
+        <v>3.42107604467401e-08</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.0004596663929987699</v>
+        <v>4.918580387425209e-08</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.0004312205710448325</v>
+        <v>2.619185011099034e-07</v>
       </c>
       <c r="CN10" t="n">
-        <v>9.689010039437562e-05</v>
+        <v>6.883663559165143e-07</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.209807760460535e-05</v>
+        <v>1.796256867692136e-07</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.001353647443465889</v>
+        <v>8.666646067467809e-08</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.001096006715670228</v>
+        <v>1.179399617967647e-07</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.0001824690698413178</v>
+        <v>2.669098080332333e-07</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.0008212868124246597</v>
+        <v>8.710155441349343e-08</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.0008382545202039182</v>
+        <v>1.357803398605029e-07</v>
       </c>
       <c r="CU10" t="n">
-        <v>5.656226130668074e-05</v>
+        <v>4.848284618219623e-08</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.0002838756772689521</v>
+        <v>7.816730374088365e-08</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.0008858844521455467</v>
+        <v>3.964043457926891e-07</v>
       </c>
       <c r="CX10" t="n">
-        <v>0.0003561144112609327</v>
+        <v>1.06126492482872e-07</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.0006638213526457548</v>
+        <v>1.314259989726452e-08</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.0003880824369844049</v>
+        <v>9.311826687508074e-08</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.0004833237908314914</v>
+        <v>7.276105407072464e-08</v>
       </c>
       <c r="DB10" t="n">
-        <v>0.0003481266903690994</v>
+        <v>4.914954843115993e-08</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.0001614757202332839</v>
+        <v>5.543468262203533e-08</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.0002510290360078216</v>
+        <v>8.834599896090367e-08</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.000469280406832695</v>
+        <v>3.053048374113132e-07</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.0005539042176678777</v>
+        <v>1.750779290432547e-07</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.001240094657987356</v>
+        <v>4.26361523864216e-09</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.003586666658520699</v>
+        <v>1.60800595949695e-07</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.0009614016162231565</v>
+        <v>1.352222369632727e-07</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.0004136333300266415</v>
+        <v>4.449738639777934e-07</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.0001590991450939327</v>
+        <v>4.723488444824397e-08</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.001074139261618257</v>
+        <v>5.060778818233302e-08</v>
       </c>
       <c r="DM10" t="n">
-        <v>0.0002244547795271501</v>
+        <v>1.479400992820956e-07</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.00052932946709916</v>
+        <v>8.865531242463476e-08</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.0005139370914548635</v>
+        <v>1.675953740232217e-07</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.0004723666643258184</v>
+        <v>7.986638905776999e-08</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.0003545284853316844</v>
+        <v>1.669874620802148e-07</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.001010237727314234</v>
+        <v>1.439191787966365e-08</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.0006239631911739707</v>
+        <v>6.949579045567589e-08</v>
       </c>
       <c r="DT10" t="n">
-        <v>4.449770131031983e-06</v>
+        <v>7.261895973442734e-08</v>
       </c>
       <c r="DU10" t="n">
-        <v>4.06726794608403e-05</v>
+        <v>5.927298474261988e-08</v>
       </c>
       <c r="DV10" t="n">
-        <v>0.0008957055979408324</v>
+        <v>7.663312118211252e-08</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.0003826488682534546</v>
+        <v>8.780753546488995e-08</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.000123735488159582</v>
+        <v>3.515503408380027e-07</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.001040686154738069</v>
+        <v>1.140368066643305e-08</v>
       </c>
       <c r="DZ10" t="n">
-        <v>9.946538921212777e-05</v>
+        <v>2.456062020428362e-09</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.0009991191327571869</v>
+        <v>2.570027390902396e-07</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.0007259366102516651</v>
+        <v>1.477385325188152e-07</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.0003669302095659077</v>
+        <v>1.524719195344915e-08</v>
       </c>
       <c r="ED10" t="n">
-        <v>4.987442298443057e-05</v>
+        <v>1.757485819098292e-07</v>
       </c>
       <c r="EE10" t="n">
-        <v>8.456107752863318e-05</v>
+        <v>1.957530031404531e-07</v>
       </c>
       <c r="EF10" t="n">
-        <v>1.985122798942029e-05</v>
+        <v>1.274016980801207e-08</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.0006053695688024163</v>
+        <v>1.859933576042749e-07</v>
       </c>
       <c r="EH10" t="n">
-        <v>9.510575182503089e-05</v>
+        <v>7.733326867764845e-09</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.0001934681058628485</v>
+        <v>1.410592176398495e-08</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.0005690761609002948</v>
+        <v>8.348673752323066e-09</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.0003359107067808509</v>
+        <v>3.859091535218795e-08</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.0006520287715829909</v>
+        <v>6.719035638980131e-08</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.0002274674479849637</v>
+        <v>5.725575036308328e-08</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.0001502875529695302</v>
+        <v>1.363459034564585e-07</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.0001997642830247059</v>
+        <v>1.076493845175719e-07</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.0002611899399198592</v>
+        <v>1.457254796832785e-07</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.0005082182469777763</v>
+        <v>9.603299844229696e-08</v>
       </c>
       <c r="ER10" t="n">
-        <v>5.275035073282197e-05</v>
+        <v>4.825147925657802e-08</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.0006697946228086948</v>
+        <v>1.2512376201812e-07</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.0009529085364192724</v>
+        <v>1.327362326719594e-07</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.0003348457103129476</v>
+        <v>4.062585290398602e-08</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.001181352301500738</v>
+        <v>3.312536023258872e-08</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.0004635402583517134</v>
+        <v>5.357590993071426e-08</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.0002494695363566279</v>
+        <v>5.398962699132426e-08</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.0008623080793768167</v>
+        <v>4.583205281960545e-07</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.0002449683961458504</v>
+        <v>9.112262944199756e-08</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.0004662623978219926</v>
+        <v>5.375952127906203e-09</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.0001922980591189116</v>
+        <v>6.285149112272848e-08</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.0004474756715353578</v>
+        <v>8.26094321837445e-08</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.0004286706971470267</v>
+        <v>1.112095304733884e-08</v>
       </c>
       <c r="FE10" t="n">
-        <v>8.141926082316786e-05</v>
+        <v>6.160738053040404e-08</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.0004508578276727349</v>
+        <v>1.004912206781228e-07</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.0002990320790559053</v>
+        <v>3.37715206910616e-08</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.0006558746681548655</v>
+        <v>1.561283795581403e-07</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.0007638728711754084</v>
+        <v>1.224203316496641e-07</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.00110002642031759</v>
+        <v>1.95169150174479e-07</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.00012888629862573</v>
+        <v>7.674198343465832e-08</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.0001269156346097589</v>
+        <v>1.226958943334466e-07</v>
       </c>
       <c r="FM10" t="n">
-        <v>1.957356289494783e-06</v>
+        <v>1.234271138628174e-07</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.0006276934873312712</v>
+        <v>6.521968032302539e-08</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.0005443866248242557</v>
+        <v>1.361232051522165e-07</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.0001604892895556986</v>
+        <v>2.117972854875916e-07</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.0002171682863263413</v>
+        <v>2.844935238499602e-07</v>
       </c>
       <c r="FR10" t="n">
-        <v>7.109687430784106e-05</v>
+        <v>2.11412078954254e-08</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.0002592676901258528</v>
+        <v>2.577193214392537e-08</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.001868758117780089</v>
+        <v>3.938444592677115e-07</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.0003536125004757196</v>
+        <v>5.72271403598279e-08</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.000770644168369472</v>
+        <v>6.622155979130184e-08</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.0004534019390121102</v>
+        <v>6.74061908512158e-08</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.0004706257313955575</v>
+        <v>1.76369226778661e-07</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.0009809596231207252</v>
+        <v>3.725543251675845e-08</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.000115335889859125</v>
+        <v>1.896756174346592e-07</v>
       </c>
       <c r="GA10" t="n">
-        <v>6.631611904595047e-05</v>
+        <v>2.589303704780832e-08</v>
       </c>
       <c r="GB10" t="n">
-        <v>5.603741010418162e-05</v>
+        <v>6.834816446144032e-08</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.0003977697051595896</v>
+        <v>7.662504231120693e-08</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.0007894745795056224</v>
+        <v>1.285699511299754e-07</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.001983851427212358</v>
+        <v>5.485355814016657e-08</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.000463117437902838</v>
+        <v>1.696789126981457e-07</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.0006323783891275525</v>
+        <v>1.687876505229724e-07</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.03737068921327591</v>
+        <v>0.1917335540056229</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3217195570468903</v>
+        <v>0.4535209834575653</v>
       </c>
       <c r="C11" t="n">
-        <v>0.03067965060472488</v>
+        <v>0.0733206644654274</v>
       </c>
       <c r="D11" t="n">
-        <v>0.229483887553215</v>
+        <v>0.1990135759115219</v>
       </c>
       <c r="E11" t="n">
-        <v>0.02875650115311146</v>
+        <v>0.2034010291099548</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2613096833229065</v>
+        <v>0.07957664132118225</v>
       </c>
       <c r="G11" t="n">
-        <v>0.01400620117783546</v>
+        <v>0.1365914344787598</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1274160444736481</v>
+        <v>0.11133923381567</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0642784982919693</v>
+        <v>0.1605264693498611</v>
       </c>
       <c r="J11" t="n">
-        <v>0.08555257320404053</v>
+        <v>0.1552025377750397</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2741750478744507</v>
+        <v>0.5906378030776978</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02072212658822536</v>
+        <v>0.09982024878263474</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1983650177717209</v>
+        <v>0.2516661286354065</v>
       </c>
       <c r="N11" t="n">
-        <v>0.01928907632827759</v>
+        <v>0.248075857758522</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2605753540992737</v>
+        <v>0.00373087078332901</v>
       </c>
       <c r="P11" t="n">
-        <v>0.03637361153960228</v>
+        <v>0.07791580259799957</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.008558597415685654</v>
+        <v>0.08729500323534012</v>
       </c>
       <c r="R11" t="n">
-        <v>0.03641487285494804</v>
+        <v>0.3334282338619232</v>
       </c>
       <c r="S11" t="n">
-        <v>0.008271743543446064</v>
+        <v>0.05957771465182304</v>
       </c>
       <c r="T11" t="n">
-        <v>0.01226460374891758</v>
+        <v>0.02241014875471592</v>
       </c>
       <c r="U11" t="n">
-        <v>0.04222498834133148</v>
+        <v>0.02014839649200439</v>
       </c>
       <c r="V11" t="n">
-        <v>0.05406596511602402</v>
+        <v>0.06409375369548798</v>
       </c>
       <c r="W11" t="n">
-        <v>0.07273294031620026</v>
+        <v>0.03879636526107788</v>
       </c>
       <c r="X11" t="n">
-        <v>0.02413001656532288</v>
+        <v>0.005610324442386627</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.03020328283309937</v>
+        <v>0.03263270854949951</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.05604981631040573</v>
+        <v>0.08991457521915436</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.04563035815954208</v>
+        <v>0.03893004357814789</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.01870910823345184</v>
+        <v>0.00654204934835434</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.006123736966401339</v>
+        <v>0.01594294235110283</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.0317186713218689</v>
+        <v>0.04795433208346367</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.002626385539770126</v>
+        <v>0.02315903455018997</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.02173427864909172</v>
+        <v>0.2417875379323959</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.02259529195725918</v>
+        <v>0.1238327622413635</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.007675993721932173</v>
+        <v>0.05214327201247215</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.01450768392533064</v>
+        <v>0.1115791201591492</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.02231215313076973</v>
+        <v>0.01689990237355232</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.04829558730125427</v>
+        <v>0.1258879452943802</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.03391605243086815</v>
+        <v>0.01143428310751915</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.01860941387712955</v>
+        <v>0.002631578361615539</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.0298760961741209</v>
+        <v>0.07437772303819656</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.01602529734373093</v>
+        <v>0.03750641644001007</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.03898439928889275</v>
+        <v>0.1206983327865601</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.01801123097538948</v>
+        <v>0.09235032647848129</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.03884419053792953</v>
+        <v>0.2281956672668457</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.03945731744170189</v>
+        <v>0.004586830735206604</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.005122460424900055</v>
+        <v>0.2286094129085541</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.1914522349834442</v>
+        <v>0.382303774356842</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.02270926535129547</v>
+        <v>0.01414159871637821</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.07905389368534088</v>
+        <v>0.02726825326681137</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.04002087190747261</v>
+        <v>0.06470324844121933</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.1338228285312653</v>
+        <v>0.0999029353260994</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.0552421435713768</v>
+        <v>0.04890178889036179</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.0251832976937294</v>
+        <v>0.01920268312096596</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.07571809738874435</v>
+        <v>0.01737425476312637</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.02971283346414566</v>
+        <v>0.05843401327729225</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.08513103425502777</v>
+        <v>0.1311053484678268</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.08483453840017319</v>
+        <v>0.04990192130208015</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.02999397739768028</v>
+        <v>0.1891719698905945</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.03381996974349022</v>
+        <v>0.07777195423841476</v>
       </c>
       <c r="BH11" t="n">
-        <v>0.02948732301592827</v>
+        <v>0.1858560740947723</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.04436928406357765</v>
+        <v>0.1332323253154755</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.03735395893454552</v>
+        <v>0.01825406029820442</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.03934058919548988</v>
+        <v>0.07354138791561127</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.01932290755212307</v>
+        <v>0.03856302052736282</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.05436165630817413</v>
+        <v>0.03869801759719849</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.04422147572040558</v>
+        <v>0.006664264015853405</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.01906754821538925</v>
+        <v>0.06219610199332237</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.001339428592473269</v>
+        <v>0.1099887192249298</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.004752091132104397</v>
+        <v>0.08514814078807831</v>
       </c>
       <c r="BR11" t="n">
-        <v>0.02225406840443611</v>
+        <v>0.1746698915958405</v>
       </c>
       <c r="BS11" t="n">
-        <v>0.02472692169249058</v>
+        <v>0.01346654258668423</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.007812278345227242</v>
+        <v>0.0174822099506855</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.01266524288803339</v>
+        <v>0.1560718417167664</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.1095548793673515</v>
+        <v>0.2072479277849197</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.05267888680100441</v>
+        <v>0.0205424539744854</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.06485909223556519</v>
+        <v>0.06697627902030945</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.01937993243336678</v>
+        <v>0.0568498894572258</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.09072965383529663</v>
+        <v>0.06155726686120033</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.00482402928173542</v>
+        <v>0.03884604200720787</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.02405717968940735</v>
+        <v>0.01095816120505333</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.0488828606903553</v>
+        <v>0.04595443606376648</v>
       </c>
       <c r="CD11" t="n">
-        <v>0.00804419256746769</v>
+        <v>0.000723646953701973</v>
       </c>
       <c r="CE11" t="n">
-        <v>0.0450594387948513</v>
+        <v>0.1073290929198265</v>
       </c>
       <c r="CF11" t="n">
-        <v>0.04710397869348526</v>
+        <v>0.005085288546979427</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.03014113381505013</v>
+        <v>0.06244492158293724</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.01100831013172865</v>
+        <v>0.04402204230427742</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.04031059890985489</v>
+        <v>0.004545355215668678</v>
       </c>
       <c r="CJ11" t="n">
-        <v>0.02370886318385601</v>
+        <v>0.05251047760248184</v>
       </c>
       <c r="CK11" t="n">
-        <v>0.02847889438271523</v>
+        <v>0.009048227220773697</v>
       </c>
       <c r="CL11" t="n">
-        <v>0.03291371837258339</v>
+        <v>0.03171111643314362</v>
       </c>
       <c r="CM11" t="n">
-        <v>0.05457184091210365</v>
+        <v>0.06933118402957916</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.01356694474816322</v>
+        <v>0.2235558331012726</v>
       </c>
       <c r="CO11" t="n">
-        <v>0.009711172431707382</v>
+        <v>0.01390534639358521</v>
       </c>
       <c r="CP11" t="n">
-        <v>0.05184077098965645</v>
+        <v>0.08454346656799316</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.005138168577104807</v>
+        <v>0.06836366653442383</v>
       </c>
       <c r="CR11" t="n">
-        <v>0.02646303549408913</v>
+        <v>0.1891468465328217</v>
       </c>
       <c r="CS11" t="n">
-        <v>0.0692262202501297</v>
+        <v>0.07354503124952316</v>
       </c>
       <c r="CT11" t="n">
-        <v>0.04688046127557755</v>
+        <v>0.07465305179357529</v>
       </c>
       <c r="CU11" t="n">
-        <v>0.008374212309718132</v>
+        <v>0.01162570714950562</v>
       </c>
       <c r="CV11" t="n">
-        <v>0.002506394172087312</v>
+        <v>0.02530152909457684</v>
       </c>
       <c r="CW11" t="n">
-        <v>0.04306318238377571</v>
+        <v>0.1166437789797783</v>
       </c>
       <c r="CX11" t="n">
-        <v>0.04722166806459427</v>
+        <v>0.01504073664546013</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.04496162384748459</v>
+        <v>0.05774367228150368</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.01198110263794661</v>
+        <v>0.07068145275115967</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.04427884146571159</v>
+        <v>0.008370885625481606</v>
       </c>
       <c r="DB11" t="n">
-        <v>0.02203365787863731</v>
+        <v>0.003232825547456741</v>
       </c>
       <c r="DC11" t="n">
-        <v>0.04480616748332977</v>
+        <v>0.02233063988387585</v>
       </c>
       <c r="DD11" t="n">
-        <v>0.02028554305434227</v>
+        <v>0.02533400803804398</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.01473829988390207</v>
+        <v>0.07169526070356369</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.00376679771579802</v>
+        <v>0.1729951500892639</v>
       </c>
       <c r="DG11" t="n">
-        <v>0.01454881485551596</v>
+        <v>0.03095537424087524</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.139159694314003</v>
+        <v>0.07381770014762878</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.04893504083156586</v>
+        <v>0.1684544384479523</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.01438118238002062</v>
+        <v>0.2779187262058258</v>
       </c>
       <c r="DK11" t="n">
-        <v>0.0399501621723175</v>
+        <v>0.01528934016823769</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.04986762255430222</v>
+        <v>0.0136464461684227</v>
       </c>
       <c r="DM11" t="n">
-        <v>0.04605065658688545</v>
+        <v>0.207629382610321</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.001652928767725825</v>
+        <v>0.1437345743179321</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.01537307910621166</v>
+        <v>0.04302166402339935</v>
       </c>
       <c r="DP11" t="n">
-        <v>0.02994381822645664</v>
+        <v>0.03631318733096123</v>
       </c>
       <c r="DQ11" t="n">
-        <v>0.01157646812498569</v>
+        <v>0.1107862517237663</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.0004095358308404684</v>
+        <v>0.02899738773703575</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.01426715962588787</v>
+        <v>0.09656883776187897</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.0167982280254364</v>
+        <v>0.02517343312501907</v>
       </c>
       <c r="DU11" t="n">
-        <v>0.003005178179591894</v>
+        <v>0.06191630661487579</v>
       </c>
       <c r="DV11" t="n">
-        <v>0.04330861568450928</v>
+        <v>0.03065462410449982</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.006123499013483524</v>
+        <v>0.1013215258717537</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.01619100943207741</v>
+        <v>0.01733753643929958</v>
       </c>
       <c r="DY11" t="n">
-        <v>0.05544985830783844</v>
+        <v>0.03653029352426529</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0.0180203877389431</v>
+        <v>0.1156765520572662</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.02220473811030388</v>
+        <v>0.06198786944150925</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.0463998019695282</v>
+        <v>0.04362696409225464</v>
       </c>
       <c r="EC11" t="n">
-        <v>0.00916533637791872</v>
+        <v>0.06250618398189545</v>
       </c>
       <c r="ED11" t="n">
-        <v>0.006637102924287319</v>
+        <v>0.1419788897037506</v>
       </c>
       <c r="EE11" t="n">
-        <v>0.01313110440969467</v>
+        <v>0.1839879155158997</v>
       </c>
       <c r="EF11" t="n">
-        <v>0.01388421468436718</v>
+        <v>0.01373606082051992</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.04581531509757042</v>
+        <v>0.04332592710852623</v>
       </c>
       <c r="EH11" t="n">
-        <v>0.03965583816170692</v>
+        <v>0.008600553497672081</v>
       </c>
       <c r="EI11" t="n">
-        <v>0.005510028917342424</v>
+        <v>0.1632578372955322</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.01256384141743183</v>
+        <v>0.06480363756418228</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.03245771676301956</v>
+        <v>0.09093183279037476</v>
       </c>
       <c r="EL11" t="n">
-        <v>0.02697017602622509</v>
+        <v>0.04568910971283913</v>
       </c>
       <c r="EM11" t="n">
-        <v>0.0166510958224535</v>
+        <v>0.0606771782040596</v>
       </c>
       <c r="EN11" t="n">
-        <v>0.01167966425418854</v>
+        <v>0.1013529449701309</v>
       </c>
       <c r="EO11" t="n">
-        <v>0.003577079623937607</v>
+        <v>0.02868199162185192</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.01470254827290773</v>
+        <v>0.005415701307356358</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0.04348230361938477</v>
+        <v>0.02978835813701153</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.04647672921419144</v>
+        <v>0.01447990536689758</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.00770633528009057</v>
+        <v>0.1585075855255127</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.05053712800145149</v>
+        <v>0.2298738956451416</v>
       </c>
       <c r="EU11" t="n">
-        <v>0.0536159873008728</v>
+        <v>0.06917471438646317</v>
       </c>
       <c r="EV11" t="n">
-        <v>0.1009166538715363</v>
+        <v>0.04428471997380257</v>
       </c>
       <c r="EW11" t="n">
-        <v>0.001641750801354647</v>
+        <v>0.001376904547214508</v>
       </c>
       <c r="EX11" t="n">
-        <v>0.0005329269915819168</v>
+        <v>0.0267176441848278</v>
       </c>
       <c r="EY11" t="n">
-        <v>0.03226180374622345</v>
+        <v>0.1576728671789169</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0.03941985592246056</v>
+        <v>0.01632022112607956</v>
       </c>
       <c r="FA11" t="n">
-        <v>0.04227092489600182</v>
+        <v>0.0798555314540863</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.01543196849524975</v>
+        <v>0.07844790071249008</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.03322456032037735</v>
+        <v>0.00862782821059227</v>
       </c>
       <c r="FD11" t="n">
-        <v>0.04280689358711243</v>
+        <v>0.05293260514736176</v>
       </c>
       <c r="FE11" t="n">
-        <v>0.03251688927412033</v>
+        <v>0.001056307926774025</v>
       </c>
       <c r="FF11" t="n">
-        <v>0.0316695049405098</v>
+        <v>0.02294464968144894</v>
       </c>
       <c r="FG11" t="n">
-        <v>0.01775004714727402</v>
+        <v>0.01211496070027351</v>
       </c>
       <c r="FH11" t="n">
-        <v>0.04072069749236107</v>
+        <v>0.2096974104642868</v>
       </c>
       <c r="FI11" t="n">
-        <v>0.04449585825204849</v>
+        <v>0.07470190525054932</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.06314310431480408</v>
+        <v>0.02756563015282154</v>
       </c>
       <c r="FK11" t="n">
-        <v>0.001108601340092719</v>
+        <v>0.07021990418434143</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.01315868366509676</v>
+        <v>0.06332069635391235</v>
       </c>
       <c r="FM11" t="n">
-        <v>0.002545872703194618</v>
+        <v>0.01269543170928955</v>
       </c>
       <c r="FN11" t="n">
-        <v>0.01887943595647812</v>
+        <v>0.05082476884126663</v>
       </c>
       <c r="FO11" t="n">
-        <v>0.01874993555247784</v>
+        <v>0.1871254146099091</v>
       </c>
       <c r="FP11" t="n">
-        <v>0.01999128982424736</v>
+        <v>0.1286299228668213</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.04824937134981155</v>
+        <v>0.0190303847193718</v>
       </c>
       <c r="FR11" t="n">
-        <v>0.06154897436499596</v>
+        <v>0.1466452032327652</v>
       </c>
       <c r="FS11" t="n">
-        <v>0.06599975377321243</v>
+        <v>0.3567709624767303</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.05312375724315643</v>
+        <v>0.06154053658246994</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.06148622930049896</v>
+        <v>0.1632431149482727</v>
       </c>
       <c r="FV11" t="n">
-        <v>0.07512025535106659</v>
+        <v>0.2009140253067017</v>
       </c>
       <c r="FW11" t="n">
-        <v>0.0098979277536273</v>
+        <v>0.07358179986476898</v>
       </c>
       <c r="FX11" t="n">
-        <v>0.002903033746406436</v>
+        <v>0.03002266772091389</v>
       </c>
       <c r="FY11" t="n">
-        <v>0.05924385040998459</v>
+        <v>0.04968028143048286</v>
       </c>
       <c r="FZ11" t="n">
-        <v>0.02904324606060982</v>
+        <v>0.04495507106184959</v>
       </c>
       <c r="GA11" t="n">
-        <v>0.02180701680481434</v>
+        <v>0.04530709981918335</v>
       </c>
       <c r="GB11" t="n">
-        <v>0.02833087742328644</v>
+        <v>0.02406281977891922</v>
       </c>
       <c r="GC11" t="n">
-        <v>0.01058767177164555</v>
+        <v>0.06013622134923935</v>
       </c>
       <c r="GD11" t="n">
-        <v>0.004680175334215164</v>
+        <v>0.0422908179461956</v>
       </c>
       <c r="GE11" t="n">
-        <v>0.1582753360271454</v>
+        <v>0.03726763278245926</v>
       </c>
       <c r="GF11" t="n">
-        <v>0.00745137594640255</v>
+        <v>0.1464591473340988</v>
       </c>
       <c r="GG11" t="n">
-        <v>0.006576872430741787</v>
+        <v>0.1088436096906662</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.004343653097748756</v>
+        <v>0.2378592193126678</v>
       </c>
       <c r="B12" t="n">
-        <v>0.3288232386112213</v>
+        <v>0.4489476084709167</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0005675407592207193</v>
+        <v>0.2218988835811615</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1357096433639526</v>
+        <v>0.08426662534475327</v>
       </c>
       <c r="E12" t="n">
-        <v>0.06591553241014481</v>
+        <v>0.1148152649402618</v>
       </c>
       <c r="F12" t="n">
-        <v>0.06433519721031189</v>
+        <v>0.05157080292701721</v>
       </c>
       <c r="G12" t="n">
-        <v>0.02953149750828743</v>
+        <v>0.1160151958465576</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0436285138130188</v>
+        <v>0.004629239439964294</v>
       </c>
       <c r="I12" t="n">
-        <v>0.05433078482747078</v>
+        <v>0.1706946641206741</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0499015636742115</v>
+        <v>0.2678650915622711</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2556174397468567</v>
+        <v>0.522121250629425</v>
       </c>
       <c r="L12" t="n">
-        <v>0.002494726562872529</v>
+        <v>0.3442176282405853</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1082673743367195</v>
+        <v>0.07104036211967468</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1075705513358116</v>
+        <v>0.1015012115240097</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1190094128251076</v>
+        <v>0.0334966629743576</v>
       </c>
       <c r="P12" t="n">
-        <v>0.02050942927598953</v>
+        <v>0.08263500034809113</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.02078153379261494</v>
+        <v>0.003649182617664337</v>
       </c>
       <c r="R12" t="n">
-        <v>0.03011953085660934</v>
+        <v>0.4075507521629333</v>
       </c>
       <c r="S12" t="n">
-        <v>0.02758365496993065</v>
+        <v>0.03318041190505028</v>
       </c>
       <c r="T12" t="n">
-        <v>0.05214548110961914</v>
+        <v>0.09623868763446808</v>
       </c>
       <c r="U12" t="n">
-        <v>0.02631457708775997</v>
+        <v>0.1608235090970993</v>
       </c>
       <c r="V12" t="n">
-        <v>0.04246247559785843</v>
+        <v>0.03892159461975098</v>
       </c>
       <c r="W12" t="n">
-        <v>0.049185611307621</v>
+        <v>0.2215030789375305</v>
       </c>
       <c r="X12" t="n">
-        <v>0.009602803736925125</v>
+        <v>0.1239749640226364</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.03123973309993744</v>
+        <v>0.05141889303922653</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.06587529927492142</v>
+        <v>0.02547519281506538</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.05297980830073357</v>
+        <v>0.001599455019459128</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.00203000009059906</v>
+        <v>0.08644069731235504</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.03079812228679657</v>
+        <v>0.06281944364309311</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.008683055639266968</v>
+        <v>0.04721766337752342</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.008597569540143013</v>
+        <v>0.119007870554924</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.01853474415838718</v>
+        <v>0.2531377077102661</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.06389579176902771</v>
+        <v>0.02517680078744888</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.01335345115512609</v>
+        <v>0.03601675480604172</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.004833799321204424</v>
+        <v>0.108684629201889</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.007783558685332537</v>
+        <v>0.03614200279116631</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.04390652105212212</v>
+        <v>0.09248731285333633</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.06953492015600204</v>
+        <v>0.0444677509367466</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.009772438555955887</v>
+        <v>0.1449795663356781</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.01771024614572525</v>
+        <v>0.1379022300243378</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.01570744812488556</v>
+        <v>0.3606109619140625</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.02956656739115715</v>
+        <v>0.1028853058815002</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.01935957558453083</v>
+        <v>0.02867063693702221</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.00339619698934257</v>
+        <v>0.1355873048305511</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.04441668465733528</v>
+        <v>0.01735533028841019</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.03786163777112961</v>
+        <v>0.1614663153886795</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.2387289255857468</v>
+        <v>0.08256536722183228</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.01343224570155144</v>
+        <v>0.2237733006477356</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.05087809264659882</v>
+        <v>0.08027556538581848</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.00715850293636322</v>
+        <v>0.3624058067798615</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.05735098570585251</v>
+        <v>0.1237584426999092</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.04273519665002823</v>
+        <v>0.005115331150591373</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.01384117640554905</v>
+        <v>0.09935063123703003</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.04062075912952423</v>
+        <v>0.1003760918974876</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.006545577198266983</v>
+        <v>0.09346118569374084</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.03449260070919991</v>
+        <v>0.4070233404636383</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.05526180192828178</v>
+        <v>0.07314897328615189</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.01636851951479912</v>
+        <v>0.01128396019339561</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.06304516643285751</v>
+        <v>0.7339328527450562</v>
       </c>
       <c r="BH12" t="n">
-        <v>0.01604320853948593</v>
+        <v>0.1616143882274628</v>
       </c>
       <c r="BI12" t="n">
-        <v>0.03929434344172478</v>
+        <v>0.1103645116090775</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.02629866451025009</v>
+        <v>0.1209736317396164</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.03190615028142929</v>
+        <v>0.04823324829339981</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.0125996358692646</v>
+        <v>0.03904865682125092</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.03133486956357956</v>
+        <v>0.1524094939231873</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.01169149205088615</v>
+        <v>0.04948104918003082</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.007039159536361694</v>
+        <v>0.02531309612095356</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.03652789443731308</v>
+        <v>0.3031904995441437</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.0386146754026413</v>
+        <v>0.01067780610173941</v>
       </c>
       <c r="BR12" t="n">
-        <v>0.003822286613285542</v>
+        <v>0.001220971113070846</v>
       </c>
       <c r="BS12" t="n">
-        <v>0.003474972443655133</v>
+        <v>0.1001775488257408</v>
       </c>
       <c r="BT12" t="n">
-        <v>0.02891368791460991</v>
+        <v>0.03460735455155373</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.03021667525172234</v>
+        <v>0.1549639850854874</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.1386108100414276</v>
+        <v>0.01717806793749332</v>
       </c>
       <c r="BW12" t="n">
-        <v>0.039827611297369</v>
+        <v>0.1370454430580139</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.05352893099188805</v>
+        <v>0.04707599431276321</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.03186579048633575</v>
+        <v>0.1043921709060669</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.02878167107701302</v>
+        <v>0.2137013971805573</v>
       </c>
       <c r="CA12" t="n">
-        <v>0.01109728496521711</v>
+        <v>0.1000595390796661</v>
       </c>
       <c r="CB12" t="n">
-        <v>0.0276767835021019</v>
+        <v>0.05761251598596573</v>
       </c>
       <c r="CC12" t="n">
-        <v>0.04869101196527481</v>
+        <v>0.102119654417038</v>
       </c>
       <c r="CD12" t="n">
-        <v>0.0001145480200648308</v>
+        <v>0.07898477464914322</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.05120637640357018</v>
+        <v>0.06463693827390671</v>
       </c>
       <c r="CF12" t="n">
-        <v>0.03199132531881332</v>
+        <v>0.003607164602726698</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.01828872412443161</v>
+        <v>0.01586352288722992</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.002598873805254698</v>
+        <v>0.02281240373849869</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.008067531511187553</v>
+        <v>0.05429944396018982</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0.01025413535535336</v>
+        <v>0.01165270991623402</v>
       </c>
       <c r="CK12" t="n">
-        <v>0.01315568387508392</v>
+        <v>0.02962593361735344</v>
       </c>
       <c r="CL12" t="n">
-        <v>0.02148346789181232</v>
+        <v>0.05222967267036438</v>
       </c>
       <c r="CM12" t="n">
-        <v>0.0739281177520752</v>
+        <v>0.0595787838101387</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.01818746700882912</v>
+        <v>0.163011372089386</v>
       </c>
       <c r="CO12" t="n">
-        <v>0.00337483617477119</v>
+        <v>0.1410888135433197</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.03363391011953354</v>
+        <v>0.08397702872753143</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.03628049790859222</v>
+        <v>0.47516268491745</v>
       </c>
       <c r="CR12" t="n">
-        <v>0.0171019434928894</v>
+        <v>0.2727925479412079</v>
       </c>
       <c r="CS12" t="n">
-        <v>0.0725395530462265</v>
+        <v>0.01103545725345612</v>
       </c>
       <c r="CT12" t="n">
-        <v>0.0398380383849144</v>
+        <v>0.03919129073619843</v>
       </c>
       <c r="CU12" t="n">
-        <v>0.03276688605546951</v>
+        <v>0.08240610361099243</v>
       </c>
       <c r="CV12" t="n">
-        <v>0.002102598547935486</v>
+        <v>0.07375739514827728</v>
       </c>
       <c r="CW12" t="n">
-        <v>0.05050605908036232</v>
+        <v>0.07640862464904785</v>
       </c>
       <c r="CX12" t="n">
-        <v>0.03442032635211945</v>
+        <v>0.02198579721152782</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.02999543584883213</v>
+        <v>0.02469752728939056</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.004941452760249376</v>
+        <v>0.01733541861176491</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.01540462579578161</v>
+        <v>0.03292347118258476</v>
       </c>
       <c r="DB12" t="n">
-        <v>0.01415688265115023</v>
+        <v>0.01312680449336767</v>
       </c>
       <c r="DC12" t="n">
-        <v>0.02208015695214272</v>
+        <v>0.03151043131947517</v>
       </c>
       <c r="DD12" t="n">
-        <v>0.01695789210498333</v>
+        <v>0.03571866452693939</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.02266259118914604</v>
+        <v>0.09148050099611282</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.04434774443507195</v>
+        <v>0.07418329268693924</v>
       </c>
       <c r="DG12" t="n">
-        <v>0.005563473328948021</v>
+        <v>0.0165630541741848</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.1433678269386292</v>
+        <v>0.04893021658062935</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.02253533899784088</v>
+        <v>0.06402436643838882</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.008839510381222e-05</v>
+        <v>0.1754732877016068</v>
       </c>
       <c r="DK12" t="n">
-        <v>0.03334736451506615</v>
+        <v>0.02840570732951164</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.01432024408131838</v>
+        <v>0.1135186925530434</v>
       </c>
       <c r="DM12" t="n">
-        <v>0.01109485793858767</v>
+        <v>0.2940015196800232</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.009692491963505745</v>
+        <v>0.01275248453021049</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.02286003530025482</v>
+        <v>0.1436571031808853</v>
       </c>
       <c r="DP12" t="n">
-        <v>0.01274090632796288</v>
+        <v>0.06817939877510071</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.01924460940063</v>
+        <v>0.08182932436466217</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.01944223046302795</v>
+        <v>0.05600257217884064</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.002193593420088291</v>
+        <v>0.1457141041755676</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.01807059906423092</v>
+        <v>0.07005935907363892</v>
       </c>
       <c r="DU12" t="n">
-        <v>0.004149137996137142</v>
+        <v>0.06799116730690002</v>
       </c>
       <c r="DV12" t="n">
-        <v>0.05395515263080597</v>
+        <v>0.1074276119470596</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.003477322403341532</v>
+        <v>0.01165396347641945</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.03847698867321014</v>
+        <v>0.04386232048273087</v>
       </c>
       <c r="DY12" t="n">
-        <v>0.05171637982130051</v>
+        <v>0.03997999429702759</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.01703405566513538</v>
+        <v>0.09021284431219101</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.02188134007155895</v>
+        <v>0.03752970695495605</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.00684910686686635</v>
+        <v>0.128846749663353</v>
       </c>
       <c r="EC12" t="n">
-        <v>0.007441733498126268</v>
+        <v>0.057857695966959</v>
       </c>
       <c r="ED12" t="n">
-        <v>0.004634655080735683</v>
+        <v>0.225306361913681</v>
       </c>
       <c r="EE12" t="n">
-        <v>0.006372049916535616</v>
+        <v>0.1342510581016541</v>
       </c>
       <c r="EF12" t="n">
-        <v>0.02871881052851677</v>
+        <v>0.09824618697166443</v>
       </c>
       <c r="EG12" t="n">
-        <v>0.02282047644257545</v>
+        <v>0.01496649347245693</v>
       </c>
       <c r="EH12" t="n">
-        <v>0.02104905992746353</v>
+        <v>0.04164186120033264</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.01298452541232109</v>
+        <v>0.03635971248149872</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.006511096376925707</v>
+        <v>0.03910784795880318</v>
       </c>
       <c r="EK12" t="n">
-        <v>0.004390910267829895</v>
+        <v>0.03424222022294998</v>
       </c>
       <c r="EL12" t="n">
-        <v>0.01642939820885658</v>
+        <v>0.001972864381968975</v>
       </c>
       <c r="EM12" t="n">
-        <v>0.004811582155525684</v>
+        <v>0.01528837531805038</v>
       </c>
       <c r="EN12" t="n">
-        <v>0.0004951924784108996</v>
+        <v>0.1574200391769409</v>
       </c>
       <c r="EO12" t="n">
-        <v>0.01329190284013748</v>
+        <v>0.0713871568441391</v>
       </c>
       <c r="EP12" t="n">
-        <v>0.02404818311333656</v>
+        <v>0.02413970977067947</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0.04519650712609291</v>
+        <v>0.0734318420290947</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.02292722091078758</v>
+        <v>0.09709969162940979</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.0171913206577301</v>
+        <v>0.07532541453838348</v>
       </c>
       <c r="ET12" t="n">
-        <v>0.04655447602272034</v>
+        <v>0.2371740639209747</v>
       </c>
       <c r="EU12" t="n">
-        <v>0.04840492457151413</v>
+        <v>0.03719017654657364</v>
       </c>
       <c r="EV12" t="n">
-        <v>0.07268539816141129</v>
+        <v>0.05155611410737038</v>
       </c>
       <c r="EW12" t="n">
-        <v>0.009006023406982422</v>
+        <v>0.04378911480307579</v>
       </c>
       <c r="EX12" t="n">
-        <v>0.003267453517764807</v>
+        <v>0.07686350494623184</v>
       </c>
       <c r="EY12" t="n">
-        <v>0.04746159538626671</v>
+        <v>0.1063463687896729</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0.02610531635582447</v>
+        <v>0.02101656794548035</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.02288868464529514</v>
+        <v>0.01776744984090328</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.00915123987942934</v>
+        <v>0.07155969738960266</v>
       </c>
       <c r="FC12" t="n">
-        <v>0.0120310140773654</v>
+        <v>0.02121154591441154</v>
       </c>
       <c r="FD12" t="n">
-        <v>0.02441995777189732</v>
+        <v>0.005594722460955381</v>
       </c>
       <c r="FE12" t="n">
-        <v>0.01157455425709486</v>
+        <v>0.008923102170228958</v>
       </c>
       <c r="FF12" t="n">
-        <v>0.02935818396508694</v>
+        <v>0.0838816910982132</v>
       </c>
       <c r="FG12" t="n">
-        <v>0.006177033763378859</v>
+        <v>0.01838257908821106</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.01167193986475468</v>
+        <v>0.0506051778793335</v>
       </c>
       <c r="FI12" t="n">
-        <v>0.04071632772684097</v>
+        <v>0.07000809162855148</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.02035030722618103</v>
+        <v>0.04012864828109741</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.003025831654667854</v>
+        <v>0.1031378284096718</v>
       </c>
       <c r="FL12" t="n">
-        <v>0.01297757215797901</v>
+        <v>0.1359008550643921</v>
       </c>
       <c r="FM12" t="n">
-        <v>0.0004435675218701363</v>
+        <v>0.05364225059747696</v>
       </c>
       <c r="FN12" t="n">
-        <v>0.02240563742816448</v>
+        <v>0.05067555233836174</v>
       </c>
       <c r="FO12" t="n">
-        <v>0.00074491195846349</v>
+        <v>0.1940257847309113</v>
       </c>
       <c r="FP12" t="n">
-        <v>0.02762640826404095</v>
+        <v>0.07361491024494171</v>
       </c>
       <c r="FQ12" t="n">
-        <v>0.05464087426662445</v>
+        <v>0.01047002524137497</v>
       </c>
       <c r="FR12" t="n">
-        <v>0.03351402655243874</v>
+        <v>0.1392221003770828</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.03083214163780212</v>
+        <v>0.1912183165550232</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.01474238652735949</v>
+        <v>0.06574538350105286</v>
       </c>
       <c r="FU12" t="n">
-        <v>0.006811202503740788</v>
+        <v>0.05135857313871384</v>
       </c>
       <c r="FV12" t="n">
-        <v>0.05748008191585541</v>
+        <v>0.0387105904519558</v>
       </c>
       <c r="FW12" t="n">
-        <v>0.003752750344574451</v>
+        <v>0.02446547895669937</v>
       </c>
       <c r="FX12" t="n">
-        <v>0.002612411975860596</v>
+        <v>0.02384099736809731</v>
       </c>
       <c r="FY12" t="n">
-        <v>0.05995987355709076</v>
+        <v>0.03418219834566116</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.01324838865548372</v>
+        <v>0.0623297244310379</v>
       </c>
       <c r="GA12" t="n">
-        <v>0.02709169499576092</v>
+        <v>0.1259754002094269</v>
       </c>
       <c r="GB12" t="n">
-        <v>0.01170891150832176</v>
+        <v>0.0536387600004673</v>
       </c>
       <c r="GC12" t="n">
-        <v>0.04593956843018532</v>
+        <v>0.01219967007637024</v>
       </c>
       <c r="GD12" t="n">
-        <v>0.04680350050330162</v>
+        <v>0.2710175216197968</v>
       </c>
       <c r="GE12" t="n">
-        <v>0.1511508226394653</v>
+        <v>0.04911288991570473</v>
       </c>
       <c r="GF12" t="n">
-        <v>0.01315079070627689</v>
+        <v>0.05450476706027985</v>
       </c>
       <c r="GG12" t="n">
-        <v>0.005504202097654343</v>
+        <v>0.1934637725353241</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.0001631181658012792</v>
+        <v>0.001170914620161057</v>
       </c>
       <c r="B13" t="n">
-        <v>0.001889335573650897</v>
+        <v>0.03537476062774658</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0001668090262683108</v>
+        <v>0.01628318428993225</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0006202576332725585</v>
+        <v>0.009156850166618824</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0005062422133050859</v>
+        <v>0.005885117221623659</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0008933903882279992</v>
+        <v>0.02683816105127335</v>
       </c>
       <c r="G13" t="n">
-        <v>2.122368096024729e-05</v>
+        <v>0.00834188237786293</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0005238043959252536</v>
+        <v>0.007337002549320459</v>
       </c>
       <c r="I13" t="n">
-        <v>3.937230758310761e-06</v>
+        <v>0.01437326427549124</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0003159629413858056</v>
+        <v>0.004702054429799318</v>
       </c>
       <c r="K13" t="n">
-        <v>0.001763940206728876</v>
+        <v>0.0324048176407814</v>
       </c>
       <c r="L13" t="n">
-        <v>2.487436540832277e-05</v>
+        <v>0.02165296114981174</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0003787704044952989</v>
+        <v>0.02529784291982651</v>
       </c>
       <c r="N13" t="n">
-        <v>6.062746251700446e-05</v>
+        <v>0.005261767655611038</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0009548652451485395</v>
+        <v>0.03220780938863754</v>
       </c>
       <c r="P13" t="n">
-        <v>4.206172889098525e-06</v>
+        <v>0.008857348002493382</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.000162035139510408</v>
+        <v>0.001031881663948298</v>
       </c>
       <c r="R13" t="n">
-        <v>6.340137770166621e-05</v>
+        <v>0.01869688369333744</v>
       </c>
       <c r="S13" t="n">
-        <v>5.778417107649148e-05</v>
+        <v>0.004868017975240946</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0001470395072828978</v>
+        <v>0.008857017382979393</v>
       </c>
       <c r="U13" t="n">
-        <v>7.867005479056388e-05</v>
+        <v>0.001924076583236456</v>
       </c>
       <c r="V13" t="n">
-        <v>0.0002334041200811043</v>
+        <v>0.002391816349700093</v>
       </c>
       <c r="W13" t="n">
-        <v>0.0001604351418791339</v>
+        <v>0.00291938753798604</v>
       </c>
       <c r="X13" t="n">
-        <v>2.668241540959571e-05</v>
+        <v>0.001088885706849396</v>
       </c>
       <c r="Y13" t="n">
-        <v>4.063694359501824e-05</v>
+        <v>0.006426462437957525</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.0001636910455999896</v>
+        <v>0.002282130066305399</v>
       </c>
       <c r="AA13" t="n">
-        <v>5.545915337279439e-05</v>
+        <v>0.004282251931726933</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.59093358181417e-05</v>
+        <v>0.003937005996704102</v>
       </c>
       <c r="AC13" t="n">
-        <v>6.759794814570341e-06</v>
+        <v>0.001434599864296615</v>
       </c>
       <c r="AD13" t="n">
-        <v>3.052860483876429e-05</v>
+        <v>0.008841199800372124</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.0001341817405773327</v>
+        <v>0.009676471352577209</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.0001374992716591805</v>
+        <v>0.008799603208899498</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.170685183955356e-05</v>
+        <v>0.01572690159082413</v>
       </c>
       <c r="AH13" t="n">
-        <v>4.709996210294776e-05</v>
+        <v>0.002816773019731045</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.0001083903480321169</v>
+        <v>0.02490947395563126</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.0001226260210387409</v>
+        <v>0.001037344569340348</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.000315203593345359</v>
+        <v>0.0036312744487077</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.0001255485694855452</v>
+        <v>0.007059879135340452</v>
       </c>
       <c r="AM13" t="n">
-        <v>2.97851838695351e-05</v>
+        <v>6.447546184062958e-06</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.8976119463332e-05</v>
+        <v>0.003232626942917705</v>
       </c>
       <c r="AO13" t="n">
-        <v>5.651088213198818e-05</v>
+        <v>0.004336984362453222</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.0002604001783765852</v>
+        <v>0.003574779722839594</v>
       </c>
       <c r="AQ13" t="n">
-        <v>5.439535016193986e-05</v>
+        <v>0.0004007230745628476</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.0001606038713362068</v>
+        <v>0.008831175044178963</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.0002110010100295767</v>
+        <v>0.003208555281162262</v>
       </c>
       <c r="AT13" t="n">
-        <v>4.611798067344353e-05</v>
+        <v>0.004545091185718775</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.001012469059787691</v>
+        <v>0.03294645994901657</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.0002355398901272565</v>
+        <v>0.01117176283150911</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.383124178275466e-06</v>
+        <v>0.009016102179884911</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.000290874857455492</v>
+        <v>0.01689797453582287</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.0004278796259313822</v>
+        <v>0.02356120571494102</v>
       </c>
       <c r="AZ13" t="n">
-        <v>7.924743840703741e-05</v>
+        <v>0.002055190969258547</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.0002002502878895029</v>
+        <v>0.009953182190656662</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.000166278550750576</v>
+        <v>0.003395111300051212</v>
       </c>
       <c r="BC13" t="n">
-        <v>3.376138920430094e-05</v>
+        <v>0.005298375152051449</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.000406842038501054</v>
+        <v>0.005488956347107887</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.0004848832322750241</v>
+        <v>0.0102805569767952</v>
       </c>
       <c r="BF13" t="n">
-        <v>7.934165478218347e-05</v>
+        <v>0.003270747140049934</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.0001632343046367168</v>
+        <v>0.01290745660662651</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.0001118674990721047</v>
+        <v>0.004394046496599913</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.0001115993363782763</v>
+        <v>0.008007928729057312</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.0001129989686887711</v>
+        <v>0.000158480484969914</v>
       </c>
       <c r="BK13" t="n">
-        <v>7.634709618287161e-05</v>
+        <v>0.00931285135447979</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.0001267630723305047</v>
+        <v>0.000703361292835325</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.0002111915091518313</v>
+        <v>0.0103660486638546</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.000210797501495108</v>
+        <v>0.006786804646253586</v>
       </c>
       <c r="BO13" t="n">
-        <v>7.818379526725039e-05</v>
+        <v>0.002731929300352931</v>
       </c>
       <c r="BP13" t="n">
-        <v>7.37597729312256e-05</v>
+        <v>0.003509191796183586</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.603511115419678e-05</v>
+        <v>0.006545693147927523</v>
       </c>
       <c r="BR13" t="n">
-        <v>4.865483788307756e-05</v>
+        <v>0.005328189115971327</v>
       </c>
       <c r="BS13" t="n">
-        <v>7.601972902193666e-05</v>
+        <v>0.00101827026810497</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.0002356663899263367</v>
+        <v>0.003091130405664444</v>
       </c>
       <c r="BU13" t="n">
-        <v>3.243096216465347e-05</v>
+        <v>0.001995916711166501</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.0006328243762254715</v>
+        <v>0.02317385748028755</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.0001935378677444533</v>
+        <v>0.002974882256239653</v>
       </c>
       <c r="BX13" t="n">
-        <v>3.565770748537034e-05</v>
+        <v>0.00487053208053112</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.0001070861326297745</v>
+        <v>0.002387237967923284</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.0002413707552477717</v>
+        <v>0.009261568076908588</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.260387504473329e-05</v>
+        <v>0.01054249703884125</v>
       </c>
       <c r="CB13" t="n">
-        <v>9.238642815034837e-05</v>
+        <v>0.0006352164782583714</v>
       </c>
       <c r="CC13" t="n">
-        <v>8.944071305450052e-05</v>
+        <v>0.004311577416956425</v>
       </c>
       <c r="CD13" t="n">
-        <v>5.237705772742629e-05</v>
+        <v>0.0004465966485440731</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.0003552263078745455</v>
+        <v>0.01198937185108662</v>
       </c>
       <c r="CF13" t="n">
-        <v>0.0001334794942522421</v>
+        <v>0.005373727530241013</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.000100217257568147</v>
+        <v>0.003378112334758043</v>
       </c>
       <c r="CH13" t="n">
-        <v>8.533026266377419e-05</v>
+        <v>0.0005961578572168946</v>
       </c>
       <c r="CI13" t="n">
-        <v>6.177782779559493e-05</v>
+        <v>0.005380411166697741</v>
       </c>
       <c r="CJ13" t="n">
-        <v>9.604453225620091e-05</v>
+        <v>9.748214506544173e-05</v>
       </c>
       <c r="CK13" t="n">
-        <v>0.0001121832829085179</v>
+        <v>0.001011554268188775</v>
       </c>
       <c r="CL13" t="n">
-        <v>9.568981477059424e-05</v>
+        <v>0.001950723817571998</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.0004060997162014246</v>
+        <v>0.004640004597604275</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.0001427193928975612</v>
+        <v>0.005664209835231304</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.067832999979146e-05</v>
+        <v>0.009152412414550781</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.0002944590232800692</v>
+        <v>0.01309758890420198</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.000269729207502678</v>
+        <v>0.004663063678890467</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.000475928740343079</v>
+        <v>0.00690039386972785</v>
       </c>
       <c r="CS13" t="n">
-        <v>0.0003509453381411731</v>
+        <v>0.005879075266420841</v>
       </c>
       <c r="CT13" t="n">
-        <v>0.0001534642797196284</v>
+        <v>0.0009333047783002257</v>
       </c>
       <c r="CU13" t="n">
-        <v>6.687518180115148e-05</v>
+        <v>0.005705111194401979</v>
       </c>
       <c r="CV13" t="n">
-        <v>4.686772808781825e-05</v>
+        <v>0.002814669394865632</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.0003457935526967049</v>
+        <v>0.009811547584831715</v>
       </c>
       <c r="CX13" t="n">
-        <v>0.0001857899769674987</v>
+        <v>0.007318746298551559</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.0001760130107868463</v>
+        <v>0.00480924267321825</v>
       </c>
       <c r="CZ13" t="n">
-        <v>6.980042235227302e-05</v>
+        <v>0.00125197833403945</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.0001013039582176134</v>
+        <v>0.008281609043478966</v>
       </c>
       <c r="DB13" t="n">
-        <v>7.840368198230863e-05</v>
+        <v>0.001391322119161487</v>
       </c>
       <c r="DC13" t="n">
-        <v>0.0002136842958861962</v>
+        <v>0.001083993120118976</v>
       </c>
       <c r="DD13" t="n">
-        <v>7.674968219362199e-05</v>
+        <v>0.002800433663651347</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.0001854291040217504</v>
+        <v>0.00119382981210947</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.0001358614681521431</v>
+        <v>0.02199529111385345</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.657517714193091e-05</v>
+        <v>0.01390496548265219</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.0005935899680480361</v>
+        <v>0.0004245604213792831</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.0007079532369971275</v>
+        <v>0.005767093505710363</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.0001573245681356639</v>
+        <v>0.01836448907852173</v>
       </c>
       <c r="DK13" t="n">
-        <v>0.0002658727462403476</v>
+        <v>0.00461293151602149</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.0002777804038487375</v>
+        <v>0.0102550620213151</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.0002659239689819515</v>
+        <v>0.002553027821704745</v>
       </c>
       <c r="DN13" t="n">
-        <v>9.680886432761326e-05</v>
+        <v>0.002103353850543499</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.0002035030047409236</v>
+        <v>0.009962008334696293</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.0001132723773480393</v>
+        <v>0.003189150476828218</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.0002021978434640914</v>
+        <v>0.008779753930866718</v>
       </c>
       <c r="DR13" t="n">
-        <v>2.729173320403788e-05</v>
+        <v>0.0007775256526656449</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.0001303450844716281</v>
+        <v>0.005791104398667812</v>
       </c>
       <c r="DT13" t="n">
-        <v>7.313933747354895e-05</v>
+        <v>0.003756608814001083</v>
       </c>
       <c r="DU13" t="n">
-        <v>7.107741839718074e-05</v>
+        <v>0.00907464511692524</v>
       </c>
       <c r="DV13" t="n">
-        <v>0.0001051186700351536</v>
+        <v>0.003691642777994275</v>
       </c>
       <c r="DW13" t="n">
-        <v>1.073316525435075e-05</v>
+        <v>4.444236401468515e-05</v>
       </c>
       <c r="DX13" t="n">
-        <v>8.342448563780636e-05</v>
+        <v>0.007355325855314732</v>
       </c>
       <c r="DY13" t="n">
-        <v>0.000190667255083099</v>
+        <v>0.01434815675020218</v>
       </c>
       <c r="DZ13" t="n">
-        <v>2.904977736761793e-05</v>
+        <v>0.002764844801276922</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.0001145925925811753</v>
+        <v>0.005015077069401741</v>
       </c>
       <c r="EB13" t="n">
-        <v>7.418404857162386e-05</v>
+        <v>0.001806750427931547</v>
       </c>
       <c r="EC13" t="n">
-        <v>0.0001109280274249613</v>
+        <v>0.01077017933130264</v>
       </c>
       <c r="ED13" t="n">
-        <v>4.2526371544227e-05</v>
+        <v>0.005345709621906281</v>
       </c>
       <c r="EE13" t="n">
-        <v>0.0001240818237420171</v>
+        <v>0.01891810074448586</v>
       </c>
       <c r="EF13" t="n">
-        <v>0.0002907193847931921</v>
+        <v>0.000287853617919609</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.000389825931051746</v>
+        <v>0.0002521926071494818</v>
       </c>
       <c r="EH13" t="n">
-        <v>0.0002340539067517966</v>
+        <v>0.0001075002364814281</v>
       </c>
       <c r="EI13" t="n">
-        <v>9.900775330606848e-05</v>
+        <v>0.0109094362705946</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.000102222191344481</v>
+        <v>0.0001466491958126426</v>
       </c>
       <c r="EK13" t="n">
-        <v>8.934622746892273e-05</v>
+        <v>0.001051033497788012</v>
       </c>
       <c r="EL13" t="n">
-        <v>5.137198604643345e-05</v>
+        <v>0.002515410538762808</v>
       </c>
       <c r="EM13" t="n">
-        <v>2.587077506177593e-05</v>
+        <v>0.003547556698322296</v>
       </c>
       <c r="EN13" t="n">
-        <v>3.026127706107218e-05</v>
+        <v>0.009404611773788929</v>
       </c>
       <c r="EO13" t="n">
-        <v>4.475095920497552e-05</v>
+        <v>0.002818424720317125</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.0001681698195170611</v>
+        <v>0.008476853370666504</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0.0001980321103474125</v>
+        <v>0.003107764991000295</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.0001700302673270926</v>
+        <v>0.004350848961621523</v>
       </c>
       <c r="ES13" t="n">
-        <v>9.772025805432349e-05</v>
+        <v>0.007099224720150232</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.0002633362601045519</v>
+        <v>0.009361130185425282</v>
       </c>
       <c r="EU13" t="n">
-        <v>0.0001939963258337229</v>
+        <v>0.00119701842777431</v>
       </c>
       <c r="EV13" t="n">
-        <v>0.0004204581491649151</v>
+        <v>7.978489156812429e-05</v>
       </c>
       <c r="EW13" t="n">
-        <v>7.263838779181242e-05</v>
+        <v>0.001520178746432066</v>
       </c>
       <c r="EX13" t="n">
-        <v>7.955156615935266e-05</v>
+        <v>0.001138753606937826</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.0003238018252886832</v>
+        <v>0.01279108040034771</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0.0001497794582974166</v>
+        <v>0.003964819945394993</v>
       </c>
       <c r="FA13" t="n">
-        <v>9.440102439839393e-05</v>
+        <v>0.005548203829675913</v>
       </c>
       <c r="FB13" t="n">
-        <v>7.331310916924849e-05</v>
+        <v>0.001100726192817092</v>
       </c>
       <c r="FC13" t="n">
-        <v>7.212588388938457e-05</v>
+        <v>0.006619445513933897</v>
       </c>
       <c r="FD13" t="n">
-        <v>0.0001129485535784625</v>
+        <v>0.001433333498425782</v>
       </c>
       <c r="FE13" t="n">
-        <v>0.0001809921959647909</v>
+        <v>0.0008237179717980325</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.000111073961306829</v>
+        <v>0.004400006029754877</v>
       </c>
       <c r="FG13" t="n">
-        <v>0.000102160673122853</v>
+        <v>0.003001033328473568</v>
       </c>
       <c r="FH13" t="n">
-        <v>2.01089051188319e-06</v>
+        <v>0.001852722954936326</v>
       </c>
       <c r="FI13" t="n">
-        <v>0.0002904756984207779</v>
+        <v>0.007819363847374916</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.0002359157806495205</v>
+        <v>0.002588840899989009</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.000143042765557766</v>
+        <v>0.002198558067902923</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.0002023005217779428</v>
+        <v>0.01106899790465832</v>
       </c>
       <c r="FM13" t="n">
-        <v>1.280935612157919e-05</v>
+        <v>0.002302519977092743</v>
       </c>
       <c r="FN13" t="n">
-        <v>0.0001257928815903142</v>
+        <v>0.009683148935437202</v>
       </c>
       <c r="FO13" t="n">
-        <v>9.641298674978316e-05</v>
+        <v>0.02058874815702438</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.0002638536388985813</v>
+        <v>0.001219585537910461</v>
       </c>
       <c r="FQ13" t="n">
-        <v>3.116457264695782e-06</v>
+        <v>0.006315313745290041</v>
       </c>
       <c r="FR13" t="n">
-        <v>0.0003567537933122367</v>
+        <v>0.003256276715546846</v>
       </c>
       <c r="FS13" t="n">
-        <v>1.024649100145325e-05</v>
+        <v>0.003777916310355067</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.0002086150052491575</v>
+        <v>0.006203638855367899</v>
       </c>
       <c r="FU13" t="n">
-        <v>9.27250730455853e-05</v>
+        <v>0.00268095824867487</v>
       </c>
       <c r="FV13" t="n">
-        <v>8.756144234212115e-05</v>
+        <v>0.002905052620917559</v>
       </c>
       <c r="FW13" t="n">
-        <v>7.449685654137284e-06</v>
+        <v>0.02529685199260712</v>
       </c>
       <c r="FX13" t="n">
-        <v>3.51199705619365e-05</v>
+        <v>0.003618353512138128</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.0003085836942773312</v>
+        <v>0.002173455897718668</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.0001325631310464814</v>
+        <v>0.0031074492726475</v>
       </c>
       <c r="GA13" t="n">
-        <v>0.0001932467421283945</v>
+        <v>0.01654097065329552</v>
       </c>
       <c r="GB13" t="n">
-        <v>2.301100539625622e-05</v>
+        <v>0.002092641312628984</v>
       </c>
       <c r="GC13" t="n">
-        <v>2.485270670149475e-06</v>
+        <v>0.01566447876393795</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.00021666671091225</v>
+        <v>0.008371374569833279</v>
       </c>
       <c r="GE13" t="n">
-        <v>0.0004234141670167446</v>
+        <v>0.006406196858733892</v>
       </c>
       <c r="GF13" t="n">
-        <v>7.103556708898395e-05</v>
+        <v>0.003060371382161975</v>
       </c>
       <c r="GG13" t="n">
-        <v>0.0002216167631559074</v>
+        <v>0.001645276322960854</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>8.117115066852421e-05</v>
+        <v>2.275499233483913e-10</v>
       </c>
       <c r="B14" t="n">
-        <v>0.006788062397390604</v>
+        <v>8.32563462616065e-10</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0005202685133554041</v>
+        <v>2.679777511005454e-10</v>
       </c>
       <c r="D14" t="n">
-        <v>0.001672831480391324</v>
+        <v>3.573983886617782e-10</v>
       </c>
       <c r="E14" t="n">
-        <v>0.002247411059215665</v>
+        <v>1.456099268937194e-10</v>
       </c>
       <c r="F14" t="n">
-        <v>0.001343720708973706</v>
+        <v>7.68738739331809e-10</v>
       </c>
       <c r="G14" t="n">
-        <v>6.129976827651262e-05</v>
+        <v>2.376693286620934e-11</v>
       </c>
       <c r="H14" t="n">
-        <v>0.001024784753099084</v>
+        <v>4.83042050802851e-10</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0001426123344572261</v>
+        <v>4.771736339392874e-10</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0003562650235835463</v>
+        <v>2.95750757217661e-10</v>
       </c>
       <c r="K14" t="n">
-        <v>0.005851478781551123</v>
+        <v>9.274496726163761e-10</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0003411334182601422</v>
+        <v>2.601952542313768e-10</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0008274443680420518</v>
+        <v>2.804848020510065e-10</v>
       </c>
       <c r="N14" t="n">
-        <v>0.001412294339388609</v>
+        <v>1.626556389577871e-10</v>
       </c>
       <c r="O14" t="n">
-        <v>0.001339037087745965</v>
+        <v>7.346084851533874e-10</v>
       </c>
       <c r="P14" t="n">
-        <v>8.717653690837324e-05</v>
+        <v>8.29661617185451e-11</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.0001254177186638117</v>
+        <v>5.517855061754062e-10</v>
       </c>
       <c r="R14" t="n">
-        <v>3.894808833138086e-05</v>
+        <v>1.637231183959642e-10</v>
       </c>
       <c r="S14" t="n">
-        <v>9.907063213177025e-05</v>
+        <v>2.108922481092179e-10</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0006956873694434762</v>
+        <v>9.737309569768371e-11</v>
       </c>
       <c r="U14" t="n">
-        <v>0.000210482714464888</v>
+        <v>4.680886928065675e-11</v>
       </c>
       <c r="V14" t="n">
-        <v>0.0007009138353168964</v>
+        <v>7.199570800642263e-11</v>
       </c>
       <c r="W14" t="n">
-        <v>0.001254660077393055</v>
+        <v>1.078273928478701e-11</v>
       </c>
       <c r="X14" t="n">
-        <v>0.0002848459698725492</v>
+        <v>1.22858279105742e-10</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.000166105484822765</v>
+        <v>8.766738029963861e-11</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.001234636292792857</v>
+        <v>1.638128521719295e-10</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.0004192389314994216</v>
+        <v>1.341098343488056e-10</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.000176253350218758</v>
+        <v>2.108119581678558e-11</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.0002696577284950763</v>
+        <v>1.043997527316876e-10</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.0003460457955952734</v>
+        <v>2.681899702317025e-10</v>
       </c>
       <c r="AE14" t="n">
-        <v>7.749452925054356e-05</v>
+        <v>2.058253428804946e-10</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.0003656554326880723</v>
+        <v>6.509703887047635e-11</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.0001504960091551766</v>
+        <v>1.985757114297826e-10</v>
       </c>
       <c r="AH14" t="n">
-        <v>4.311002339818515e-05</v>
+        <v>2.086028572101384e-11</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.0003695377963595092</v>
+        <v>2.136995302937095e-10</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.0005672528059221804</v>
+        <v>3.825037786509e-10</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.0009708751458674669</v>
+        <v>2.712483015976375e-10</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.0006354301003739238</v>
+        <v>3.841477830279771e-11</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.0001166855145129375</v>
+        <v>2.158802858698294e-10</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.0001522952516097575</v>
+        <v>4.348447990576432e-11</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.0006270452286116779</v>
+        <v>4.808639944564597e-11</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.0005243479972705245</v>
+        <v>1.165023199439785e-11</v>
       </c>
       <c r="AQ14" t="n">
-        <v>5.068192695034668e-05</v>
+        <v>2.101755748606937e-11</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.0002443056146148592</v>
+        <v>1.14425986047495e-11</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.0002049975009867921</v>
+        <v>1.632526579198323e-11</v>
       </c>
       <c r="AT14" t="n">
-        <v>6.546442455146462e-05</v>
+        <v>4.433862721420212e-10</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.004267036449164152</v>
+        <v>8.765044245961917e-12</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.0001437949540559202</v>
+        <v>2.448944935729003e-10</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.0002683326310943812</v>
+        <v>1.217472789249996e-10</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.0009986970108002424</v>
+        <v>5.542011294323856e-10</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.000655911338981241</v>
+        <v>2.033095913844818e-10</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.0003605915699154139</v>
+        <v>1.637257274200721e-10</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.0001485201646573842</v>
+        <v>2.470585021285832e-11</v>
       </c>
       <c r="BB14" t="n">
-        <v>0.0001109309232560918</v>
+        <v>1.494325219120185e-10</v>
       </c>
       <c r="BC14" t="n">
-        <v>0.0004173951456323266</v>
+        <v>2.30829452774195e-10</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.001629539066925645</v>
+        <v>5.40292810491394e-10</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.001033445238135755</v>
+        <v>1.392307380498892e-10</v>
       </c>
       <c r="BF14" t="n">
-        <v>0.0002355108445044607</v>
+        <v>2.65448107938937e-10</v>
       </c>
       <c r="BG14" t="n">
-        <v>0.001420099288225174</v>
+        <v>7.025044435060579e-10</v>
       </c>
       <c r="BH14" t="n">
-        <v>0.0006453137029893696</v>
+        <v>2.193368264791218e-10</v>
       </c>
       <c r="BI14" t="n">
-        <v>0.0003724122070707381</v>
+        <v>7.576066163306194e-11</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.0002631075331009924</v>
+        <v>2.193923098747774e-10</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.0001999879750655964</v>
+        <v>5.963665117292294e-10</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.0006107053486630321</v>
+        <v>7.211413410868062e-11</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.001155867241322994</v>
+        <v>1.330764110019089e-10</v>
       </c>
       <c r="BN14" t="n">
-        <v>0.000624251551926136</v>
+        <v>1.142352878957809e-11</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.0001084687100956216</v>
+        <v>9.839332126837519e-11</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.0005750969867222011</v>
+        <v>6.366753652065071e-11</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0.0001013930304907262</v>
+        <v>1.057489304456816e-10</v>
       </c>
       <c r="BR14" t="n">
-        <v>0.0001757729332894087</v>
+        <v>2.15783196866326e-10</v>
       </c>
       <c r="BS14" t="n">
-        <v>0.0002464959397912025</v>
+        <v>6.60093993354316e-11</v>
       </c>
       <c r="BT14" t="n">
-        <v>0.0003909982042387128</v>
+        <v>1.223709189535072e-10</v>
       </c>
       <c r="BU14" t="n">
-        <v>0.0001433812431059778</v>
+        <v>3.651716151686912e-10</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.002440851414576173</v>
+        <v>3.400453529867065e-11</v>
       </c>
       <c r="BW14" t="n">
-        <v>0.0005644572665914893</v>
+        <v>7.375093591388548e-12</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.0002264044451294467</v>
+        <v>9.727475075438363e-11</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.0004995109047740698</v>
+        <v>9.998688682566481e-11</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0.0001882829674286768</v>
+        <v>5.211621412204437e-11</v>
       </c>
       <c r="CA14" t="n">
-        <v>0.0002947131870314479</v>
+        <v>1.728402143630348e-11</v>
       </c>
       <c r="CB14" t="n">
-        <v>0.0001659547269809991</v>
+        <v>7.271122592911183e-11</v>
       </c>
       <c r="CC14" t="n">
-        <v>0.000253308069659397</v>
+        <v>6.24764129319999e-12</v>
       </c>
       <c r="CD14" t="n">
-        <v>0.0001349720550933853</v>
+        <v>4.785622245706556e-11</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.00103107385803014</v>
+        <v>1.739933197519861e-10</v>
       </c>
       <c r="CF14" t="n">
-        <v>0.0002836918574757874</v>
+        <v>2.854705014043724e-11</v>
       </c>
       <c r="CG14" t="n">
-        <v>0.0002452794287819415</v>
+        <v>5.347971371305604e-11</v>
       </c>
       <c r="CH14" t="n">
-        <v>0.0001308146020164713</v>
+        <v>1.214815192884799e-10</v>
       </c>
       <c r="CI14" t="n">
-        <v>0.0001317678834311664</v>
+        <v>2.186720249319762e-10</v>
       </c>
       <c r="CJ14" t="n">
-        <v>0.0003341020783409476</v>
+        <v>6.966785481843374e-11</v>
       </c>
       <c r="CK14" t="n">
-        <v>0.0001960750669240952</v>
+        <v>5.618482068481256e-11</v>
       </c>
       <c r="CL14" t="n">
-        <v>9.002475417219102e-05</v>
+        <v>7.225639531149852e-11</v>
       </c>
       <c r="CM14" t="n">
-        <v>0.00148152292240411</v>
+        <v>6.206878067072097e-11</v>
       </c>
       <c r="CN14" t="n">
-        <v>0.0005389873986132443</v>
+        <v>1.160405105338214e-10</v>
       </c>
       <c r="CO14" t="n">
-        <v>0.0001981304958462715</v>
+        <v>2.444688063096834e-10</v>
       </c>
       <c r="CP14" t="n">
-        <v>0.0005463762208819389</v>
+        <v>6.458428236655323e-11</v>
       </c>
       <c r="CQ14" t="n">
-        <v>0.000784562318585813</v>
+        <v>2.963725376226023e-10</v>
       </c>
       <c r="CR14" t="n">
-        <v>0.0007044312660582364</v>
+        <v>3.039743456945132e-11</v>
       </c>
       <c r="CS14" t="n">
-        <v>0.001118994667194784</v>
+        <v>6.316977496645393e-11</v>
       </c>
       <c r="CT14" t="n">
-        <v>0.0007002639467827976</v>
+        <v>5.962423610395007e-11</v>
       </c>
       <c r="CU14" t="n">
-        <v>0.0003045173361897469</v>
+        <v>2.366135343212505e-10</v>
       </c>
       <c r="CV14" t="n">
-        <v>0.0001028082624543458</v>
+        <v>8.191036043880828e-11</v>
       </c>
       <c r="CW14" t="n">
-        <v>0.0009183087386190891</v>
+        <v>1.859216253174978e-10</v>
       </c>
       <c r="CX14" t="n">
-        <v>0.0003545683284755796</v>
+        <v>3.365377421182814e-11</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.0004865524533670396</v>
+        <v>5.814864562081468e-11</v>
       </c>
       <c r="CZ14" t="n">
-        <v>0.0002183283068006858</v>
+        <v>6.427250398566287e-11</v>
       </c>
       <c r="DA14" t="n">
-        <v>0.000179987633600831</v>
+        <v>2.262295351052046e-10</v>
       </c>
       <c r="DB14" t="n">
-        <v>0.0002412924804957584</v>
+        <v>1.012656972165793e-12</v>
       </c>
       <c r="DC14" t="n">
-        <v>0.0003479516017250717</v>
+        <v>1.067883073635478e-10</v>
       </c>
       <c r="DD14" t="n">
-        <v>7.603409358125646e-06</v>
+        <v>1.054242942943873e-10</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.0005238026496954262</v>
+        <v>4.168825701311718e-11</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.0006508718943223357</v>
+        <v>3.748274746140368e-10</v>
       </c>
       <c r="DG14" t="n">
-        <v>5.246531509328634e-05</v>
+        <v>3.741793264122606e-10</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.001977031817659736</v>
+        <v>2.001010329655273e-10</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.001065439661033452</v>
+        <v>1.611688560387847e-10</v>
       </c>
       <c r="DJ14" t="n">
-        <v>0.0002703523787204176</v>
+        <v>1.136720162442373e-10</v>
       </c>
       <c r="DK14" t="n">
-        <v>0.0005639686132781208</v>
+        <v>2.228886519795026e-10</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.0002065541048068553</v>
+        <v>6.065955376888255e-11</v>
       </c>
       <c r="DM14" t="n">
-        <v>0.0003551821573637426</v>
+        <v>3.861537825611272e-11</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.0003250412410125136</v>
+        <v>2.609717442147996e-10</v>
       </c>
       <c r="DO14" t="n">
-        <v>0.0003017034323420376</v>
+        <v>2.375999397230544e-10</v>
       </c>
       <c r="DP14" t="n">
-        <v>0.0005711772246286273</v>
+        <v>3.99289004637815e-11</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0.0004107607528567314</v>
+        <v>1.72780192930766e-10</v>
       </c>
       <c r="DR14" t="n">
-        <v>0.0004267902404535562</v>
+        <v>1.205553851191254e-10</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.0002152969245798886</v>
+        <v>1.189504883480907e-10</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.0002094184892484918</v>
+        <v>1.750908446007671e-10</v>
       </c>
       <c r="DU14" t="n">
-        <v>0.0001920658542076126</v>
+        <v>1.103486607645365e-10</v>
       </c>
       <c r="DV14" t="n">
-        <v>5.475203943205997e-05</v>
+        <v>2.247063368709945e-10</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.0001644006406422704</v>
+        <v>1.486741008083214e-10</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.0004748940991703421</v>
+        <v>6.725448670197309e-11</v>
       </c>
       <c r="DY14" t="n">
-        <v>6.825233867857605e-05</v>
+        <v>1.758951040375933e-10</v>
       </c>
       <c r="DZ14" t="n">
-        <v>8.970191993284971e-05</v>
+        <v>8.837658382887525e-11</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.0005935552180744708</v>
+        <v>5.14027154174812e-10</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.0001790811365935951</v>
+        <v>2.366816742593869e-10</v>
       </c>
       <c r="EC14" t="n">
-        <v>9.13669791771099e-05</v>
+        <v>3.486894661897111e-10</v>
       </c>
       <c r="ED14" t="n">
-        <v>0.0001195172662846744</v>
+        <v>4.405320205846941e-11</v>
       </c>
       <c r="EE14" t="n">
-        <v>4.042358341393992e-06</v>
+        <v>4.058056841949043e-12</v>
       </c>
       <c r="EF14" t="n">
-        <v>0.0005967990728095174</v>
+        <v>1.460298375277613e-11</v>
       </c>
       <c r="EG14" t="n">
-        <v>0.001253570197150111</v>
+        <v>1.085770084952031e-10</v>
       </c>
       <c r="EH14" t="n">
-        <v>0.0001913908490678295</v>
+        <v>8.540047835570164e-11</v>
       </c>
       <c r="EI14" t="n">
-        <v>8.722973143449053e-05</v>
+        <v>1.068982263818796e-10</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.0002418204967398196</v>
+        <v>1.798316703882641e-11</v>
       </c>
       <c r="EK14" t="n">
-        <v>5.809215872432105e-05</v>
+        <v>1.106946270756914e-10</v>
       </c>
       <c r="EL14" t="n">
-        <v>0.0001609788741916418</v>
+        <v>6.349390457849324e-11</v>
       </c>
       <c r="EM14" t="n">
-        <v>0.0002199082373408601</v>
+        <v>8.488782593518707e-11</v>
       </c>
       <c r="EN14" t="n">
-        <v>3.959932291763835e-05</v>
+        <v>9.974954889857557e-11</v>
       </c>
       <c r="EO14" t="n">
-        <v>0.0002168589999200776</v>
+        <v>5.904117472699255e-11</v>
       </c>
       <c r="EP14" t="n">
-        <v>7.405025826301426e-05</v>
+        <v>1.521197473541847e-10</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0.0004423432983458042</v>
+        <v>6.116260276023411e-11</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.0002302950160810724</v>
+        <v>2.910285901158716e-11</v>
       </c>
       <c r="ES14" t="n">
-        <v>7.121325324987993e-05</v>
+        <v>2.135892851473642e-10</v>
       </c>
       <c r="ET14" t="n">
-        <v>0.0004635045188479125</v>
+        <v>2.277973226716412e-10</v>
       </c>
       <c r="EU14" t="n">
-        <v>0.0003447415074333549</v>
+        <v>3.757983507712837e-11</v>
       </c>
       <c r="EV14" t="n">
-        <v>0.0009067165665328503</v>
+        <v>6.192208551469847e-11</v>
       </c>
       <c r="EW14" t="n">
-        <v>0.0005168516072444618</v>
+        <v>5.613906908785715e-11</v>
       </c>
       <c r="EX14" t="n">
-        <v>0.00020006881095469</v>
+        <v>6.225641530077652e-11</v>
       </c>
       <c r="EY14" t="n">
-        <v>0.0008944897563196719</v>
+        <v>2.262243725681401e-10</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0.0002752671716734767</v>
+        <v>2.742219992746264e-11</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.0002048621536232531</v>
+        <v>7.89517201615908e-11</v>
       </c>
       <c r="FB14" t="n">
-        <v>2.56908515439136e-05</v>
+        <v>1.067838040214042e-10</v>
       </c>
       <c r="FC14" t="n">
-        <v>0.0002220598398707807</v>
+        <v>2.141253285792288e-10</v>
       </c>
       <c r="FD14" t="n">
-        <v>0.0003616097965277731</v>
+        <v>6.652126766093502e-11</v>
       </c>
       <c r="FE14" t="n">
-        <v>0.0001761477033142</v>
+        <v>1.448636904877176e-10</v>
       </c>
       <c r="FF14" t="n">
-        <v>0.0001342935720458627</v>
+        <v>4.474133216691989e-11</v>
       </c>
       <c r="FG14" t="n">
-        <v>0.0002327393740415573</v>
+        <v>4.938929820674787e-11</v>
       </c>
       <c r="FH14" t="n">
-        <v>7.617331721121445e-05</v>
+        <v>1.304045066374826e-10</v>
       </c>
       <c r="FI14" t="n">
-        <v>0.0003430568613111973</v>
+        <v>3.265999692914079e-10</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.0009686864214017987</v>
+        <v>2.417133160292906e-11</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.0005795203032903373</v>
+        <v>3.350044963656984e-10</v>
       </c>
       <c r="FL14" t="n">
-        <v>0.0004534214967861772</v>
+        <v>1.083372350163536e-10</v>
       </c>
       <c r="FM14" t="n">
-        <v>3.987083618994802e-05</v>
+        <v>4.784382959255318e-11</v>
       </c>
       <c r="FN14" t="n">
-        <v>0.0001442464417777956</v>
+        <v>2.588733116759556e-10</v>
       </c>
       <c r="FO14" t="n">
-        <v>0.0006410012720152736</v>
+        <v>1.625325429799318e-10</v>
       </c>
       <c r="FP14" t="n">
-        <v>0.0009353606146760285</v>
+        <v>2.448636016172401e-10</v>
       </c>
       <c r="FQ14" t="n">
-        <v>0.0009214926394633949</v>
+        <v>4.304793743692414e-10</v>
       </c>
       <c r="FR14" t="n">
-        <v>0.0008270975667983294</v>
+        <v>6.196484991782825e-10</v>
       </c>
       <c r="FS14" t="n">
-        <v>0.0002423790865577757</v>
+        <v>3.97654020822813e-10</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.0001743342872941867</v>
+        <v>1.668545440702829e-10</v>
       </c>
       <c r="FU14" t="n">
-        <v>0.0003871133667416871</v>
+        <v>6.093529847372992e-11</v>
       </c>
       <c r="FV14" t="n">
-        <v>0.0001478217454859987</v>
+        <v>1.493835471988447e-10</v>
       </c>
       <c r="FW14" t="n">
-        <v>0.0001632447965675965</v>
+        <v>2.40331032852481e-10</v>
       </c>
       <c r="FX14" t="n">
-        <v>3.599657429731451e-05</v>
+        <v>1.512806824255364e-10</v>
       </c>
       <c r="FY14" t="n">
-        <v>0.0008112962241284549</v>
+        <v>1.128203433453656e-11</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.0002262651978526264</v>
+        <v>2.119643349729472e-10</v>
       </c>
       <c r="GA14" t="n">
-        <v>0.0001037994152284227</v>
+        <v>2.646443619802596e-10</v>
       </c>
       <c r="GB14" t="n">
-        <v>7.840098987799138e-05</v>
+        <v>1.941168892294343e-10</v>
       </c>
       <c r="GC14" t="n">
-        <v>0.0004117109056096524</v>
+        <v>4.083400839682838e-10</v>
       </c>
       <c r="GD14" t="n">
-        <v>0.0007938856142573059</v>
+        <v>2.627098816265772e-10</v>
       </c>
       <c r="GE14" t="n">
-        <v>0.001036171684972942</v>
+        <v>9.644891829641011e-11</v>
       </c>
       <c r="GF14" t="n">
-        <v>0.0004344294720795006</v>
+        <v>1.420895068271477e-10</v>
       </c>
       <c r="GG14" t="n">
-        <v>0.0003023425815626979</v>
+        <v>2.757439936107442e-11</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2.058714380837046e-05</v>
+        <v>0.0005475124344229698</v>
       </c>
       <c r="B15" t="n">
-        <v>0.0009866023901849985</v>
+        <v>0.008823378011584282</v>
       </c>
       <c r="C15" t="n">
-        <v>4.456725582713261e-05</v>
+        <v>0.001908156787976623</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0006171261193230748</v>
+        <v>0.006176161579787731</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0001197730598505586</v>
+        <v>0.0005996848922222853</v>
       </c>
       <c r="F15" t="n">
-        <v>8.669677481520921e-05</v>
+        <v>0.01316423993557692</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0001150008174590766</v>
+        <v>0.003502516308799386</v>
       </c>
       <c r="H15" t="n">
-        <v>4.820261892746203e-05</v>
+        <v>0.00300425523892045</v>
       </c>
       <c r="I15" t="n">
-        <v>5.167737981537357e-05</v>
+        <v>0.002183638978749514</v>
       </c>
       <c r="J15" t="n">
-        <v>7.600997196277604e-05</v>
+        <v>0.0006422032020054758</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0008762187790125608</v>
+        <v>0.009721655398607254</v>
       </c>
       <c r="L15" t="n">
-        <v>2.135581235052086e-05</v>
+        <v>0.003368637524545193</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0005674986750818789</v>
+        <v>0.00789475254714489</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0001662725262576714</v>
+        <v>0.003818545956164598</v>
       </c>
       <c r="O15" t="n">
-        <v>1.592583976162132e-05</v>
+        <v>0.01366297155618668</v>
       </c>
       <c r="P15" t="n">
-        <v>7.592232577735558e-05</v>
+        <v>0.002156909089535475</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.0001201984123326838</v>
+        <v>0.002867753617465496</v>
       </c>
       <c r="R15" t="n">
-        <v>1.36018843477359e-06</v>
+        <v>0.0007285678293555975</v>
       </c>
       <c r="S15" t="n">
-        <v>6.824116280768067e-05</v>
+        <v>0.0003927446960005909</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0001161544423666783</v>
+        <v>9.818136459216475e-05</v>
       </c>
       <c r="U15" t="n">
-        <v>6.736408977303654e-06</v>
+        <v>0.000882859923876822</v>
       </c>
       <c r="V15" t="n">
-        <v>6.401594146154821e-05</v>
+        <v>0.0009976733708754182</v>
       </c>
       <c r="W15" t="n">
-        <v>6.387772009475157e-05</v>
+        <v>0.0002682059421204031</v>
       </c>
       <c r="X15" t="n">
-        <v>2.223954652436078e-05</v>
+        <v>0.002294214908033609</v>
       </c>
       <c r="Y15" t="n">
-        <v>9.17009892873466e-05</v>
+        <v>0.001264995662495494</v>
       </c>
       <c r="Z15" t="n">
-        <v>7.681331044295803e-05</v>
+        <v>0.001083155977539718</v>
       </c>
       <c r="AA15" t="n">
-        <v>8.83682441781275e-05</v>
+        <v>0.0004038460610900074</v>
       </c>
       <c r="AB15" t="n">
-        <v>8.936501399148256e-05</v>
+        <v>0.001077996334061027</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.0001953913451870903</v>
+        <v>0.0009851752547547221</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.184344182547648e-05</v>
+        <v>0.002241421025246382</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.813059498090297e-05</v>
+        <v>0.00171721784863621</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.088466317218263e-05</v>
+        <v>0.001422866247594357</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.574593418103177e-05</v>
+        <v>0.004208620637655258</v>
       </c>
       <c r="AH15" t="n">
-        <v>6.345196015900001e-05</v>
+        <v>0.0005980970454402268</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.535775663796812e-05</v>
+        <v>0.004694585688412189</v>
       </c>
       <c r="AJ15" t="n">
-        <v>3.597034083213657e-05</v>
+        <v>0.0001632433995837346</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.541487447160762e-05</v>
+        <v>0.001288525527343154</v>
       </c>
       <c r="AL15" t="n">
-        <v>9.909516666084528e-05</v>
+        <v>0.002041961066424847</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.228367455041735e-05</v>
+        <v>0.001601041993126273</v>
       </c>
       <c r="AN15" t="n">
-        <v>2.78607003565412e-05</v>
+        <v>0.001073729712516069</v>
       </c>
       <c r="AO15" t="n">
-        <v>8.777678158367053e-05</v>
+        <v>0.0005343595985323191</v>
       </c>
       <c r="AP15" t="n">
-        <v>6.297202344285324e-05</v>
+        <v>0.0006735683418810368</v>
       </c>
       <c r="AQ15" t="n">
-        <v>7.489058771170676e-05</v>
+        <v>0.0004442062345333397</v>
       </c>
       <c r="AR15" t="n">
-        <v>2.443620360281784e-05</v>
+        <v>0.0006151674897409976</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.496191336831544e-05</v>
+        <v>0.001433438039384782</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.0001037472247844562</v>
+        <v>0.0005919579416513443</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.0006030232179909945</v>
+        <v>0.004419606178998947</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.0001331372477579862</v>
+        <v>0.00281904824078083</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.000193000043509528</v>
+        <v>0.00216713547706604</v>
       </c>
       <c r="AX15" t="n">
-        <v>3.091126563958824e-05</v>
+        <v>0.008539697155356407</v>
       </c>
       <c r="AY15" t="n">
-        <v>6.489126826636493e-05</v>
+        <v>0.006911150179803371</v>
       </c>
       <c r="AZ15" t="n">
-        <v>2.632712130434811e-05</v>
+        <v>0.0004893761943094432</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.344619446783327e-05</v>
+        <v>0.001263384008780122</v>
       </c>
       <c r="BB15" t="n">
-        <v>2.670444882824086e-05</v>
+        <v>0.0002192543906858191</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.848256139666773e-05</v>
+        <v>0.0001342208270216361</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.0001437909522792324</v>
+        <v>0.00205190060660243</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.0001712354278424755</v>
+        <v>0.002242960967123508</v>
       </c>
       <c r="BF15" t="n">
-        <v>0.0001049090351443738</v>
+        <v>0.001632978091947734</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.000108077801996842</v>
+        <v>0.003946074284613132</v>
       </c>
       <c r="BH15" t="n">
-        <v>2.874144047382288e-05</v>
+        <v>0.002923223422840238</v>
       </c>
       <c r="BI15" t="n">
-        <v>6.239317735889927e-05</v>
+        <v>0.001096024876460433</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.0001232745125889778</v>
+        <v>0.003081013448536396</v>
       </c>
       <c r="BK15" t="n">
-        <v>2.83333192783175e-05</v>
+        <v>0.0005288302199915051</v>
       </c>
       <c r="BL15" t="n">
-        <v>8.444831473752856e-05</v>
+        <v>5.047575905336998e-05</v>
       </c>
       <c r="BM15" t="n">
-        <v>4.08679261454381e-05</v>
+        <v>0.0006788767641410232</v>
       </c>
       <c r="BN15" t="n">
-        <v>6.92580288159661e-05</v>
+        <v>6.794737419113517e-05</v>
       </c>
       <c r="BO15" t="n">
-        <v>3.666246266220696e-05</v>
+        <v>0.002264149952679873</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.0001548287982586771</v>
+        <v>0.0003197830519638956</v>
       </c>
       <c r="BQ15" t="n">
-        <v>1.841438461269718e-05</v>
+        <v>0.001804353436455131</v>
       </c>
       <c r="BR15" t="n">
-        <v>3.56006421498023e-05</v>
+        <v>0.0006300853565335274</v>
       </c>
       <c r="BS15" t="n">
-        <v>4.315821206546389e-05</v>
+        <v>0.001342007308267057</v>
       </c>
       <c r="BT15" t="n">
-        <v>7.249508053064346e-05</v>
+        <v>0.001792173599824309</v>
       </c>
       <c r="BU15" t="n">
-        <v>7.311454100999981e-05</v>
+        <v>0.0003481527091935277</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.0003154189616907388</v>
+        <v>0.002788952318951488</v>
       </c>
       <c r="BW15" t="n">
-        <v>7.389087841147557e-05</v>
+        <v>0.0009166655363515019</v>
       </c>
       <c r="BX15" t="n">
-        <v>0.000134873014758341</v>
+        <v>0.002364033833146095</v>
       </c>
       <c r="BY15" t="n">
-        <v>6.045097688911483e-05</v>
+        <v>0.002112470101565123</v>
       </c>
       <c r="BZ15" t="n">
-        <v>1.657731445448007e-05</v>
+        <v>0.003797363955527544</v>
       </c>
       <c r="CA15" t="n">
-        <v>4.772068132297136e-05</v>
+        <v>0.001971497898921371</v>
       </c>
       <c r="CB15" t="n">
-        <v>1.169232291431399e-05</v>
+        <v>0.001094981678761542</v>
       </c>
       <c r="CC15" t="n">
-        <v>6.575268344022334e-05</v>
+        <v>0.001061495626345277</v>
       </c>
       <c r="CD15" t="n">
-        <v>1.539772893011104e-05</v>
+        <v>0.0004785011988133192</v>
       </c>
       <c r="CE15" t="n">
-        <v>0.000168110229424201</v>
+        <v>0.002599111991003156</v>
       </c>
       <c r="CF15" t="n">
-        <v>3.902295793523081e-05</v>
+        <v>0.0004394197021611035</v>
       </c>
       <c r="CG15" t="n">
-        <v>7.015892333583906e-05</v>
+        <v>0.002042599022388458</v>
       </c>
       <c r="CH15" t="n">
-        <v>3.558414755389094e-05</v>
+        <v>0.0001534279290353879</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.914233325805981e-05</v>
+        <v>0.003176635829731822</v>
       </c>
       <c r="CJ15" t="n">
-        <v>2.411348577879835e-05</v>
+        <v>4.200093826511875e-05</v>
       </c>
       <c r="CK15" t="n">
-        <v>4.792635081685148e-06</v>
+        <v>0.0009768196614459157</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.35413208429236e-05</v>
+        <v>0.001617357367649674</v>
       </c>
       <c r="CM15" t="n">
-        <v>0.0002234408457297832</v>
+        <v>0.001359326648525894</v>
       </c>
       <c r="CN15" t="n">
-        <v>4.454784721019678e-05</v>
+        <v>0.000733843189664185</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.845657243393362e-05</v>
+        <v>0.003558741183951497</v>
       </c>
       <c r="CP15" t="n">
-        <v>0.0001562289835419506</v>
+        <v>0.002618294209241867</v>
       </c>
       <c r="CQ15" t="n">
-        <v>0.0001793158007785678</v>
+        <v>0.004037149250507355</v>
       </c>
       <c r="CR15" t="n">
-        <v>0.0001103037866414525</v>
+        <v>0.001056471024639904</v>
       </c>
       <c r="CS15" t="n">
-        <v>0.0001238895347341895</v>
+        <v>0.0004895063466392457</v>
       </c>
       <c r="CT15" t="n">
-        <v>0.000167143385624513</v>
+        <v>0.0008007293799892068</v>
       </c>
       <c r="CU15" t="n">
-        <v>3.422963345656171e-06</v>
+        <v>0.00135025754570961</v>
       </c>
       <c r="CV15" t="n">
-        <v>4.462381639314117e-06</v>
+        <v>0.0006717949872836471</v>
       </c>
       <c r="CW15" t="n">
-        <v>0.0001692528312560171</v>
+        <v>0.00256106024608016</v>
       </c>
       <c r="CX15" t="n">
-        <v>6.75083720125258e-05</v>
+        <v>0.0006506913341581821</v>
       </c>
       <c r="CY15" t="n">
-        <v>0.000101805584563408</v>
+        <v>0.00231688329949975</v>
       </c>
       <c r="CZ15" t="n">
-        <v>3.780703627853654e-05</v>
+        <v>0.0008038936066441238</v>
       </c>
       <c r="DA15" t="n">
-        <v>4.079496193298837e-06</v>
+        <v>0.003514833515509963</v>
       </c>
       <c r="DB15" t="n">
-        <v>3.043870128749404e-05</v>
+        <v>0.000202026276383549</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.806661202863324e-05</v>
+        <v>0.0009962724288925529</v>
       </c>
       <c r="DD15" t="n">
-        <v>8.83587563293986e-06</v>
+        <v>0.001248811604455113</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.00012885921751149</v>
+        <v>0.001768964342772961</v>
       </c>
       <c r="DF15" t="n">
-        <v>9.389823389938101e-05</v>
+        <v>0.003395537380129099</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.988440999411978e-06</v>
+        <v>0.00212015793658793</v>
       </c>
       <c r="DH15" t="n">
-        <v>0.0002003082481678575</v>
+        <v>0.001571991830132902</v>
       </c>
       <c r="DI15" t="n">
-        <v>5.551990034291521e-05</v>
+        <v>0.001447455724701285</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.365374166402034e-05</v>
+        <v>0.004679310601204634</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.640472616301849e-05</v>
+        <v>0.0004849045362789184</v>
       </c>
       <c r="DL15" t="n">
-        <v>5.886787039344199e-05</v>
+        <v>0.002103542909026146</v>
       </c>
       <c r="DM15" t="n">
-        <v>2.441963442834094e-05</v>
+        <v>0.00193028140347451</v>
       </c>
       <c r="DN15" t="n">
-        <v>2.342845982639119e-05</v>
+        <v>0.001440029358491302</v>
       </c>
       <c r="DO15" t="n">
-        <v>6.973365088924766e-05</v>
+        <v>0.002128870226442814</v>
       </c>
       <c r="DP15" t="n">
-        <v>5.043987039243802e-05</v>
+        <v>0.0009467109339311719</v>
       </c>
       <c r="DQ15" t="n">
-        <v>5.389799116528593e-05</v>
+        <v>0.001194258918985724</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.0001247401523869485</v>
+        <v>0.0005156163824722171</v>
       </c>
       <c r="DS15" t="n">
-        <v>9.549231435812544e-06</v>
+        <v>0.000716020877007395</v>
       </c>
       <c r="DT15" t="n">
-        <v>1.45676867759903e-05</v>
+        <v>0.001072788378223777</v>
       </c>
       <c r="DU15" t="n">
-        <v>4.600985266733915e-05</v>
+        <v>0.001817385433241725</v>
       </c>
       <c r="DV15" t="n">
-        <v>4.964384788763709e-05</v>
+        <v>0.001273415051400661</v>
       </c>
       <c r="DW15" t="n">
-        <v>6.240425136638805e-05</v>
+        <v>0.0009840612765401602</v>
       </c>
       <c r="DX15" t="n">
-        <v>0.000141421114676632</v>
+        <v>2.046097506536171e-05</v>
       </c>
       <c r="DY15" t="n">
-        <v>1.8121683751815e-05</v>
+        <v>0.003303293604403734</v>
       </c>
       <c r="DZ15" t="n">
-        <v>6.485759513452649e-05</v>
+        <v>0.0002311880816705525</v>
       </c>
       <c r="EA15" t="n">
-        <v>5.987809345242567e-05</v>
+        <v>0.001490572467446327</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.759539190970827e-05</v>
+        <v>0.0008847626158967614</v>
       </c>
       <c r="EC15" t="n">
-        <v>4.277492189430632e-05</v>
+        <v>0.000655912677757442</v>
       </c>
       <c r="ED15" t="n">
-        <v>9.075358320842497e-06</v>
+        <v>0.002576330676674843</v>
       </c>
       <c r="EE15" t="n">
-        <v>1.131295357481577e-05</v>
+        <v>0.002221991075202823</v>
       </c>
       <c r="EF15" t="n">
-        <v>2.324714478163514e-05</v>
+        <v>0.0006461078301072121</v>
       </c>
       <c r="EG15" t="n">
-        <v>0.0001219745608977973</v>
+        <v>0.001382737653329968</v>
       </c>
       <c r="EH15" t="n">
-        <v>8.0105361121241e-05</v>
+        <v>0.001896741101518273</v>
       </c>
       <c r="EI15" t="n">
-        <v>0.0001091891099349596</v>
+        <v>0.001006520702503622</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.0001343280600849539</v>
+        <v>0.001407909556291997</v>
       </c>
       <c r="EK15" t="n">
-        <v>4.434493348526303e-06</v>
+        <v>0.002321783220395446</v>
       </c>
       <c r="EL15" t="n">
-        <v>2.397709431534167e-05</v>
+        <v>0.0005828192224726081</v>
       </c>
       <c r="EM15" t="n">
-        <v>3.24309803545475e-05</v>
+        <v>0.0007354198605753481</v>
       </c>
       <c r="EN15" t="n">
-        <v>1.993652040255256e-05</v>
+        <v>0.0009256673511117697</v>
       </c>
       <c r="EO15" t="n">
-        <v>1.328662619926035e-07</v>
+        <v>0.0005565554602071643</v>
       </c>
       <c r="EP15" t="n">
-        <v>0.0001928494602907449</v>
+        <v>0.001493731630034745</v>
       </c>
       <c r="EQ15" t="n">
-        <v>9.268540452467278e-05</v>
+        <v>0.001314126886427402</v>
       </c>
       <c r="ER15" t="n">
-        <v>6.527938967337832e-05</v>
+        <v>0.001512611750513315</v>
       </c>
       <c r="ES15" t="n">
-        <v>3.212432056898251e-05</v>
+        <v>0.001181481988169253</v>
       </c>
       <c r="ET15" t="n">
-        <v>2.09929912671214e-05</v>
+        <v>0.0003759206156246364</v>
       </c>
       <c r="EU15" t="n">
-        <v>7.547536370111629e-05</v>
+        <v>0.0004672157228924334</v>
       </c>
       <c r="EV15" t="n">
-        <v>4.480478310142644e-05</v>
+        <v>0.001296358881518245</v>
       </c>
       <c r="EW15" t="n">
-        <v>3.683211252791807e-05</v>
+        <v>0.002072998555377126</v>
       </c>
       <c r="EX15" t="n">
-        <v>3.301293327240273e-05</v>
+        <v>0.00071213289629668</v>
       </c>
       <c r="EY15" t="n">
-        <v>0.0001771846582414582</v>
+        <v>0.003159843385219574</v>
       </c>
       <c r="EZ15" t="n">
-        <v>4.620844993041828e-05</v>
+        <v>0.0003293557674624026</v>
       </c>
       <c r="FA15" t="n">
-        <v>8.301632624352351e-05</v>
+        <v>0.002511363010853529</v>
       </c>
       <c r="FB15" t="n">
-        <v>2.41766592807835e-05</v>
+        <v>1.745301779010333e-05</v>
       </c>
       <c r="FC15" t="n">
-        <v>7.571634341729805e-07</v>
+        <v>0.002916254801675677</v>
       </c>
       <c r="FD15" t="n">
-        <v>2.499610855011269e-05</v>
+        <v>2.33584432862699e-05</v>
       </c>
       <c r="FE15" t="n">
-        <v>2.552679688960779e-06</v>
+        <v>0.0008509992039762437</v>
       </c>
       <c r="FF15" t="n">
-        <v>1.963186514331028e-05</v>
+        <v>0.0006690581212751567</v>
       </c>
       <c r="FG15" t="n">
-        <v>2.297506580362096e-05</v>
+        <v>0.0003480054438114166</v>
       </c>
       <c r="FH15" t="n">
-        <v>8.760490891290829e-05</v>
+        <v>0.002164471196010709</v>
       </c>
       <c r="FI15" t="n">
-        <v>8.097208046820015e-05</v>
+        <v>0.003254947485402226</v>
       </c>
       <c r="FJ15" t="n">
-        <v>6.634354213019833e-05</v>
+        <v>0.002560034394264221</v>
       </c>
       <c r="FK15" t="n">
-        <v>6.755127833457664e-05</v>
+        <v>0.0006257204222492874</v>
       </c>
       <c r="FL15" t="n">
-        <v>3.343030039104633e-05</v>
+        <v>0.004554367158561945</v>
       </c>
       <c r="FM15" t="n">
-        <v>2.439192030578852e-05</v>
+        <v>6.969229434616864e-05</v>
       </c>
       <c r="FN15" t="n">
-        <v>2.715006485232152e-05</v>
+        <v>0.002324848901480436</v>
       </c>
       <c r="FO15" t="n">
-        <v>2.335617500648368e-05</v>
+        <v>0.003492617513984442</v>
       </c>
       <c r="FP15" t="n">
-        <v>0.0001043900119839236</v>
+        <v>0.001500427257269621</v>
       </c>
       <c r="FQ15" t="n">
-        <v>4.411645568325184e-05</v>
+        <v>0.0009535991121083498</v>
       </c>
       <c r="FR15" t="n">
-        <v>0.0001440420746803284</v>
+        <v>0.005923353601247072</v>
       </c>
       <c r="FS15" t="n">
-        <v>5.019141099182889e-06</v>
+        <v>0.001579211791977286</v>
       </c>
       <c r="FT15" t="n">
-        <v>7.356984497164376e-06</v>
+        <v>0.001804167055524886</v>
       </c>
       <c r="FU15" t="n">
-        <v>9.261511149816215e-05</v>
+        <v>0.002435705391690135</v>
       </c>
       <c r="FV15" t="n">
-        <v>2.017623592109885e-05</v>
+        <v>0.0008636143174953759</v>
       </c>
       <c r="FW15" t="n">
-        <v>3.709663724293932e-05</v>
+        <v>0.002795486943796277</v>
       </c>
       <c r="FX15" t="n">
-        <v>4.451838321983814e-05</v>
+        <v>0.001709638745523989</v>
       </c>
       <c r="FY15" t="n">
-        <v>9.112866246141493e-05</v>
+        <v>0.0002916593512054533</v>
       </c>
       <c r="FZ15" t="n">
-        <v>1.549049193272367e-05</v>
+        <v>0.001452957163564861</v>
       </c>
       <c r="GA15" t="n">
-        <v>5.062611671746708e-05</v>
+        <v>0.002749990904703736</v>
       </c>
       <c r="GB15" t="n">
-        <v>2.993959788000211e-05</v>
+        <v>0.0009107612422667444</v>
       </c>
       <c r="GC15" t="n">
-        <v>1.314523069595452e-05</v>
+        <v>0.006003934424370527</v>
       </c>
       <c r="GD15" t="n">
-        <v>0.0001151762844529003</v>
+        <v>0.005575411487370729</v>
       </c>
       <c r="GE15" t="n">
-        <v>0.0001972179743461311</v>
+        <v>0.0008468825253657997</v>
       </c>
       <c r="GF15" t="n">
-        <v>3.116689913440496e-05</v>
+        <v>0.000721051765140146</v>
       </c>
       <c r="GG15" t="n">
-        <v>7.787378126522526e-05</v>
+        <v>0.0005718914908356965</v>
       </c>
     </row>
     <row r="16">
@@ -9534,571 +9534,571 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>8.153043745551258e-05</v>
+        <v>0.1167784035205841</v>
       </c>
       <c r="B17" t="n">
-        <v>0.003475620644167066</v>
+        <v>0.4109968841075897</v>
       </c>
       <c r="C17" t="n">
-        <v>7.31020190869458e-05</v>
+        <v>0.04624879732728004</v>
       </c>
       <c r="D17" t="n">
-        <v>0.00107965525239706</v>
+        <v>0.06781882047653198</v>
       </c>
       <c r="E17" t="n">
-        <v>0.000738389091566205</v>
+        <v>0.2505896389484406</v>
       </c>
       <c r="F17" t="n">
-        <v>0.001429045805707574</v>
+        <v>0.1726661324501038</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0004112602618988603</v>
+        <v>0.1451172977685928</v>
       </c>
       <c r="H17" t="n">
-        <v>0.001133183599449694</v>
+        <v>0.1595468372106552</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0006260884110815823</v>
+        <v>0.2569265365600586</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0005953273503109813</v>
+        <v>0.1170490011572838</v>
       </c>
       <c r="K17" t="n">
-        <v>0.003055971348658204</v>
+        <v>0.5778017044067383</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0002456163638271391</v>
+        <v>0.01162795536220074</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0004427119856700301</v>
+        <v>0.252984493970871</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0001459080813219771</v>
+        <v>0.1702937930822372</v>
       </c>
       <c r="O17" t="n">
-        <v>0.00178953749127686</v>
+        <v>0.1553368419408798</v>
       </c>
       <c r="P17" t="n">
-        <v>0.0005202017491683364</v>
+        <v>0.1442825794219971</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.459411138668656e-05</v>
+        <v>0.05661804229021072</v>
       </c>
       <c r="R17" t="n">
-        <v>0.0007471776916645467</v>
+        <v>0.2100709974765778</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0001608217426110059</v>
+        <v>0.01044661551713943</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0002526182506699115</v>
+        <v>0.08715641498565674</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0003081365721300244</v>
+        <v>0.02545581385493279</v>
       </c>
       <c r="V17" t="n">
-        <v>0.0003347779274918139</v>
+        <v>0.1865131556987762</v>
       </c>
       <c r="W17" t="n">
-        <v>0.0004795514978468418</v>
+        <v>0.1223261207342148</v>
       </c>
       <c r="X17" t="n">
-        <v>0.0003482208703644574</v>
+        <v>0.05177201330661774</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.0002416503848508</v>
+        <v>0.008956991136074066</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.0006584924994967878</v>
+        <v>0.06801671534776688</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.0004698206030298024</v>
+        <v>0.02490286901593208</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.0001624104043003172</v>
+        <v>0.01796473376452923</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.0001873312867246568</v>
+        <v>0.04746041819453239</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.0002977538388222456</v>
+        <v>0.0233343280851841</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.0001127685463870876</v>
+        <v>0.1786893010139465</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.0003115542931482196</v>
+        <v>0.2514139413833618</v>
       </c>
       <c r="AG17" t="n">
-        <v>9.341518307337537e-05</v>
+        <v>0.1521828025579453</v>
       </c>
       <c r="AH17" t="n">
-        <v>5.506776506081223e-05</v>
+        <v>0.009049169719219208</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.0004439088224899024</v>
+        <v>0.1562268733978271</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.0001001452546915971</v>
+        <v>0.09338054060935974</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.0004641771083697677</v>
+        <v>0.05333460122346878</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.0005355927860364318</v>
+        <v>0.1252607554197311</v>
       </c>
       <c r="AM17" t="n">
-        <v>5.922118361922912e-05</v>
+        <v>0.04400226846337318</v>
       </c>
       <c r="AN17" t="n">
-        <v>0.000147799146361649</v>
+        <v>0.1533300876617432</v>
       </c>
       <c r="AO17" t="n">
-        <v>4.252813596394844e-05</v>
+        <v>0.02396076545119286</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.0004354912089183927</v>
+        <v>0.01603959500789642</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.0002263356582261622</v>
+        <v>0.03763952851295471</v>
       </c>
       <c r="AR17" t="n">
-        <v>0.0002774936147034168</v>
+        <v>0.1918636560440063</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.0004297738487366587</v>
+        <v>0.01656492799520493</v>
       </c>
       <c r="AT17" t="n">
-        <v>7.829202513676137e-05</v>
+        <v>0.1345456391572952</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.002264845184981823</v>
+        <v>0.5631925463676453</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.0005460645188577473</v>
+        <v>0.0241903979331255</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.0003504250198602676</v>
+        <v>0.1888709366321564</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.0003412513178773224</v>
+        <v>0.03664050251245499</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.0008532890351489186</v>
+        <v>0.1173742935061455</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.0007423705537803471</v>
+        <v>0.05876385420560837</v>
       </c>
       <c r="BA17" t="n">
-        <v>0.0006455878610722721</v>
+        <v>0.05155038088560104</v>
       </c>
       <c r="BB17" t="n">
-        <v>0.0006363975116983056</v>
+        <v>0.03478825092315674</v>
       </c>
       <c r="BC17" t="n">
-        <v>4.939211066812277e-05</v>
+        <v>0.05784003809094429</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.0007691241335123777</v>
+        <v>0.06534068286418915</v>
       </c>
       <c r="BE17" t="n">
-        <v>0.0008923534769564867</v>
+        <v>0.0004615169018507004</v>
       </c>
       <c r="BF17" t="n">
-        <v>0.0002737119793891907</v>
+        <v>0.01659981161355972</v>
       </c>
       <c r="BG17" t="n">
-        <v>0.000174642467754893</v>
+        <v>0.05003850162029266</v>
       </c>
       <c r="BH17" t="n">
-        <v>0.0005163059686310589</v>
+        <v>0.02657268196344376</v>
       </c>
       <c r="BI17" t="n">
-        <v>0.0002167216007364914</v>
+        <v>0.1903656125068665</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.0005327627877704799</v>
+        <v>0.134371891617775</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.00041542062535882</v>
+        <v>0.142975315451622</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.0001827408996177837</v>
+        <v>0.04075378179550171</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.0002605878980830312</v>
+        <v>0.107510432600975</v>
       </c>
       <c r="BN17" t="n">
-        <v>0.000363129423931241</v>
+        <v>0.03158716857433319</v>
       </c>
       <c r="BO17" t="n">
-        <v>8.713174611330032e-05</v>
+        <v>0.05513418465852737</v>
       </c>
       <c r="BP17" t="n">
-        <v>2.94028504868038e-05</v>
+        <v>0.04317202419042587</v>
       </c>
       <c r="BQ17" t="n">
-        <v>0.0002180162555305287</v>
+        <v>0.06525102257728577</v>
       </c>
       <c r="BR17" t="n">
-        <v>0.0004294584505259991</v>
+        <v>0.1500824987888336</v>
       </c>
       <c r="BS17" t="n">
-        <v>0.000111398876470048</v>
+        <v>0.03413652628660202</v>
       </c>
       <c r="BT17" t="n">
-        <v>0.0001659451518207788</v>
+        <v>0.04628884792327881</v>
       </c>
       <c r="BU17" t="n">
-        <v>1.972864993149415e-05</v>
+        <v>0.05366117134690285</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.001246946048922837</v>
+        <v>0.318471759557724</v>
       </c>
       <c r="BW17" t="n">
-        <v>0.0003675366169773042</v>
+        <v>0.01216505654156208</v>
       </c>
       <c r="BX17" t="n">
-        <v>3.134974394924939e-05</v>
+        <v>0.1582812666893005</v>
       </c>
       <c r="BY17" t="n">
-        <v>0.0002764226519502699</v>
+        <v>0.04933606088161469</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0.0004191215266473591</v>
+        <v>0.1266701221466064</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.239986886503175e-05</v>
+        <v>0.04420836642384529</v>
       </c>
       <c r="CB17" t="n">
-        <v>0.0001257985277334228</v>
+        <v>0.02899765223264694</v>
       </c>
       <c r="CC17" t="n">
-        <v>0.0004661374841816723</v>
+        <v>0.06556722521781921</v>
       </c>
       <c r="CD17" t="n">
-        <v>5.100181442685425e-05</v>
+        <v>0.01918864995241165</v>
       </c>
       <c r="CE17" t="n">
-        <v>0.0006262257229536772</v>
+        <v>0.1473773270845413</v>
       </c>
       <c r="CF17" t="n">
-        <v>0.0003285881830379367</v>
+        <v>0.03224994987249374</v>
       </c>
       <c r="CG17" t="n">
-        <v>0.0002151223015971482</v>
+        <v>0.01347340270876884</v>
       </c>
       <c r="CH17" t="n">
-        <v>0.0001194702563225292</v>
+        <v>0.000429052859544754</v>
       </c>
       <c r="CI17" t="n">
-        <v>7.398489833576605e-05</v>
+        <v>0.04695633053779602</v>
       </c>
       <c r="CJ17" t="n">
-        <v>0.0002292517892783508</v>
+        <v>0.0200503021478653</v>
       </c>
       <c r="CK17" t="n">
-        <v>0.0001326678320765495</v>
+        <v>0.03231089934706688</v>
       </c>
       <c r="CL17" t="n">
-        <v>0.0003583545912988484</v>
+        <v>0.07148510217666626</v>
       </c>
       <c r="CM17" t="n">
-        <v>0.0004817015142180026</v>
+        <v>0.06392045319080353</v>
       </c>
       <c r="CN17" t="n">
-        <v>0.0004817630688194185</v>
+        <v>0.246640682220459</v>
       </c>
       <c r="CO17" t="n">
-        <v>0.0001473407173762098</v>
+        <v>0.04154534637928009</v>
       </c>
       <c r="CP17" t="n">
-        <v>0.0008592132362537086</v>
+        <v>0.1187124103307724</v>
       </c>
       <c r="CQ17" t="n">
-        <v>0.0005278708413243294</v>
+        <v>0.1314001679420471</v>
       </c>
       <c r="CR17" t="n">
-        <v>0.0004090686561539769</v>
+        <v>0.08560758829116821</v>
       </c>
       <c r="CS17" t="n">
-        <v>0.0006902486202307045</v>
+        <v>0.004873479716479778</v>
       </c>
       <c r="CT17" t="n">
-        <v>0.000524751259945333</v>
+        <v>0.02606942504644394</v>
       </c>
       <c r="CU17" t="n">
-        <v>7.990214362507686e-05</v>
+        <v>0.1229733526706696</v>
       </c>
       <c r="CV17" t="n">
-        <v>5.52021010662429e-05</v>
+        <v>0.01688198000192642</v>
       </c>
       <c r="CW17" t="n">
-        <v>0.0005291368579491973</v>
+        <v>0.1252960115671158</v>
       </c>
       <c r="CX17" t="n">
-        <v>0.0003355216176714748</v>
+        <v>0.03706705197691917</v>
       </c>
       <c r="CY17" t="n">
-        <v>0.000413659552577883</v>
+        <v>0.01727365702390671</v>
       </c>
       <c r="CZ17" t="n">
-        <v>0.0001768590009305626</v>
+        <v>0.04133978113532066</v>
       </c>
       <c r="DA17" t="n">
-        <v>6.107371882535517e-05</v>
+        <v>0.06669019162654877</v>
       </c>
       <c r="DB17" t="n">
-        <v>0.0002497613895684481</v>
+        <v>0.01579594425857067</v>
       </c>
       <c r="DC17" t="n">
-        <v>0.0002604143228381872</v>
+        <v>0.02974477037787437</v>
       </c>
       <c r="DD17" t="n">
-        <v>0.0003059135051444173</v>
+        <v>0.0824868306517601</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.000394676229916513</v>
+        <v>0.01201360300183296</v>
       </c>
       <c r="DF17" t="n">
-        <v>0.0002832130994647741</v>
+        <v>0.01950905472040176</v>
       </c>
       <c r="DG17" t="n">
-        <v>4.315715341363102e-05</v>
+        <v>0.06249948963522911</v>
       </c>
       <c r="DH17" t="n">
-        <v>0.001631285645999014</v>
+        <v>0.04299795627593994</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.0008669724920764565</v>
+        <v>0.2534130811691284</v>
       </c>
       <c r="DJ17" t="n">
-        <v>0.001159523730166256</v>
+        <v>0.04133745282888412</v>
       </c>
       <c r="DK17" t="n">
-        <v>0.0005223337793722749</v>
+        <v>0.05263622850179672</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.0005551115609705448</v>
+        <v>0.1349383443593979</v>
       </c>
       <c r="DM17" t="n">
-        <v>0.0006020250730216503</v>
+        <v>0.05382534116506577</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.0001854960719356313</v>
+        <v>0.005558907054364681</v>
       </c>
       <c r="DO17" t="n">
-        <v>4.766117854160257e-06</v>
+        <v>0.08103532344102859</v>
       </c>
       <c r="DP17" t="n">
-        <v>0.0003492338582873344</v>
+        <v>0.005901941563934088</v>
       </c>
       <c r="DQ17" t="n">
-        <v>0.0001101482921512797</v>
+        <v>0.144956111907959</v>
       </c>
       <c r="DR17" t="n">
-        <v>1.902408257592469e-06</v>
+        <v>0.02033074572682381</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.0001391483674524352</v>
+        <v>0.02100457437336445</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.0002764716336969286</v>
+        <v>0.002867495641112328</v>
       </c>
       <c r="DU17" t="n">
-        <v>0.0002138233830919489</v>
+        <v>0.08890531957149506</v>
       </c>
       <c r="DV17" t="n">
-        <v>0.0002526120224501938</v>
+        <v>0.01700521446764469</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.0001583572739036754</v>
+        <v>0.07329682260751724</v>
       </c>
       <c r="DX17" t="n">
-        <v>0.0002104490267811343</v>
+        <v>0.0001690010540187359</v>
       </c>
       <c r="DY17" t="n">
-        <v>0.0004864131333306432</v>
+        <v>0.1160835474729538</v>
       </c>
       <c r="DZ17" t="n">
-        <v>0.0002223165647592396</v>
+        <v>0.05452292412519455</v>
       </c>
       <c r="EA17" t="n">
-        <v>6.416747783077881e-05</v>
+        <v>0.07674086838960648</v>
       </c>
       <c r="EB17" t="n">
-        <v>0.0002265140356030315</v>
+        <v>0.08199232816696167</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.508599962107837e-05</v>
+        <v>0.06778406351804733</v>
       </c>
       <c r="ED17" t="n">
-        <v>0.0001283274468732998</v>
+        <v>0.1432731449604034</v>
       </c>
       <c r="EE17" t="n">
-        <v>0.0005487574962899089</v>
+        <v>0.2251032590866089</v>
       </c>
       <c r="EF17" t="n">
-        <v>0.0002120643621310592</v>
+        <v>0.03228046745061874</v>
       </c>
       <c r="EG17" t="n">
-        <v>0.0009133368730545044</v>
+        <v>0.01852163672447205</v>
       </c>
       <c r="EH17" t="n">
-        <v>3.543821367202327e-05</v>
+        <v>0.02975530177354813</v>
       </c>
       <c r="EI17" t="n">
-        <v>6.784965808037668e-05</v>
+        <v>0.05524975806474686</v>
       </c>
       <c r="EJ17" t="n">
-        <v>0.0004480790230445564</v>
+        <v>0.1086373776197433</v>
       </c>
       <c r="EK17" t="n">
-        <v>0.0001711763616185635</v>
+        <v>0.01947341859340668</v>
       </c>
       <c r="EL17" t="n">
-        <v>0.0003094092535320669</v>
+        <v>0.05919202789664268</v>
       </c>
       <c r="EM17" t="n">
-        <v>3.674428444355726e-05</v>
+        <v>0.06126781180500984</v>
       </c>
       <c r="EN17" t="n">
-        <v>0.0001651004422456026</v>
+        <v>0.09178278595209122</v>
       </c>
       <c r="EO17" t="n">
-        <v>3.656238550320268e-05</v>
+        <v>0.07693487405776978</v>
       </c>
       <c r="EP17" t="n">
-        <v>0.0002551807265263051</v>
+        <v>0.07972411811351776</v>
       </c>
       <c r="EQ17" t="n">
-        <v>0.0007744453032501042</v>
+        <v>0.01176468562334776</v>
       </c>
       <c r="ER17" t="n">
-        <v>0.0007438409957103431</v>
+        <v>0.08355956524610519</v>
       </c>
       <c r="ES17" t="n">
-        <v>0.0004645500448532403</v>
+        <v>0.04088341444730759</v>
       </c>
       <c r="ET17" t="n">
-        <v>0.0002704156213440001</v>
+        <v>0.05377838760614395</v>
       </c>
       <c r="EU17" t="n">
-        <v>0.0006362966960296035</v>
+        <v>0.05152419954538345</v>
       </c>
       <c r="EV17" t="n">
-        <v>0.0006512175896205008</v>
+        <v>0.05473785847425461</v>
       </c>
       <c r="EW17" t="n">
-        <v>8.113745570881292e-05</v>
+        <v>0.02979756519198418</v>
       </c>
       <c r="EX17" t="n">
-        <v>1.838523894548416e-05</v>
+        <v>0.007161185145378113</v>
       </c>
       <c r="EY17" t="n">
-        <v>0.000535500468686223</v>
+        <v>0.1567295044660568</v>
       </c>
       <c r="EZ17" t="n">
-        <v>0.0002838920918293297</v>
+        <v>0.03512879461050034</v>
       </c>
       <c r="FA17" t="n">
-        <v>0.0001464377128286287</v>
+        <v>0.01565518975257874</v>
       </c>
       <c r="FB17" t="n">
-        <v>0.0002086299355141819</v>
+        <v>0.07399865984916687</v>
       </c>
       <c r="FC17" t="n">
-        <v>8.628469367977232e-05</v>
+        <v>0.07222650945186615</v>
       </c>
       <c r="FD17" t="n">
-        <v>0.0004377941659186035</v>
+        <v>0.03515142947435379</v>
       </c>
       <c r="FE17" t="n">
-        <v>0.0002604076871648431</v>
+        <v>0.02826637029647827</v>
       </c>
       <c r="FF17" t="n">
-        <v>0.0004246577445883304</v>
+        <v>0.08941549807786942</v>
       </c>
       <c r="FG17" t="n">
-        <v>0.0001662899885559455</v>
+        <v>0.01824378222227097</v>
       </c>
       <c r="FH17" t="n">
-        <v>3.516658762237057e-05</v>
+        <v>0.1224639788269997</v>
       </c>
       <c r="FI17" t="n">
-        <v>0.0007499672938138247</v>
+        <v>0.04510177299380302</v>
       </c>
       <c r="FJ17" t="n">
-        <v>0.0003010205982718617</v>
+        <v>0.01283210515975952</v>
       </c>
       <c r="FK17" t="n">
-        <v>0.0001266548642888665</v>
+        <v>0.03214867040514946</v>
       </c>
       <c r="FL17" t="n">
-        <v>0.0001752383832354099</v>
+        <v>0.08580112457275391</v>
       </c>
       <c r="FM17" t="n">
-        <v>0.0002981629513669759</v>
+        <v>0.1335624605417252</v>
       </c>
       <c r="FN17" t="n">
-        <v>0.0002524431911297143</v>
+        <v>0.1467871516942978</v>
       </c>
       <c r="FO17" t="n">
-        <v>0.000246103445533663</v>
+        <v>0.1199244111776352</v>
       </c>
       <c r="FP17" t="n">
-        <v>0.000244879862293601</v>
+        <v>0.0263960175216198</v>
       </c>
       <c r="FQ17" t="n">
-        <v>0.0003069716040045023</v>
+        <v>0.1876441091299057</v>
       </c>
       <c r="FR17" t="n">
-        <v>0.0007004642975516617</v>
+        <v>0.08598551154136658</v>
       </c>
       <c r="FS17" t="n">
-        <v>0.0005671463441103697</v>
+        <v>0.1458248198032379</v>
       </c>
       <c r="FT17" t="n">
-        <v>0.0007643052958883345</v>
+        <v>0.07704980671405792</v>
       </c>
       <c r="FU17" t="n">
-        <v>0.0003262875834479928</v>
+        <v>0.2700804471969604</v>
       </c>
       <c r="FV17" t="n">
-        <v>0.0005349087296053767</v>
+        <v>0.1108552664518356</v>
       </c>
       <c r="FW17" t="n">
-        <v>9.82500787358731e-05</v>
+        <v>0.120037741959095</v>
       </c>
       <c r="FX17" t="n">
-        <v>0.0001760334416758269</v>
+        <v>0.1343919038772583</v>
       </c>
       <c r="FY17" t="n">
-        <v>0.0007830619579181075</v>
+        <v>0.08245321363210678</v>
       </c>
       <c r="FZ17" t="n">
-        <v>0.0002250848920084536</v>
+        <v>0.08077282458543777</v>
       </c>
       <c r="GA17" t="n">
-        <v>0.0002258459862787277</v>
+        <v>0.08435171842575073</v>
       </c>
       <c r="GB17" t="n">
-        <v>0.0001955795451067388</v>
+        <v>0.08486682176589966</v>
       </c>
       <c r="GC17" t="n">
-        <v>0.000274924241239205</v>
+        <v>0.06524226814508438</v>
       </c>
       <c r="GD17" t="n">
-        <v>0.0004641708510462195</v>
+        <v>0.00792822428047657</v>
       </c>
       <c r="GE17" t="n">
-        <v>0.001046423800289631</v>
+        <v>0.08967996388673782</v>
       </c>
       <c r="GF17" t="n">
-        <v>0.0001224839506903663</v>
+        <v>0.01558602973818779</v>
       </c>
       <c r="GG17" t="n">
-        <v>0.0001465395180275664</v>
+        <v>0.1327211260795593</v>
       </c>
     </row>
     <row r="18">
